--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124657817</v>
+        <v>124658285</v>
       </c>
       <c r="B2" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473891</v>
+        <v>473876</v>
       </c>
       <c r="R2" t="n">
-        <v>6872741</v>
+        <v>6872637</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124659240</v>
+        <v>124658172</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473810</v>
+        <v>473877</v>
       </c>
       <c r="R4" t="n">
-        <v>6872485</v>
+        <v>6872665</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658285</v>
+        <v>124659214</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473876</v>
+        <v>473837</v>
       </c>
       <c r="R5" t="n">
-        <v>6872637</v>
+        <v>6872441</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124658043</v>
+        <v>124659240</v>
       </c>
       <c r="B6" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473876</v>
+        <v>473810</v>
       </c>
       <c r="R6" t="n">
-        <v>6872692</v>
+        <v>6872485</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1159,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124658172</v>
+        <v>124658043</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473877</v>
+        <v>473876</v>
       </c>
       <c r="R7" t="n">
-        <v>6872665</v>
+        <v>6872692</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124659214</v>
+        <v>124657817</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78455</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473837</v>
+        <v>473891</v>
       </c>
       <c r="R8" t="n">
-        <v>6872441</v>
+        <v>6872741</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124658285</v>
+        <v>124657817</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473876</v>
+        <v>473891</v>
       </c>
       <c r="R2" t="n">
-        <v>6872637</v>
+        <v>6872741</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124658443</v>
+        <v>124658172</v>
       </c>
       <c r="B3" t="n">
         <v>78547</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473856</v>
+        <v>473877</v>
       </c>
       <c r="R3" t="n">
-        <v>6872612</v>
+        <v>6872665</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124658172</v>
+        <v>124658285</v>
       </c>
       <c r="B4" t="n">
         <v>78547</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473877</v>
+        <v>473876</v>
       </c>
       <c r="R4" t="n">
-        <v>6872665</v>
+        <v>6872637</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124659240</v>
+        <v>124658043</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>78455</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473810</v>
+        <v>473876</v>
       </c>
       <c r="R6" t="n">
-        <v>6872485</v>
+        <v>6872692</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1159,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124658043</v>
+        <v>124659240</v>
       </c>
       <c r="B7" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473876</v>
+        <v>473810</v>
       </c>
       <c r="R7" t="n">
-        <v>6872692</v>
+        <v>6872485</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124657817</v>
+        <v>124658443</v>
       </c>
       <c r="B8" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473891</v>
+        <v>473856</v>
       </c>
       <c r="R8" t="n">
-        <v>6872741</v>
+        <v>6872612</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124657817</v>
+        <v>124659240</v>
       </c>
       <c r="B2" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473891</v>
+        <v>473810</v>
       </c>
       <c r="R2" t="n">
-        <v>6872741</v>
+        <v>6872485</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124658172</v>
+        <v>124658285</v>
       </c>
       <c r="B3" t="n">
         <v>78547</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473877</v>
+        <v>473876</v>
       </c>
       <c r="R3" t="n">
-        <v>6872665</v>
+        <v>6872637</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124658285</v>
+        <v>124659214</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473876</v>
+        <v>473837</v>
       </c>
       <c r="R4" t="n">
-        <v>6872637</v>
+        <v>6872441</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124659214</v>
+        <v>124657817</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>78455</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473837</v>
+        <v>473891</v>
       </c>
       <c r="R5" t="n">
-        <v>6872441</v>
+        <v>6872741</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124658043</v>
+        <v>124658443</v>
       </c>
       <c r="B6" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473876</v>
+        <v>473856</v>
       </c>
       <c r="R6" t="n">
-        <v>6872692</v>
+        <v>6872612</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124659240</v>
+        <v>124658172</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473810</v>
+        <v>473877</v>
       </c>
       <c r="R7" t="n">
-        <v>6872485</v>
+        <v>6872665</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124658443</v>
+        <v>124658043</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473856</v>
+        <v>473876</v>
       </c>
       <c r="R8" t="n">
-        <v>6872612</v>
+        <v>6872692</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124659240</v>
+        <v>124658285</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473810</v>
+        <v>473876</v>
       </c>
       <c r="R2" t="n">
-        <v>6872485</v>
+        <v>6872637</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124658285</v>
+        <v>124659214</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473876</v>
+        <v>473837</v>
       </c>
       <c r="R3" t="n">
-        <v>6872637</v>
+        <v>6872441</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124659214</v>
+        <v>124658172</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473837</v>
+        <v>473877</v>
       </c>
       <c r="R4" t="n">
-        <v>6872441</v>
+        <v>6872665</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124657817</v>
+        <v>124658443</v>
       </c>
       <c r="B5" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473891</v>
+        <v>473856</v>
       </c>
       <c r="R5" t="n">
-        <v>6872741</v>
+        <v>6872612</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124658443</v>
+        <v>124657817</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473856</v>
+        <v>473891</v>
       </c>
       <c r="R6" t="n">
-        <v>6872612</v>
+        <v>6872741</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124658172</v>
+        <v>124658043</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473877</v>
+        <v>473876</v>
       </c>
       <c r="R7" t="n">
-        <v>6872665</v>
+        <v>6872692</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124658043</v>
+        <v>124659240</v>
       </c>
       <c r="B8" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473876</v>
+        <v>473810</v>
       </c>
       <c r="R8" t="n">
-        <v>6872692</v>
+        <v>6872485</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1363,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,6 +1391,1536 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124826736</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>473821</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6872738</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124827748</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>473754</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6872803</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124826941</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>473804</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6872761</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124828245</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>473687</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6872750</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124827627</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>473780</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6872856</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124828707</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>473614</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6872815</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124827497</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>473801</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6872850</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124827660</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78455</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>353</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>473782</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6872817</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124828081</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>473705</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6872721</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124828791</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78194</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>473589</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6872813</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124829793</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>473654</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6872997</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124827491</v>
+      </c>
+      <c r="B20" t="n">
+        <v>77738</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>473801</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6872850</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124829811</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79926</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>473654</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6872997</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124828676</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>473614</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6872815</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124828799</v>
+      </c>
+      <c r="B23" t="n">
+        <v>77738</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>473591</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6872817</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124658285</v>
+        <v>124659214</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473876</v>
+        <v>473837</v>
       </c>
       <c r="R2" t="n">
-        <v>6872637</v>
+        <v>6872441</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124659214</v>
+        <v>124658443</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473837</v>
+        <v>473856</v>
       </c>
       <c r="R3" t="n">
-        <v>6872441</v>
+        <v>6872612</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124658172</v>
+        <v>124658043</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473877</v>
+        <v>473876</v>
       </c>
       <c r="R4" t="n">
-        <v>6872665</v>
+        <v>6872692</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658443</v>
+        <v>124658172</v>
       </c>
       <c r="B5" t="n">
         <v>78547</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473856</v>
+        <v>473877</v>
       </c>
       <c r="R5" t="n">
-        <v>6872612</v>
+        <v>6872665</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124658043</v>
+        <v>124659240</v>
       </c>
       <c r="B7" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473876</v>
+        <v>473810</v>
       </c>
       <c r="R7" t="n">
-        <v>6872692</v>
+        <v>6872485</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124659240</v>
+        <v>124658285</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473810</v>
+        <v>473876</v>
       </c>
       <c r="R8" t="n">
-        <v>6872485</v>
+        <v>6872637</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124826736</v>
+        <v>124829811</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>79926</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473821</v>
+        <v>473654</v>
       </c>
       <c r="R9" t="n">
-        <v>6872738</v>
+        <v>6872997</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124827748</v>
+        <v>124827497</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473754</v>
+        <v>473801</v>
       </c>
       <c r="R10" t="n">
-        <v>6872803</v>
+        <v>6872850</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124826941</v>
+        <v>124829793</v>
       </c>
       <c r="B11" t="n">
-        <v>78547</v>
+        <v>79927</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473804</v>
+        <v>473654</v>
       </c>
       <c r="R11" t="n">
-        <v>6872761</v>
+        <v>6872997</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124828245</v>
+        <v>124828081</v>
       </c>
       <c r="B12" t="n">
-        <v>78546</v>
+        <v>79399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473687</v>
+        <v>473705</v>
       </c>
       <c r="R12" t="n">
-        <v>6872750</v>
+        <v>6872721</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124827627</v>
+        <v>124827748</v>
       </c>
       <c r="B13" t="n">
         <v>78547</v>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473780</v>
+        <v>473754</v>
       </c>
       <c r="R13" t="n">
-        <v>6872856</v>
+        <v>6872803</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124828707</v>
+        <v>124827491</v>
       </c>
       <c r="B14" t="n">
-        <v>78546</v>
+        <v>77738</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473614</v>
+        <v>473801</v>
       </c>
       <c r="R14" t="n">
-        <v>6872815</v>
+        <v>6872850</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124827497</v>
+        <v>124827627</v>
       </c>
       <c r="B15" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473801</v>
+        <v>473780</v>
       </c>
       <c r="R15" t="n">
-        <v>6872850</v>
+        <v>6872856</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124827660</v>
+        <v>124828791</v>
       </c>
       <c r="B16" t="n">
-        <v>78455</v>
+        <v>78194</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473782</v>
+        <v>473589</v>
       </c>
       <c r="R16" t="n">
-        <v>6872817</v>
+        <v>6872813</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124828081</v>
+        <v>124828799</v>
       </c>
       <c r="B17" t="n">
-        <v>79399</v>
+        <v>77738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473705</v>
+        <v>473591</v>
       </c>
       <c r="R17" t="n">
-        <v>6872721</v>
+        <v>6872817</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124828791</v>
+        <v>124828245</v>
       </c>
       <c r="B18" t="n">
-        <v>78194</v>
+        <v>78546</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473589</v>
+        <v>473687</v>
       </c>
       <c r="R18" t="n">
-        <v>6872813</v>
+        <v>6872750</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124829793</v>
+        <v>124826941</v>
       </c>
       <c r="B19" t="n">
-        <v>79927</v>
+        <v>78547</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473654</v>
+        <v>473804</v>
       </c>
       <c r="R19" t="n">
-        <v>6872997</v>
+        <v>6872761</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124827491</v>
+        <v>124826736</v>
       </c>
       <c r="B20" t="n">
-        <v>77738</v>
+        <v>78547</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473801</v>
+        <v>473821</v>
       </c>
       <c r="R20" t="n">
-        <v>6872850</v>
+        <v>6872738</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124829811</v>
+        <v>124828676</v>
       </c>
       <c r="B21" t="n">
-        <v>79926</v>
+        <v>78547</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473654</v>
+        <v>473614</v>
       </c>
       <c r="R21" t="n">
-        <v>6872997</v>
+        <v>6872815</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124828676</v>
+        <v>124828707</v>
       </c>
       <c r="B22" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2766,7 +2766,7 @@
         <v>6872815</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124828799</v>
+        <v>124827660</v>
       </c>
       <c r="B23" t="n">
-        <v>77738</v>
+        <v>78455</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473591</v>
+        <v>473782</v>
       </c>
       <c r="R23" t="n">
         <v>6872817</v>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124658043</v>
+        <v>124658172</v>
       </c>
       <c r="B4" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473876</v>
+        <v>473877</v>
       </c>
       <c r="R4" t="n">
-        <v>6872692</v>
+        <v>6872665</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658172</v>
+        <v>124658043</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473877</v>
+        <v>473876</v>
       </c>
       <c r="R5" t="n">
-        <v>6872665</v>
+        <v>6872692</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124659214</v>
+        <v>124658443</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473837</v>
+        <v>473856</v>
       </c>
       <c r="R2" t="n">
-        <v>6872441</v>
+        <v>6872612</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124658443</v>
+        <v>124659214</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473856</v>
+        <v>473837</v>
       </c>
       <c r="R3" t="n">
-        <v>6872612</v>
+        <v>6872441</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124658172</v>
+        <v>124657817</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473877</v>
+        <v>473891</v>
       </c>
       <c r="R4" t="n">
-        <v>6872665</v>
+        <v>6872741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658043</v>
+        <v>124658285</v>
       </c>
       <c r="B5" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
         <v>473876</v>
       </c>
       <c r="R5" t="n">
-        <v>6872692</v>
+        <v>6872637</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124657817</v>
+        <v>124658043</v>
       </c>
       <c r="B6" t="n">
         <v>78455</v>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473891</v>
+        <v>473876</v>
       </c>
       <c r="R6" t="n">
-        <v>6872741</v>
+        <v>6872692</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124658285</v>
+        <v>124658172</v>
       </c>
       <c r="B8" t="n">
         <v>78547</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473876</v>
+        <v>473877</v>
       </c>
       <c r="R8" t="n">
-        <v>6872637</v>
+        <v>6872665</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124829811</v>
+        <v>124828707</v>
       </c>
       <c r="B9" t="n">
-        <v>79926</v>
+        <v>78546</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473654</v>
+        <v>473614</v>
       </c>
       <c r="R9" t="n">
-        <v>6872997</v>
+        <v>6872815</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124827497</v>
+        <v>124829793</v>
       </c>
       <c r="B10" t="n">
-        <v>79399</v>
+        <v>79927</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473801</v>
+        <v>473654</v>
       </c>
       <c r="R10" t="n">
-        <v>6872850</v>
+        <v>6872997</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124829793</v>
+        <v>124828245</v>
       </c>
       <c r="B11" t="n">
-        <v>79927</v>
+        <v>78546</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473654</v>
+        <v>473687</v>
       </c>
       <c r="R11" t="n">
-        <v>6872997</v>
+        <v>6872750</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124828081</v>
+        <v>124826941</v>
       </c>
       <c r="B12" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473705</v>
+        <v>473804</v>
       </c>
       <c r="R12" t="n">
-        <v>6872721</v>
+        <v>6872761</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124827748</v>
+        <v>124827491</v>
       </c>
       <c r="B13" t="n">
-        <v>78547</v>
+        <v>77738</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473754</v>
+        <v>473801</v>
       </c>
       <c r="R13" t="n">
-        <v>6872803</v>
+        <v>6872850</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124827491</v>
+        <v>124828081</v>
       </c>
       <c r="B14" t="n">
-        <v>77738</v>
+        <v>79399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473801</v>
+        <v>473705</v>
       </c>
       <c r="R14" t="n">
-        <v>6872850</v>
+        <v>6872721</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124828791</v>
+        <v>124827748</v>
       </c>
       <c r="B16" t="n">
-        <v>78194</v>
+        <v>78547</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473589</v>
+        <v>473754</v>
       </c>
       <c r="R16" t="n">
-        <v>6872813</v>
+        <v>6872803</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124828245</v>
+        <v>124829811</v>
       </c>
       <c r="B18" t="n">
-        <v>78546</v>
+        <v>79926</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473687</v>
+        <v>473654</v>
       </c>
       <c r="R18" t="n">
-        <v>6872750</v>
+        <v>6872997</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124826941</v>
+        <v>124828791</v>
       </c>
       <c r="B19" t="n">
-        <v>78547</v>
+        <v>78194</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473804</v>
+        <v>473589</v>
       </c>
       <c r="R19" t="n">
-        <v>6872761</v>
+        <v>6872813</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124828707</v>
+        <v>124827497</v>
       </c>
       <c r="B22" t="n">
-        <v>78546</v>
+        <v>79399</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473614</v>
+        <v>473801</v>
       </c>
       <c r="R22" t="n">
-        <v>6872815</v>
+        <v>6872850</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124658443</v>
+        <v>124657817</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473856</v>
+        <v>473891</v>
       </c>
       <c r="R2" t="n">
-        <v>6872612</v>
+        <v>6872741</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124657817</v>
+        <v>124658172</v>
       </c>
       <c r="B4" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473891</v>
+        <v>473877</v>
       </c>
       <c r="R4" t="n">
-        <v>6872741</v>
+        <v>6872665</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124658043</v>
+        <v>124658443</v>
       </c>
       <c r="B6" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473876</v>
+        <v>473856</v>
       </c>
       <c r="R6" t="n">
-        <v>6872692</v>
+        <v>6872612</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124659240</v>
+        <v>124658043</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>78455</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473810</v>
+        <v>473876</v>
       </c>
       <c r="R7" t="n">
-        <v>6872485</v>
+        <v>6872692</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1266,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124658172</v>
+        <v>124659240</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473877</v>
+        <v>473810</v>
       </c>
       <c r="R8" t="n">
-        <v>6872665</v>
+        <v>6872485</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124828707</v>
+        <v>124829811</v>
       </c>
       <c r="B9" t="n">
-        <v>78546</v>
+        <v>79926</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473614</v>
+        <v>473654</v>
       </c>
       <c r="R9" t="n">
-        <v>6872815</v>
+        <v>6872997</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124828245</v>
+        <v>124828799</v>
       </c>
       <c r="B11" t="n">
-        <v>78546</v>
+        <v>77738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473687</v>
+        <v>473591</v>
       </c>
       <c r="R11" t="n">
-        <v>6872750</v>
+        <v>6872817</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124826941</v>
+        <v>124828245</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473804</v>
+        <v>473687</v>
       </c>
       <c r="R12" t="n">
-        <v>6872761</v>
+        <v>6872750</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124827491</v>
+        <v>124828791</v>
       </c>
       <c r="B13" t="n">
-        <v>77738</v>
+        <v>78194</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473801</v>
+        <v>473589</v>
       </c>
       <c r="R13" t="n">
-        <v>6872850</v>
+        <v>6872813</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124828081</v>
+        <v>124827660</v>
       </c>
       <c r="B14" t="n">
-        <v>79399</v>
+        <v>78455</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473705</v>
+        <v>473782</v>
       </c>
       <c r="R14" t="n">
-        <v>6872721</v>
+        <v>6872817</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124827748</v>
+        <v>124826941</v>
       </c>
       <c r="B16" t="n">
         <v>78547</v>
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473754</v>
+        <v>473804</v>
       </c>
       <c r="R16" t="n">
-        <v>6872803</v>
+        <v>6872761</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124828799</v>
+        <v>124828676</v>
       </c>
       <c r="B17" t="n">
-        <v>77738</v>
+        <v>78547</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473591</v>
+        <v>473614</v>
       </c>
       <c r="R17" t="n">
-        <v>6872817</v>
+        <v>6872815</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124829811</v>
+        <v>124827491</v>
       </c>
       <c r="B18" t="n">
-        <v>79926</v>
+        <v>77738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>6487</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473654</v>
+        <v>473801</v>
       </c>
       <c r="R18" t="n">
-        <v>6872997</v>
+        <v>6872850</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124828791</v>
+        <v>124828081</v>
       </c>
       <c r="B19" t="n">
-        <v>78194</v>
+        <v>79399</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473589</v>
+        <v>473705</v>
       </c>
       <c r="R19" t="n">
-        <v>6872813</v>
+        <v>6872721</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124826736</v>
+        <v>124827497</v>
       </c>
       <c r="B20" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473821</v>
+        <v>473801</v>
       </c>
       <c r="R20" t="n">
-        <v>6872738</v>
+        <v>6872850</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124828676</v>
+        <v>124828707</v>
       </c>
       <c r="B21" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2664,7 +2664,7 @@
         <v>6872815</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124827497</v>
+        <v>124826736</v>
       </c>
       <c r="B22" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,13 +2760,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473801</v>
+        <v>473821</v>
       </c>
       <c r="R22" t="n">
-        <v>6872850</v>
+        <v>6872738</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124827660</v>
+        <v>124827748</v>
       </c>
       <c r="B23" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473782</v>
+        <v>473754</v>
       </c>
       <c r="R23" t="n">
-        <v>6872817</v>
+        <v>6872803</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124829793</v>
+        <v>124828799</v>
       </c>
       <c r="B10" t="n">
-        <v>79927</v>
+        <v>77738</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473654</v>
+        <v>473591</v>
       </c>
       <c r="R10" t="n">
-        <v>6872997</v>
+        <v>6872817</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124828799</v>
+        <v>124829793</v>
       </c>
       <c r="B11" t="n">
-        <v>77738</v>
+        <v>79927</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473591</v>
+        <v>473654</v>
       </c>
       <c r="R11" t="n">
-        <v>6872817</v>
+        <v>6872997</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2922,6 +2922,4679 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125073474</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>473716</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6872520</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125073530</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>473728</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6872500</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125073833</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78455</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>353</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>473697</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6872466</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125074232</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>473700</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6872562</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125074047</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78455</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>353</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>473665</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6872487</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125075154</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78455</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>353</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>473625</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6872585</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125075202</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78455</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>353</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>473594</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6872603</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125072596</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>473742</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6872438</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125075295</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>473553</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6872662</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125073936</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>473695</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6872466</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125074741</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79892</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>473756</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6872526</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125074681</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>473765</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6872521</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125076500</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>473798</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6872597</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125074731</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>473769</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6872532</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125075349</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>473530</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6872681</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125075710</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>473570</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6872751</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125075630</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>473566</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6872757</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125075883</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78455</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>353</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>473613</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6872761</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125074165</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78455</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>353</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>473690</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6872539</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125073107</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78842</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>185</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>473750</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6872492</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125072999</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>473747</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6872493</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125073255</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79892</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>473735</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6872503</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125075258</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78455</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>353</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>473585</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6872639</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125075491</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>473523</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6872722</v>
+      </c>
+      <c r="S47" t="n">
+        <v>20</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125073267</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>473732</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6872498</v>
+      </c>
+      <c r="S48" t="n">
+        <v>20</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125074134</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78455</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>353</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>473684</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6872544</v>
+      </c>
+      <c r="S49" t="n">
+        <v>20</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125075505</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78455</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>353</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>473523</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6872722</v>
+      </c>
+      <c r="S50" t="n">
+        <v>20</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125073052</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>473748</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6872489</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125074811</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>473732</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6872579</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125076033</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>473693</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6872740</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125071546</v>
+      </c>
+      <c r="B54" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>473832</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6872552</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Spillning under barrgles tall.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125072827</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>473758</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6872471</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>125073146</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>473748</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6872493</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125073578</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98122</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>473736</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6872499</v>
+      </c>
+      <c r="S57" t="n">
+        <v>20</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125073338</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>473722</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6872521</v>
+      </c>
+      <c r="S58" t="n">
+        <v>20</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125073430</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>473712</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6872523</v>
+      </c>
+      <c r="S59" t="n">
+        <v>20</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Konstaterad på läte.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125074664</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>473761</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6872503</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125072916</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>473748</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6872490</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125072658</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>473760</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6872467</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125072602</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>473742</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6872438</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125073455</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>473712</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6872517</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125076393</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>473731</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6872691</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>125072978</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79892</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>473749</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6872487</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>125075336</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>473532</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6872688</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125074318</v>
+      </c>
+      <c r="B68" t="n">
+        <v>78455</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>353</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>473722</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6872544</v>
+      </c>
+      <c r="S68" t="n">
+        <v>20</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124657817</v>
+        <v>124658443</v>
       </c>
       <c r="B2" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473891</v>
+        <v>473856</v>
       </c>
       <c r="R2" t="n">
-        <v>6872741</v>
+        <v>6872612</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124659214</v>
+        <v>124658285</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473837</v>
+        <v>473876</v>
       </c>
       <c r="R3" t="n">
-        <v>6872441</v>
+        <v>6872637</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124658172</v>
+        <v>124657817</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473877</v>
+        <v>473891</v>
       </c>
       <c r="R4" t="n">
-        <v>6872665</v>
+        <v>6872741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658285</v>
+        <v>124658172</v>
       </c>
       <c r="B5" t="n">
         <v>78547</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473876</v>
+        <v>473877</v>
       </c>
       <c r="R5" t="n">
-        <v>6872637</v>
+        <v>6872665</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124658443</v>
+        <v>124658043</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473856</v>
+        <v>473876</v>
       </c>
       <c r="R6" t="n">
-        <v>6872612</v>
+        <v>6872692</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124658043</v>
+        <v>124659240</v>
       </c>
       <c r="B7" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473876</v>
+        <v>473810</v>
       </c>
       <c r="R7" t="n">
-        <v>6872692</v>
+        <v>6872485</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124659240</v>
+        <v>124659214</v>
       </c>
       <c r="B8" t="n">
         <v>79891</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473810</v>
+        <v>473837</v>
       </c>
       <c r="R8" t="n">
-        <v>6872485</v>
+        <v>6872441</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124829811</v>
+        <v>124827748</v>
       </c>
       <c r="B9" t="n">
-        <v>79926</v>
+        <v>78547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473654</v>
+        <v>473754</v>
       </c>
       <c r="R9" t="n">
-        <v>6872997</v>
+        <v>6872803</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124828799</v>
+        <v>124827497</v>
       </c>
       <c r="B10" t="n">
-        <v>77738</v>
+        <v>79399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473591</v>
+        <v>473801</v>
       </c>
       <c r="R10" t="n">
-        <v>6872817</v>
+        <v>6872850</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124829793</v>
+        <v>124828799</v>
       </c>
       <c r="B11" t="n">
-        <v>79927</v>
+        <v>77738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473654</v>
+        <v>473591</v>
       </c>
       <c r="R11" t="n">
-        <v>6872997</v>
+        <v>6872817</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124828245</v>
+        <v>124827627</v>
       </c>
       <c r="B12" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473687</v>
+        <v>473780</v>
       </c>
       <c r="R12" t="n">
-        <v>6872750</v>
+        <v>6872856</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124828791</v>
+        <v>124829793</v>
       </c>
       <c r="B13" t="n">
-        <v>78194</v>
+        <v>79927</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473589</v>
+        <v>473654</v>
       </c>
       <c r="R13" t="n">
-        <v>6872813</v>
+        <v>6872997</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124827660</v>
+        <v>124829811</v>
       </c>
       <c r="B14" t="n">
-        <v>78455</v>
+        <v>79926</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473782</v>
+        <v>473654</v>
       </c>
       <c r="R14" t="n">
-        <v>6872817</v>
+        <v>6872997</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124827627</v>
+        <v>124828791</v>
       </c>
       <c r="B15" t="n">
-        <v>78547</v>
+        <v>78194</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473780</v>
+        <v>473589</v>
       </c>
       <c r="R15" t="n">
-        <v>6872856</v>
+        <v>6872813</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124826941</v>
+        <v>124828676</v>
       </c>
       <c r="B16" t="n">
         <v>78547</v>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473804</v>
+        <v>473614</v>
       </c>
       <c r="R16" t="n">
-        <v>6872761</v>
+        <v>6872815</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124828676</v>
+        <v>124828707</v>
       </c>
       <c r="B17" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2256,7 +2256,7 @@
         <v>6872815</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124827491</v>
+        <v>124826736</v>
       </c>
       <c r="B18" t="n">
-        <v>77738</v>
+        <v>78547</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473801</v>
+        <v>473821</v>
       </c>
       <c r="R18" t="n">
-        <v>6872850</v>
+        <v>6872738</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124827497</v>
+        <v>124827660</v>
       </c>
       <c r="B20" t="n">
-        <v>79399</v>
+        <v>78455</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473801</v>
+        <v>473782</v>
       </c>
       <c r="R20" t="n">
-        <v>6872850</v>
+        <v>6872817</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124828707</v>
+        <v>124827491</v>
       </c>
       <c r="B21" t="n">
-        <v>78546</v>
+        <v>77738</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473614</v>
+        <v>473801</v>
       </c>
       <c r="R21" t="n">
-        <v>6872815</v>
+        <v>6872850</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124826736</v>
+        <v>124828245</v>
       </c>
       <c r="B22" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,13 +2760,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473821</v>
+        <v>473687</v>
       </c>
       <c r="R22" t="n">
-        <v>6872738</v>
+        <v>6872750</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124827748</v>
+        <v>124826941</v>
       </c>
       <c r="B23" t="n">
         <v>78547</v>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473754</v>
+        <v>473804</v>
       </c>
       <c r="R23" t="n">
-        <v>6872803</v>
+        <v>6872761</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125073474</v>
+        <v>125076393</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,47 +2936,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473716</v>
+        <v>473731</v>
       </c>
       <c r="R24" t="n">
-        <v>6872520</v>
+        <v>6872691</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3009,6 +3000,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3035,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125073530</v>
+        <v>125071546</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,47 +3043,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473728</v>
+        <v>473832</v>
       </c>
       <c r="R25" t="n">
-        <v>6872500</v>
+        <v>6872552</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,6 +3107,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3146,10 +3138,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125073833</v>
+        <v>125073474</v>
       </c>
       <c r="B26" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3158,38 +3150,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473697</v>
+        <v>473716</v>
       </c>
       <c r="R26" t="n">
-        <v>6872466</v>
+        <v>6872520</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3248,10 +3249,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125074232</v>
+        <v>125072658</v>
       </c>
       <c r="B27" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3264,21 +3265,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3288,10 +3289,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473700</v>
+        <v>473760</v>
       </c>
       <c r="R27" t="n">
-        <v>6872562</v>
+        <v>6872467</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3350,7 +3351,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125074047</v>
+        <v>125075505</v>
       </c>
       <c r="B28" t="n">
         <v>78455</v>
@@ -3386,14 +3387,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473665</v>
+        <v>473523</v>
       </c>
       <c r="R28" t="n">
-        <v>6872487</v>
+        <v>6872722</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3452,7 +3453,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125075154</v>
+        <v>125074165</v>
       </c>
       <c r="B29" t="n">
         <v>78455</v>
@@ -3488,14 +3489,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473625</v>
+        <v>473690</v>
       </c>
       <c r="R29" t="n">
-        <v>6872585</v>
+        <v>6872539</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3554,10 +3555,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125075202</v>
+        <v>125074811</v>
       </c>
       <c r="B30" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3570,21 +3571,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3594,13 +3595,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473594</v>
+        <v>473732</v>
       </c>
       <c r="R30" t="n">
-        <v>6872603</v>
+        <v>6872579</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3656,10 +3657,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125072596</v>
+        <v>125075154</v>
       </c>
       <c r="B31" t="n">
-        <v>78546</v>
+        <v>78455</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3672,34 +3673,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473742</v>
+        <v>473625</v>
       </c>
       <c r="R31" t="n">
-        <v>6872438</v>
+        <v>6872585</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3758,10 +3759,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125075295</v>
+        <v>125075710</v>
       </c>
       <c r="B32" t="n">
-        <v>78547</v>
+        <v>79428</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3774,21 +3775,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3798,13 +3799,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473553</v>
+        <v>473570</v>
       </c>
       <c r="R32" t="n">
-        <v>6872662</v>
+        <v>6872751</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3860,10 +3861,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125073936</v>
+        <v>125074741</v>
       </c>
       <c r="B33" t="n">
-        <v>79399</v>
+        <v>79892</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3876,34 +3877,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473695</v>
+        <v>473756</v>
       </c>
       <c r="R33" t="n">
-        <v>6872466</v>
+        <v>6872526</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3962,10 +3963,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125074741</v>
+        <v>125074318</v>
       </c>
       <c r="B34" t="n">
-        <v>79892</v>
+        <v>78455</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3978,21 +3979,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4002,13 +4003,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473756</v>
+        <v>473722</v>
       </c>
       <c r="R34" t="n">
-        <v>6872526</v>
+        <v>6872544</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4064,10 +4065,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125074681</v>
+        <v>125073430</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4076,50 +4077,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473765</v>
+        <v>473712</v>
       </c>
       <c r="R35" t="n">
-        <v>6872521</v>
+        <v>6872523</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4149,6 +4141,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4175,10 +4172,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125076500</v>
+        <v>125074134</v>
       </c>
       <c r="B36" t="n">
-        <v>79891</v>
+        <v>78455</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4191,37 +4188,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473798</v>
+        <v>473684</v>
       </c>
       <c r="R36" t="n">
-        <v>6872597</v>
+        <v>6872544</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4277,10 +4274,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125074731</v>
+        <v>125073052</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4289,47 +4286,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473769</v>
+        <v>473748</v>
       </c>
       <c r="R37" t="n">
-        <v>6872532</v>
+        <v>6872489</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,10 +4478,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125075710</v>
+        <v>125072827</v>
       </c>
       <c r="B39" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4506,34 +4494,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473570</v>
+        <v>473758</v>
       </c>
       <c r="R39" t="n">
-        <v>6872751</v>
+        <v>6872471</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4592,10 +4580,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125075630</v>
+        <v>125073267</v>
       </c>
       <c r="B40" t="n">
-        <v>79399</v>
+        <v>79920</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4604,38 +4592,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473566</v>
+        <v>473732</v>
       </c>
       <c r="R40" t="n">
-        <v>6872757</v>
+        <v>6872498</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4694,10 +4682,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125075883</v>
+        <v>125073338</v>
       </c>
       <c r="B41" t="n">
-        <v>78455</v>
+        <v>79399</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4710,37 +4698,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473613</v>
+        <v>473722</v>
       </c>
       <c r="R41" t="n">
-        <v>6872761</v>
+        <v>6872521</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4796,10 +4784,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125074165</v>
+        <v>125073936</v>
       </c>
       <c r="B42" t="n">
-        <v>78455</v>
+        <v>79399</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4812,21 +4800,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4836,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473690</v>
+        <v>473695</v>
       </c>
       <c r="R42" t="n">
-        <v>6872539</v>
+        <v>6872466</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4898,10 +4886,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125073107</v>
+        <v>125075258</v>
       </c>
       <c r="B43" t="n">
-        <v>78842</v>
+        <v>78455</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4914,34 +4902,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473750</v>
+        <v>473585</v>
       </c>
       <c r="R43" t="n">
-        <v>6872492</v>
+        <v>6872639</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5000,10 +4988,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125072999</v>
+        <v>125072916</v>
       </c>
       <c r="B44" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5012,25 +5000,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5040,10 +5028,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473747</v>
+        <v>473748</v>
       </c>
       <c r="R44" t="n">
-        <v>6872493</v>
+        <v>6872490</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5102,10 +5090,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125073255</v>
+        <v>125072602</v>
       </c>
       <c r="B45" t="n">
-        <v>79892</v>
+        <v>78547</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5118,21 +5106,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5142,10 +5130,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473735</v>
+        <v>473742</v>
       </c>
       <c r="R45" t="n">
-        <v>6872503</v>
+        <v>6872438</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5204,10 +5192,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125075258</v>
+        <v>125074681</v>
       </c>
       <c r="B46" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5216,41 +5204,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473585</v>
+        <v>473765</v>
       </c>
       <c r="R46" t="n">
-        <v>6872639</v>
+        <v>6872521</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5306,10 +5303,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125075491</v>
+        <v>125073530</v>
       </c>
       <c r="B47" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5318,41 +5315,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473523</v>
+        <v>473728</v>
       </c>
       <c r="R47" t="n">
-        <v>6872722</v>
+        <v>6872500</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5408,10 +5414,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125073267</v>
+        <v>125075336</v>
       </c>
       <c r="B48" t="n">
-        <v>79920</v>
+        <v>78547</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5420,41 +5426,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473732</v>
+        <v>473532</v>
       </c>
       <c r="R48" t="n">
-        <v>6872498</v>
+        <v>6872688</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5510,10 +5516,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125074134</v>
+        <v>125072999</v>
       </c>
       <c r="B49" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5526,21 +5532,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5550,13 +5556,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473684</v>
+        <v>473747</v>
       </c>
       <c r="R49" t="n">
-        <v>6872544</v>
+        <v>6872493</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5612,10 +5618,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125075505</v>
+        <v>125072978</v>
       </c>
       <c r="B50" t="n">
-        <v>78455</v>
+        <v>79892</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5628,37 +5634,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473523</v>
+        <v>473749</v>
       </c>
       <c r="R50" t="n">
-        <v>6872722</v>
+        <v>6872487</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5714,10 +5720,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125073052</v>
+        <v>125075295</v>
       </c>
       <c r="B51" t="n">
-        <v>79920</v>
+        <v>78547</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5726,41 +5732,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473748</v>
+        <v>473553</v>
       </c>
       <c r="R51" t="n">
-        <v>6872489</v>
+        <v>6872662</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5816,10 +5822,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125074811</v>
+        <v>125073146</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5828,38 +5834,47 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473732</v>
+        <v>473748</v>
       </c>
       <c r="R52" t="n">
-        <v>6872579</v>
+        <v>6872493</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5918,10 +5933,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125076033</v>
+        <v>125075202</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>78455</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5934,21 +5949,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5958,13 +5973,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473693</v>
+        <v>473594</v>
       </c>
       <c r="R53" t="n">
-        <v>6872740</v>
+        <v>6872603</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5994,11 +6009,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6025,10 +6035,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125071546</v>
+        <v>125073578</v>
       </c>
       <c r="B54" t="n">
-        <v>56722</v>
+        <v>98122</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6041,37 +6051,46 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473832</v>
+        <v>473736</v>
       </c>
       <c r="R54" t="n">
-        <v>6872552</v>
+        <v>6872499</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6101,11 +6120,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6132,10 +6146,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125072827</v>
+        <v>125075491</v>
       </c>
       <c r="B55" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6148,37 +6162,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473758</v>
+        <v>473523</v>
       </c>
       <c r="R55" t="n">
-        <v>6872471</v>
+        <v>6872722</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6234,7 +6248,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125073146</v>
+        <v>125074664</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -6269,7 +6283,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6279,14 +6293,14 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473748</v>
+        <v>473761</v>
       </c>
       <c r="R56" t="n">
-        <v>6872493</v>
+        <v>6872503</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6345,10 +6359,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125073578</v>
+        <v>125073255</v>
       </c>
       <c r="B57" t="n">
-        <v>98122</v>
+        <v>79892</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6357,50 +6371,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473736</v>
+        <v>473735</v>
       </c>
       <c r="R57" t="n">
-        <v>6872499</v>
+        <v>6872503</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6456,7 +6461,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125073338</v>
+        <v>125075630</v>
       </c>
       <c r="B58" t="n">
         <v>79399</v>
@@ -6492,14 +6497,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>473722</v>
+        <v>473566</v>
       </c>
       <c r="R58" t="n">
-        <v>6872521</v>
+        <v>6872757</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6558,10 +6563,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125073430</v>
+        <v>125076033</v>
       </c>
       <c r="B59" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6574,37 +6579,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473712</v>
+        <v>473693</v>
       </c>
       <c r="R59" t="n">
-        <v>6872523</v>
+        <v>6872740</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6638,7 +6643,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Konstaterad på läte.</t>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6665,7 +6670,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125074664</v>
+        <v>125074731</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -6700,7 +6705,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6714,10 +6719,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473761</v>
+        <v>473769</v>
       </c>
       <c r="R60" t="n">
-        <v>6872503</v>
+        <v>6872532</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6776,10 +6781,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125072916</v>
+        <v>125075883</v>
       </c>
       <c r="B61" t="n">
-        <v>79927</v>
+        <v>78455</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6788,38 +6793,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473748</v>
+        <v>473613</v>
       </c>
       <c r="R61" t="n">
-        <v>6872490</v>
+        <v>6872761</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6878,10 +6883,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125072658</v>
+        <v>125076500</v>
       </c>
       <c r="B62" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6894,34 +6899,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>473760</v>
+        <v>473798</v>
       </c>
       <c r="R62" t="n">
-        <v>6872467</v>
+        <v>6872597</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6980,10 +6985,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125072602</v>
+        <v>125072596</v>
       </c>
       <c r="B63" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6996,21 +7001,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7082,10 +7087,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125073455</v>
+        <v>125074047</v>
       </c>
       <c r="B64" t="n">
-        <v>79399</v>
+        <v>78455</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7098,21 +7103,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7122,13 +7127,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>473712</v>
+        <v>473665</v>
       </c>
       <c r="R64" t="n">
-        <v>6872517</v>
+        <v>6872487</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7184,10 +7189,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125076393</v>
+        <v>125074232</v>
       </c>
       <c r="B65" t="n">
-        <v>57513</v>
+        <v>78547</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7200,34 +7205,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473731</v>
+        <v>473700</v>
       </c>
       <c r="R65" t="n">
-        <v>6872691</v>
+        <v>6872562</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7260,11 +7265,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7291,10 +7291,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125072978</v>
+        <v>125073107</v>
       </c>
       <c r="B66" t="n">
-        <v>79892</v>
+        <v>78842</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7307,21 +7307,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7331,13 +7331,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>473749</v>
+        <v>473750</v>
       </c>
       <c r="R66" t="n">
-        <v>6872487</v>
+        <v>6872492</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7393,10 +7393,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125075336</v>
+        <v>125073455</v>
       </c>
       <c r="B67" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7409,34 +7409,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>473532</v>
+        <v>473712</v>
       </c>
       <c r="R67" t="n">
-        <v>6872688</v>
+        <v>6872517</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7495,7 +7495,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125074318</v>
+        <v>125073833</v>
       </c>
       <c r="B68" t="n">
         <v>78455</v>
@@ -7531,17 +7531,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>473722</v>
+        <v>473697</v>
       </c>
       <c r="R68" t="n">
-        <v>6872544</v>
+        <v>6872466</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124829793</v>
+        <v>124828791</v>
       </c>
       <c r="B13" t="n">
-        <v>79927</v>
+        <v>78194</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473654</v>
+        <v>473589</v>
       </c>
       <c r="R13" t="n">
-        <v>6872997</v>
+        <v>6872813</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124829811</v>
+        <v>124829793</v>
       </c>
       <c r="B14" t="n">
-        <v>79926</v>
+        <v>79927</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124828791</v>
+        <v>124829811</v>
       </c>
       <c r="B15" t="n">
-        <v>78194</v>
+        <v>79926</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473589</v>
+        <v>473654</v>
       </c>
       <c r="R15" t="n">
-        <v>6872813</v>
+        <v>6872997</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -6248,10 +6248,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125074664</v>
+        <v>125075630</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>79399</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6260,50 +6260,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473761</v>
+        <v>473566</v>
       </c>
       <c r="R56" t="n">
-        <v>6872503</v>
+        <v>6872757</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6359,10 +6350,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125073255</v>
+        <v>125074664</v>
       </c>
       <c r="B57" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6371,35 +6362,44 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473735</v>
+        <v>473761</v>
       </c>
       <c r="R57" t="n">
         <v>6872503</v>
@@ -6461,10 +6461,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125075630</v>
+        <v>125073255</v>
       </c>
       <c r="B58" t="n">
-        <v>79399</v>
+        <v>79892</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6477,37 +6477,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>473566</v>
+        <v>473735</v>
       </c>
       <c r="R58" t="n">
-        <v>6872757</v>
+        <v>6872503</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124658443</v>
+        <v>124658043</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473856</v>
+        <v>473876</v>
       </c>
       <c r="R2" t="n">
-        <v>6872612</v>
+        <v>6872692</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124658285</v>
+        <v>124659240</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473876</v>
+        <v>473810</v>
       </c>
       <c r="R3" t="n">
-        <v>6872637</v>
+        <v>6872485</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124657817</v>
+        <v>124659214</v>
       </c>
       <c r="B4" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473891</v>
+        <v>473837</v>
       </c>
       <c r="R4" t="n">
-        <v>6872741</v>
+        <v>6872441</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124658043</v>
+        <v>124658443</v>
       </c>
       <c r="B6" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473876</v>
+        <v>473856</v>
       </c>
       <c r="R6" t="n">
-        <v>6872692</v>
+        <v>6872612</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124659240</v>
+        <v>124657817</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>78455</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473810</v>
+        <v>473891</v>
       </c>
       <c r="R7" t="n">
-        <v>6872485</v>
+        <v>6872741</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124659214</v>
+        <v>124658285</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473837</v>
+        <v>473876</v>
       </c>
       <c r="R8" t="n">
-        <v>6872441</v>
+        <v>6872637</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124827748</v>
+        <v>124827497</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473754</v>
+        <v>473801</v>
       </c>
       <c r="R9" t="n">
-        <v>6872803</v>
+        <v>6872850</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124827497</v>
+        <v>124829811</v>
       </c>
       <c r="B10" t="n">
-        <v>79399</v>
+        <v>79926</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473801</v>
+        <v>473654</v>
       </c>
       <c r="R10" t="n">
-        <v>6872850</v>
+        <v>6872997</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124828799</v>
+        <v>124829793</v>
       </c>
       <c r="B11" t="n">
-        <v>77738</v>
+        <v>79927</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473591</v>
+        <v>473654</v>
       </c>
       <c r="R11" t="n">
-        <v>6872817</v>
+        <v>6872997</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124827627</v>
+        <v>124826736</v>
       </c>
       <c r="B12" t="n">
         <v>78547</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473780</v>
+        <v>473821</v>
       </c>
       <c r="R12" t="n">
-        <v>6872856</v>
+        <v>6872738</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124828791</v>
+        <v>124827660</v>
       </c>
       <c r="B13" t="n">
-        <v>78194</v>
+        <v>78455</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473589</v>
+        <v>473782</v>
       </c>
       <c r="R13" t="n">
-        <v>6872813</v>
+        <v>6872817</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124829793</v>
+        <v>124827748</v>
       </c>
       <c r="B14" t="n">
-        <v>79927</v>
+        <v>78547</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473654</v>
+        <v>473754</v>
       </c>
       <c r="R14" t="n">
-        <v>6872997</v>
+        <v>6872803</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124829811</v>
+        <v>124828245</v>
       </c>
       <c r="B15" t="n">
-        <v>79926</v>
+        <v>78546</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473654</v>
+        <v>473687</v>
       </c>
       <c r="R15" t="n">
-        <v>6872997</v>
+        <v>6872750</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124828676</v>
+        <v>124827627</v>
       </c>
       <c r="B16" t="n">
         <v>78547</v>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473614</v>
+        <v>473780</v>
       </c>
       <c r="R16" t="n">
-        <v>6872815</v>
+        <v>6872856</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124828707</v>
+        <v>124828676</v>
       </c>
       <c r="B17" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2256,7 +2256,7 @@
         <v>6872815</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124826736</v>
+        <v>124827491</v>
       </c>
       <c r="B18" t="n">
-        <v>78547</v>
+        <v>77738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473821</v>
+        <v>473801</v>
       </c>
       <c r="R18" t="n">
-        <v>6872738</v>
+        <v>6872850</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124828081</v>
+        <v>124828707</v>
       </c>
       <c r="B19" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,13 +2454,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473705</v>
+        <v>473614</v>
       </c>
       <c r="R19" t="n">
-        <v>6872721</v>
+        <v>6872815</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124827660</v>
+        <v>124826941</v>
       </c>
       <c r="B20" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473782</v>
+        <v>473804</v>
       </c>
       <c r="R20" t="n">
-        <v>6872817</v>
+        <v>6872761</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,7 +2618,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124827491</v>
+        <v>124828799</v>
       </c>
       <c r="B21" t="n">
         <v>77738</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473801</v>
+        <v>473591</v>
       </c>
       <c r="R21" t="n">
-        <v>6872850</v>
+        <v>6872817</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124828245</v>
+        <v>124828791</v>
       </c>
       <c r="B22" t="n">
-        <v>78546</v>
+        <v>78194</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,13 +2760,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473687</v>
+        <v>473589</v>
       </c>
       <c r="R22" t="n">
-        <v>6872750</v>
+        <v>6872813</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124826941</v>
+        <v>124828081</v>
       </c>
       <c r="B23" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473804</v>
+        <v>473705</v>
       </c>
       <c r="R23" t="n">
-        <v>6872761</v>
+        <v>6872721</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125076393</v>
+        <v>125075202</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>78455</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,13 +2964,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473731</v>
+        <v>473594</v>
       </c>
       <c r="R24" t="n">
-        <v>6872691</v>
+        <v>6872603</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3000,11 +3000,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3031,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125071546</v>
+        <v>125073267</v>
       </c>
       <c r="B25" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,13 +3066,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473832</v>
+        <v>473732</v>
       </c>
       <c r="R25" t="n">
-        <v>6872552</v>
+        <v>6872498</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3107,11 +3102,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3138,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125073474</v>
+        <v>125076500</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3150,47 +3140,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473716</v>
+        <v>473798</v>
       </c>
       <c r="R26" t="n">
-        <v>6872520</v>
+        <v>6872597</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125072658</v>
+        <v>125075295</v>
       </c>
       <c r="B27" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,37 +3246,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473760</v>
+        <v>473553</v>
       </c>
       <c r="R27" t="n">
-        <v>6872467</v>
+        <v>6872662</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3351,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125075505</v>
+        <v>125072596</v>
       </c>
       <c r="B28" t="n">
-        <v>78455</v>
+        <v>78546</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3367,37 +3348,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473523</v>
+        <v>473742</v>
       </c>
       <c r="R28" t="n">
-        <v>6872722</v>
+        <v>6872438</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3453,7 +3434,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125074165</v>
+        <v>125074318</v>
       </c>
       <c r="B29" t="n">
         <v>78455</v>
@@ -3489,17 +3470,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473690</v>
+        <v>473722</v>
       </c>
       <c r="R29" t="n">
-        <v>6872539</v>
+        <v>6872544</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3555,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125074811</v>
+        <v>125075336</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3571,21 +3552,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3595,10 +3576,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473732</v>
+        <v>473532</v>
       </c>
       <c r="R30" t="n">
-        <v>6872579</v>
+        <v>6872688</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3657,10 +3638,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125075154</v>
+        <v>125076033</v>
       </c>
       <c r="B31" t="n">
-        <v>78455</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3673,21 +3654,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3697,10 +3678,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473625</v>
+        <v>473693</v>
       </c>
       <c r="R31" t="n">
-        <v>6872585</v>
+        <v>6872740</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3733,6 +3714,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3759,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125075710</v>
+        <v>125072999</v>
       </c>
       <c r="B32" t="n">
-        <v>79428</v>
+        <v>79891</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3775,34 +3761,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473570</v>
+        <v>473747</v>
       </c>
       <c r="R32" t="n">
-        <v>6872751</v>
+        <v>6872493</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3861,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125074741</v>
+        <v>125073338</v>
       </c>
       <c r="B33" t="n">
-        <v>79892</v>
+        <v>79399</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3877,37 +3863,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473756</v>
+        <v>473722</v>
       </c>
       <c r="R33" t="n">
-        <v>6872526</v>
+        <v>6872521</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3963,7 +3949,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125074318</v>
+        <v>125075883</v>
       </c>
       <c r="B34" t="n">
         <v>78455</v>
@@ -4003,13 +3989,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473722</v>
+        <v>473613</v>
       </c>
       <c r="R34" t="n">
-        <v>6872544</v>
+        <v>6872761</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4065,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125073430</v>
+        <v>125073833</v>
       </c>
       <c r="B35" t="n">
-        <v>57666</v>
+        <v>78455</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4081,21 +4067,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4105,13 +4091,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473712</v>
+        <v>473697</v>
       </c>
       <c r="R35" t="n">
-        <v>6872523</v>
+        <v>6872466</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4141,11 +4127,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4172,10 +4153,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125074134</v>
+        <v>125075710</v>
       </c>
       <c r="B36" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4188,37 +4169,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473684</v>
+        <v>473570</v>
       </c>
       <c r="R36" t="n">
-        <v>6872544</v>
+        <v>6872751</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4274,10 +4255,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125073052</v>
+        <v>125072602</v>
       </c>
       <c r="B37" t="n">
-        <v>79920</v>
+        <v>78547</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4286,25 +4267,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4314,10 +4295,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473748</v>
+        <v>473742</v>
       </c>
       <c r="R37" t="n">
-        <v>6872489</v>
+        <v>6872438</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4376,10 +4357,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125075349</v>
+        <v>125075154</v>
       </c>
       <c r="B38" t="n">
-        <v>78546</v>
+        <v>78455</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4392,21 +4373,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4416,10 +4397,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473530</v>
+        <v>473625</v>
       </c>
       <c r="R38" t="n">
-        <v>6872681</v>
+        <v>6872585</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4478,10 +4459,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125072827</v>
+        <v>125074165</v>
       </c>
       <c r="B39" t="n">
-        <v>78546</v>
+        <v>78455</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4494,21 +4475,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4518,10 +4499,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473758</v>
+        <v>473690</v>
       </c>
       <c r="R39" t="n">
-        <v>6872471</v>
+        <v>6872539</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4580,10 +4561,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125073267</v>
+        <v>125073578</v>
       </c>
       <c r="B40" t="n">
-        <v>79920</v>
+        <v>98122</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4596,34 +4577,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473732</v>
+        <v>473736</v>
       </c>
       <c r="R40" t="n">
-        <v>6872498</v>
+        <v>6872499</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4682,10 +4672,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125073338</v>
+        <v>125074741</v>
       </c>
       <c r="B41" t="n">
-        <v>79399</v>
+        <v>79892</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4698,37 +4688,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473722</v>
+        <v>473756</v>
       </c>
       <c r="R41" t="n">
-        <v>6872521</v>
+        <v>6872526</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4784,10 +4774,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125073936</v>
+        <v>125075258</v>
       </c>
       <c r="B42" t="n">
-        <v>79399</v>
+        <v>78455</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4800,37 +4790,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473695</v>
+        <v>473585</v>
       </c>
       <c r="R42" t="n">
-        <v>6872466</v>
+        <v>6872639</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4886,10 +4876,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125075258</v>
+        <v>125073107</v>
       </c>
       <c r="B43" t="n">
-        <v>78455</v>
+        <v>78842</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4902,34 +4892,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473585</v>
+        <v>473750</v>
       </c>
       <c r="R43" t="n">
-        <v>6872639</v>
+        <v>6872492</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4988,10 +4978,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125072916</v>
+        <v>125074731</v>
       </c>
       <c r="B44" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5000,38 +4990,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473748</v>
+        <v>473769</v>
       </c>
       <c r="R44" t="n">
-        <v>6872490</v>
+        <v>6872532</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5090,10 +5089,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125072602</v>
+        <v>125074664</v>
       </c>
       <c r="B45" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5102,38 +5101,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473742</v>
+        <v>473761</v>
       </c>
       <c r="R45" t="n">
-        <v>6872438</v>
+        <v>6872503</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5192,10 +5200,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125074681</v>
+        <v>125072658</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5204,47 +5212,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473765</v>
+        <v>473760</v>
       </c>
       <c r="R46" t="n">
-        <v>6872521</v>
+        <v>6872467</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5303,10 +5302,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125073530</v>
+        <v>125071546</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5315,47 +5314,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473728</v>
+        <v>473832</v>
       </c>
       <c r="R47" t="n">
-        <v>6872500</v>
+        <v>6872552</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5388,6 +5378,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5414,10 +5409,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125075336</v>
+        <v>125073430</v>
       </c>
       <c r="B48" t="n">
-        <v>78547</v>
+        <v>57666</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5430,37 +5425,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473532</v>
+        <v>473712</v>
       </c>
       <c r="R48" t="n">
-        <v>6872688</v>
+        <v>6872523</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5490,6 +5485,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5516,10 +5516,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125072999</v>
+        <v>125073455</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>79399</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5532,21 +5532,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473747</v>
+        <v>473712</v>
       </c>
       <c r="R49" t="n">
-        <v>6872493</v>
+        <v>6872517</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5618,7 +5618,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125072978</v>
+        <v>125073255</v>
       </c>
       <c r="B50" t="n">
         <v>79892</v>
@@ -5658,10 +5658,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473749</v>
+        <v>473735</v>
       </c>
       <c r="R50" t="n">
-        <v>6872487</v>
+        <v>6872503</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,10 +5720,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125075295</v>
+        <v>125074134</v>
       </c>
       <c r="B51" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5736,34 +5736,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473553</v>
+        <v>473684</v>
       </c>
       <c r="R51" t="n">
-        <v>6872662</v>
+        <v>6872544</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5933,7 +5933,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125075202</v>
+        <v>125075505</v>
       </c>
       <c r="B53" t="n">
         <v>78455</v>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473594</v>
+        <v>473523</v>
       </c>
       <c r="R53" t="n">
-        <v>6872603</v>
+        <v>6872722</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6035,10 +6035,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125073578</v>
+        <v>125075491</v>
       </c>
       <c r="B54" t="n">
-        <v>98122</v>
+        <v>79428</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6047,47 +6047,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473736</v>
+        <v>473523</v>
       </c>
       <c r="R54" t="n">
-        <v>6872499</v>
+        <v>6872722</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6146,10 +6137,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125075491</v>
+        <v>125074232</v>
       </c>
       <c r="B55" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6162,37 +6153,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473523</v>
+        <v>473700</v>
       </c>
       <c r="R55" t="n">
-        <v>6872722</v>
+        <v>6872562</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6350,7 +6341,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125074664</v>
+        <v>125074681</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -6385,7 +6376,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6399,10 +6390,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473761</v>
+        <v>473765</v>
       </c>
       <c r="R57" t="n">
-        <v>6872503</v>
+        <v>6872521</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6461,10 +6452,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125073255</v>
+        <v>125073936</v>
       </c>
       <c r="B58" t="n">
-        <v>79892</v>
+        <v>79399</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6477,21 +6468,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6501,10 +6492,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>473735</v>
+        <v>473695</v>
       </c>
       <c r="R58" t="n">
-        <v>6872503</v>
+        <v>6872466</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6563,7 +6554,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125076033</v>
+        <v>125076393</v>
       </c>
       <c r="B59" t="n">
         <v>57513</v>
@@ -6603,10 +6594,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473693</v>
+        <v>473731</v>
       </c>
       <c r="R59" t="n">
-        <v>6872740</v>
+        <v>6872691</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6670,7 +6661,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125074731</v>
+        <v>125073474</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -6705,7 +6696,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6715,14 +6706,14 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473769</v>
+        <v>473716</v>
       </c>
       <c r="R60" t="n">
-        <v>6872532</v>
+        <v>6872520</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6781,10 +6772,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125075883</v>
+        <v>125072916</v>
       </c>
       <c r="B61" t="n">
-        <v>78455</v>
+        <v>79927</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6793,38 +6784,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473613</v>
+        <v>473748</v>
       </c>
       <c r="R61" t="n">
-        <v>6872761</v>
+        <v>6872490</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6883,10 +6874,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125076500</v>
+        <v>125074811</v>
       </c>
       <c r="B62" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6899,21 +6890,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6923,10 +6914,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>473798</v>
+        <v>473732</v>
       </c>
       <c r="R62" t="n">
-        <v>6872597</v>
+        <v>6872579</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6985,10 +6976,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125072596</v>
+        <v>125073052</v>
       </c>
       <c r="B63" t="n">
-        <v>78546</v>
+        <v>79920</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6997,25 +6988,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7025,10 +7016,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>473742</v>
+        <v>473748</v>
       </c>
       <c r="R63" t="n">
-        <v>6872438</v>
+        <v>6872489</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7087,10 +7078,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125074047</v>
+        <v>125075349</v>
       </c>
       <c r="B64" t="n">
-        <v>78455</v>
+        <v>78546</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7103,37 +7094,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>473665</v>
+        <v>473530</v>
       </c>
       <c r="R64" t="n">
-        <v>6872487</v>
+        <v>6872681</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7189,10 +7180,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125074232</v>
+        <v>125073530</v>
       </c>
       <c r="B65" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7201,38 +7192,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473700</v>
+        <v>473728</v>
       </c>
       <c r="R65" t="n">
-        <v>6872562</v>
+        <v>6872500</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125073107</v>
+        <v>125074047</v>
       </c>
       <c r="B66" t="n">
-        <v>78842</v>
+        <v>78455</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7307,21 +7307,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7331,10 +7331,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>473750</v>
+        <v>473665</v>
       </c>
       <c r="R66" t="n">
-        <v>6872492</v>
+        <v>6872487</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7393,10 +7393,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125073455</v>
+        <v>125072978</v>
       </c>
       <c r="B67" t="n">
-        <v>79399</v>
+        <v>79892</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7409,21 +7409,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7433,10 +7433,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>473712</v>
+        <v>473749</v>
       </c>
       <c r="R67" t="n">
-        <v>6872517</v>
+        <v>6872487</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7495,10 +7495,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125073833</v>
+        <v>125072827</v>
       </c>
       <c r="B68" t="n">
-        <v>78455</v>
+        <v>78546</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7511,21 +7511,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7535,10 +7535,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>473697</v>
+        <v>473758</v>
       </c>
       <c r="R68" t="n">
-        <v>6872466</v>
+        <v>6872471</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124658043</v>
+        <v>124659240</v>
       </c>
       <c r="B2" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473876</v>
+        <v>473810</v>
       </c>
       <c r="R2" t="n">
-        <v>6872692</v>
+        <v>6872485</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124659240</v>
+        <v>124657817</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78455</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473810</v>
+        <v>473891</v>
       </c>
       <c r="R3" t="n">
-        <v>6872485</v>
+        <v>6872741</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124659214</v>
+        <v>124658285</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473837</v>
+        <v>473876</v>
       </c>
       <c r="R4" t="n">
-        <v>6872441</v>
+        <v>6872637</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124658443</v>
+        <v>124659214</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473856</v>
+        <v>473837</v>
       </c>
       <c r="R6" t="n">
-        <v>6872612</v>
+        <v>6872441</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124657817</v>
+        <v>124658043</v>
       </c>
       <c r="B7" t="n">
         <v>78455</v>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473891</v>
+        <v>473876</v>
       </c>
       <c r="R7" t="n">
-        <v>6872741</v>
+        <v>6872692</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124658285</v>
+        <v>124658443</v>
       </c>
       <c r="B8" t="n">
         <v>78547</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473876</v>
+        <v>473856</v>
       </c>
       <c r="R8" t="n">
-        <v>6872637</v>
+        <v>6872612</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124827497</v>
+        <v>124828245</v>
       </c>
       <c r="B9" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473801</v>
+        <v>473687</v>
       </c>
       <c r="R9" t="n">
-        <v>6872850</v>
+        <v>6872750</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124829793</v>
+        <v>124827627</v>
       </c>
       <c r="B11" t="n">
-        <v>79927</v>
+        <v>78547</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473654</v>
+        <v>473780</v>
       </c>
       <c r="R11" t="n">
-        <v>6872997</v>
+        <v>6872856</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124826736</v>
+        <v>124827497</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473821</v>
+        <v>473801</v>
       </c>
       <c r="R12" t="n">
-        <v>6872738</v>
+        <v>6872850</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124827660</v>
+        <v>124828791</v>
       </c>
       <c r="B13" t="n">
-        <v>78455</v>
+        <v>78194</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473782</v>
+        <v>473589</v>
       </c>
       <c r="R13" t="n">
-        <v>6872817</v>
+        <v>6872813</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124827748</v>
+        <v>124826736</v>
       </c>
       <c r="B14" t="n">
         <v>78547</v>
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473754</v>
+        <v>473821</v>
       </c>
       <c r="R14" t="n">
-        <v>6872803</v>
+        <v>6872738</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124828245</v>
+        <v>124827748</v>
       </c>
       <c r="B15" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473687</v>
+        <v>473754</v>
       </c>
       <c r="R15" t="n">
-        <v>6872750</v>
+        <v>6872803</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124827627</v>
+        <v>124827660</v>
       </c>
       <c r="B16" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473780</v>
+        <v>473782</v>
       </c>
       <c r="R16" t="n">
-        <v>6872856</v>
+        <v>6872817</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124828676</v>
+        <v>124827491</v>
       </c>
       <c r="B17" t="n">
-        <v>78547</v>
+        <v>77738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,13 +2250,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473614</v>
+        <v>473801</v>
       </c>
       <c r="R17" t="n">
-        <v>6872815</v>
+        <v>6872850</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124827491</v>
+        <v>124828676</v>
       </c>
       <c r="B18" t="n">
-        <v>77738</v>
+        <v>78547</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473801</v>
+        <v>473614</v>
       </c>
       <c r="R18" t="n">
-        <v>6872850</v>
+        <v>6872815</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124828707</v>
+        <v>124826941</v>
       </c>
       <c r="B19" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,13 +2454,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473614</v>
+        <v>473804</v>
       </c>
       <c r="R19" t="n">
-        <v>6872815</v>
+        <v>6872761</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124826941</v>
+        <v>124828799</v>
       </c>
       <c r="B20" t="n">
-        <v>78547</v>
+        <v>77738</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473804</v>
+        <v>473591</v>
       </c>
       <c r="R20" t="n">
-        <v>6872761</v>
+        <v>6872817</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124828799</v>
+        <v>124828081</v>
       </c>
       <c r="B21" t="n">
-        <v>77738</v>
+        <v>79399</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473591</v>
+        <v>473705</v>
       </c>
       <c r="R21" t="n">
-        <v>6872817</v>
+        <v>6872721</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124828791</v>
+        <v>124829793</v>
       </c>
       <c r="B22" t="n">
-        <v>78194</v>
+        <v>79927</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,25 +2732,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473589</v>
+        <v>473654</v>
       </c>
       <c r="R22" t="n">
-        <v>6872813</v>
+        <v>6872997</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124828081</v>
+        <v>124828707</v>
       </c>
       <c r="B23" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473705</v>
+        <v>473614</v>
       </c>
       <c r="R23" t="n">
-        <v>6872721</v>
+        <v>6872815</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125075202</v>
+        <v>125074811</v>
       </c>
       <c r="B24" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,13 +2964,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473594</v>
+        <v>473732</v>
       </c>
       <c r="R24" t="n">
-        <v>6872603</v>
+        <v>6872579</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125073267</v>
+        <v>125074165</v>
       </c>
       <c r="B25" t="n">
-        <v>79920</v>
+        <v>78455</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,13 +3066,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473732</v>
+        <v>473690</v>
       </c>
       <c r="R25" t="n">
-        <v>6872498</v>
+        <v>6872539</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125076500</v>
+        <v>125073146</v>
       </c>
       <c r="B26" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,38 +3140,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473798</v>
+        <v>473748</v>
       </c>
       <c r="R26" t="n">
-        <v>6872597</v>
+        <v>6872493</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125075295</v>
+        <v>125073338</v>
       </c>
       <c r="B27" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,34 +3255,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473553</v>
+        <v>473722</v>
       </c>
       <c r="R27" t="n">
-        <v>6872662</v>
+        <v>6872521</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3332,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125072596</v>
+        <v>125076393</v>
       </c>
       <c r="B28" t="n">
-        <v>78546</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,34 +3357,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473742</v>
+        <v>473731</v>
       </c>
       <c r="R28" t="n">
-        <v>6872438</v>
+        <v>6872691</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3408,6 +3417,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3434,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125074318</v>
+        <v>125073430</v>
       </c>
       <c r="B29" t="n">
-        <v>78455</v>
+        <v>57666</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,34 +3464,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473722</v>
+        <v>473712</v>
       </c>
       <c r="R29" t="n">
-        <v>6872544</v>
+        <v>6872523</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3510,6 +3524,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3536,10 +3555,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125075336</v>
+        <v>125073474</v>
       </c>
       <c r="B30" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3548,38 +3567,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473532</v>
+        <v>473716</v>
       </c>
       <c r="R30" t="n">
-        <v>6872688</v>
+        <v>6872520</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,10 +3666,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125076033</v>
+        <v>125075883</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>78455</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3654,21 +3682,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3678,10 +3706,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473693</v>
+        <v>473613</v>
       </c>
       <c r="R31" t="n">
-        <v>6872740</v>
+        <v>6872761</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3714,11 +3742,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3745,10 +3768,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125072999</v>
+        <v>125075491</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>79428</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,37 +3784,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473747</v>
+        <v>473523</v>
       </c>
       <c r="R32" t="n">
-        <v>6872493</v>
+        <v>6872722</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3847,10 +3870,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125073338</v>
+        <v>125076500</v>
       </c>
       <c r="B33" t="n">
-        <v>79399</v>
+        <v>79891</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,37 +3886,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473722</v>
+        <v>473798</v>
       </c>
       <c r="R33" t="n">
-        <v>6872521</v>
+        <v>6872597</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3949,10 +3972,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125075883</v>
+        <v>125073578</v>
       </c>
       <c r="B34" t="n">
-        <v>78455</v>
+        <v>98122</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3961,41 +3984,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473613</v>
+        <v>473736</v>
       </c>
       <c r="R34" t="n">
-        <v>6872761</v>
+        <v>6872499</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4051,10 +4083,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125073833</v>
+        <v>125072916</v>
       </c>
       <c r="B35" t="n">
-        <v>78455</v>
+        <v>79927</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4063,25 +4095,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4091,10 +4123,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473697</v>
+        <v>473748</v>
       </c>
       <c r="R35" t="n">
-        <v>6872466</v>
+        <v>6872490</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4255,10 +4287,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125072602</v>
+        <v>125074318</v>
       </c>
       <c r="B37" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4271,37 +4303,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473742</v>
+        <v>473722</v>
       </c>
       <c r="R37" t="n">
-        <v>6872438</v>
+        <v>6872544</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4357,10 +4389,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125075154</v>
+        <v>125074731</v>
       </c>
       <c r="B38" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4369,38 +4401,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473625</v>
+        <v>473769</v>
       </c>
       <c r="R38" t="n">
-        <v>6872585</v>
+        <v>6872532</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4459,10 +4500,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125074165</v>
+        <v>125073052</v>
       </c>
       <c r="B39" t="n">
-        <v>78455</v>
+        <v>79920</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4471,25 +4512,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4499,10 +4540,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473690</v>
+        <v>473748</v>
       </c>
       <c r="R39" t="n">
-        <v>6872539</v>
+        <v>6872489</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,10 +4602,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125073578</v>
+        <v>125074232</v>
       </c>
       <c r="B40" t="n">
-        <v>98122</v>
+        <v>78547</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4573,50 +4614,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473736</v>
+        <v>473700</v>
       </c>
       <c r="R40" t="n">
-        <v>6872499</v>
+        <v>6872562</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4672,10 +4704,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125074741</v>
+        <v>125075630</v>
       </c>
       <c r="B41" t="n">
-        <v>79892</v>
+        <v>79399</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4688,21 +4720,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4712,13 +4744,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473756</v>
+        <v>473566</v>
       </c>
       <c r="R41" t="n">
-        <v>6872526</v>
+        <v>6872757</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4774,10 +4806,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125075258</v>
+        <v>125073107</v>
       </c>
       <c r="B42" t="n">
-        <v>78455</v>
+        <v>78842</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4790,34 +4822,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473585</v>
+        <v>473750</v>
       </c>
       <c r="R42" t="n">
-        <v>6872639</v>
+        <v>6872492</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4876,10 +4908,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125073107</v>
+        <v>125075202</v>
       </c>
       <c r="B43" t="n">
-        <v>78842</v>
+        <v>78455</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4892,34 +4924,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473750</v>
+        <v>473594</v>
       </c>
       <c r="R43" t="n">
-        <v>6872492</v>
+        <v>6872603</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -4978,7 +5010,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125074731</v>
+        <v>125073530</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5013,7 +5045,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5023,14 +5055,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473769</v>
+        <v>473728</v>
       </c>
       <c r="R44" t="n">
-        <v>6872532</v>
+        <v>6872500</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5089,10 +5121,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125074664</v>
+        <v>125073455</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>79399</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5101,47 +5133,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473761</v>
+        <v>473712</v>
       </c>
       <c r="R45" t="n">
-        <v>6872503</v>
+        <v>6872517</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5200,10 +5223,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125072658</v>
+        <v>125072602</v>
       </c>
       <c r="B46" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5216,21 +5239,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5240,10 +5263,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473760</v>
+        <v>473742</v>
       </c>
       <c r="R46" t="n">
-        <v>6872467</v>
+        <v>6872438</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5302,10 +5325,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125071546</v>
+        <v>125072999</v>
       </c>
       <c r="B47" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5314,25 +5337,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5342,10 +5365,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473832</v>
+        <v>473747</v>
       </c>
       <c r="R47" t="n">
-        <v>6872552</v>
+        <v>6872493</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5378,11 +5401,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5409,10 +5427,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125073430</v>
+        <v>125074664</v>
       </c>
       <c r="B48" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5421,41 +5439,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473712</v>
+        <v>473761</v>
       </c>
       <c r="R48" t="n">
-        <v>6872523</v>
+        <v>6872503</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5485,11 +5512,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5516,10 +5538,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125073455</v>
+        <v>125071546</v>
       </c>
       <c r="B49" t="n">
-        <v>79399</v>
+        <v>56722</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5528,25 +5550,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5556,10 +5578,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473712</v>
+        <v>473832</v>
       </c>
       <c r="R49" t="n">
-        <v>6872517</v>
+        <v>6872552</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5592,6 +5614,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5618,10 +5645,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125073255</v>
+        <v>125075295</v>
       </c>
       <c r="B50" t="n">
-        <v>79892</v>
+        <v>78547</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5634,37 +5661,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473735</v>
+        <v>473553</v>
       </c>
       <c r="R50" t="n">
-        <v>6872503</v>
+        <v>6872662</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5720,10 +5747,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125074134</v>
+        <v>125074741</v>
       </c>
       <c r="B51" t="n">
-        <v>78455</v>
+        <v>79892</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5736,37 +5763,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473684</v>
+        <v>473756</v>
       </c>
       <c r="R51" t="n">
-        <v>6872544</v>
+        <v>6872526</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5822,10 +5849,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125073146</v>
+        <v>125073936</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>79399</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5834,47 +5861,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473748</v>
+        <v>473695</v>
       </c>
       <c r="R52" t="n">
-        <v>6872493</v>
+        <v>6872466</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6035,10 +6053,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125075491</v>
+        <v>125073255</v>
       </c>
       <c r="B54" t="n">
-        <v>79428</v>
+        <v>79892</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6051,37 +6069,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473523</v>
+        <v>473735</v>
       </c>
       <c r="R54" t="n">
-        <v>6872722</v>
+        <v>6872503</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6137,10 +6155,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125074232</v>
+        <v>125072827</v>
       </c>
       <c r="B55" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6153,21 +6171,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6177,10 +6195,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473700</v>
+        <v>473758</v>
       </c>
       <c r="R55" t="n">
-        <v>6872562</v>
+        <v>6872471</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6239,10 +6257,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125075630</v>
+        <v>125073267</v>
       </c>
       <c r="B56" t="n">
-        <v>79399</v>
+        <v>79920</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6251,38 +6269,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473566</v>
+        <v>473732</v>
       </c>
       <c r="R56" t="n">
-        <v>6872757</v>
+        <v>6872498</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6341,10 +6359,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125074681</v>
+        <v>125075349</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6353,47 +6371,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473765</v>
+        <v>473530</v>
       </c>
       <c r="R57" t="n">
-        <v>6872521</v>
+        <v>6872681</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6452,10 +6461,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125073936</v>
+        <v>125075336</v>
       </c>
       <c r="B58" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6468,34 +6477,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>473695</v>
+        <v>473532</v>
       </c>
       <c r="R58" t="n">
-        <v>6872466</v>
+        <v>6872688</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6554,10 +6563,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125076393</v>
+        <v>125074047</v>
       </c>
       <c r="B59" t="n">
-        <v>57513</v>
+        <v>78455</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6570,37 +6579,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473731</v>
+        <v>473665</v>
       </c>
       <c r="R59" t="n">
-        <v>6872691</v>
+        <v>6872487</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6630,11 +6639,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6661,10 +6665,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125073474</v>
+        <v>125075154</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6673,47 +6677,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473716</v>
+        <v>473625</v>
       </c>
       <c r="R60" t="n">
-        <v>6872520</v>
+        <v>6872585</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6772,10 +6767,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125072916</v>
+        <v>125072596</v>
       </c>
       <c r="B61" t="n">
-        <v>79927</v>
+        <v>78546</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6784,25 +6779,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6812,10 +6807,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473748</v>
+        <v>473742</v>
       </c>
       <c r="R61" t="n">
-        <v>6872490</v>
+        <v>6872438</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6874,10 +6869,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125074811</v>
+        <v>125074134</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6890,37 +6885,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>473732</v>
+        <v>473684</v>
       </c>
       <c r="R62" t="n">
-        <v>6872579</v>
+        <v>6872544</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6976,10 +6971,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125073052</v>
+        <v>125072658</v>
       </c>
       <c r="B63" t="n">
-        <v>79920</v>
+        <v>78546</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6988,25 +6983,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7016,10 +7011,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>473748</v>
+        <v>473760</v>
       </c>
       <c r="R63" t="n">
-        <v>6872489</v>
+        <v>6872467</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7078,10 +7073,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125075349</v>
+        <v>125075258</v>
       </c>
       <c r="B64" t="n">
-        <v>78546</v>
+        <v>78455</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7094,21 +7089,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7118,13 +7113,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>473530</v>
+        <v>473585</v>
       </c>
       <c r="R64" t="n">
-        <v>6872681</v>
+        <v>6872639</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7180,10 +7175,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125073530</v>
+        <v>125072978</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>79892</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7192,47 +7187,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473728</v>
+        <v>473749</v>
       </c>
       <c r="R65" t="n">
-        <v>6872500</v>
+        <v>6872487</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7291,10 +7277,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125074047</v>
+        <v>125076033</v>
       </c>
       <c r="B66" t="n">
-        <v>78455</v>
+        <v>57513</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7307,37 +7293,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>473665</v>
+        <v>473693</v>
       </c>
       <c r="R66" t="n">
-        <v>6872487</v>
+        <v>6872740</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7367,6 +7353,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7393,10 +7384,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125072978</v>
+        <v>125073833</v>
       </c>
       <c r="B67" t="n">
-        <v>79892</v>
+        <v>78455</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7409,21 +7400,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7433,10 +7424,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>473749</v>
+        <v>473697</v>
       </c>
       <c r="R67" t="n">
-        <v>6872487</v>
+        <v>6872466</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7495,10 +7486,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125072827</v>
+        <v>125074681</v>
       </c>
       <c r="B68" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7507,38 +7498,47 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>473758</v>
+        <v>473765</v>
       </c>
       <c r="R68" t="n">
-        <v>6872471</v>
+        <v>6872521</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124827660</v>
+        <v>124828676</v>
       </c>
       <c r="B16" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473782</v>
+        <v>473614</v>
       </c>
       <c r="R16" t="n">
-        <v>6872817</v>
+        <v>6872815</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124827491</v>
+        <v>124827660</v>
       </c>
       <c r="B17" t="n">
-        <v>77738</v>
+        <v>78455</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,13 +2250,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473801</v>
+        <v>473782</v>
       </c>
       <c r="R17" t="n">
-        <v>6872850</v>
+        <v>6872817</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124828676</v>
+        <v>124827491</v>
       </c>
       <c r="B18" t="n">
-        <v>78547</v>
+        <v>77738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473614</v>
+        <v>473801</v>
       </c>
       <c r="R18" t="n">
-        <v>6872815</v>
+        <v>6872850</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125074811</v>
+        <v>125073146</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,38 +2936,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473732</v>
+        <v>473748</v>
       </c>
       <c r="R24" t="n">
-        <v>6872579</v>
+        <v>6872493</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3128,10 +3137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125073146</v>
+        <v>125074811</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,47 +3149,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473748</v>
+        <v>473732</v>
       </c>
       <c r="R26" t="n">
-        <v>6872493</v>
+        <v>6872579</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125076393</v>
+        <v>125073430</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3357,37 +3357,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473731</v>
+        <v>473712</v>
       </c>
       <c r="R28" t="n">
-        <v>6872691</v>
+        <v>6872523</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3448,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125073430</v>
+        <v>125073474</v>
       </c>
       <c r="B29" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3460,41 +3460,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473712</v>
+        <v>473716</v>
       </c>
       <c r="R29" t="n">
-        <v>6872523</v>
+        <v>6872520</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3524,11 +3533,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3555,10 +3559,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125073474</v>
+        <v>125075883</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3567,47 +3571,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473716</v>
+        <v>473613</v>
       </c>
       <c r="R30" t="n">
-        <v>6872520</v>
+        <v>6872761</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3666,10 +3661,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125075883</v>
+        <v>125075491</v>
       </c>
       <c r="B31" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3682,21 +3677,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3706,13 +3701,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473613</v>
+        <v>473523</v>
       </c>
       <c r="R31" t="n">
-        <v>6872761</v>
+        <v>6872722</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3768,10 +3763,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125075491</v>
+        <v>125076500</v>
       </c>
       <c r="B32" t="n">
-        <v>79428</v>
+        <v>79891</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3784,21 +3779,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3808,13 +3803,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473523</v>
+        <v>473798</v>
       </c>
       <c r="R32" t="n">
-        <v>6872722</v>
+        <v>6872597</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3870,10 +3865,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125076500</v>
+        <v>125076393</v>
       </c>
       <c r="B33" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3886,21 +3881,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3910,10 +3905,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473798</v>
+        <v>473731</v>
       </c>
       <c r="R33" t="n">
-        <v>6872597</v>
+        <v>6872691</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3946,6 +3941,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4806,10 +4806,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125073107</v>
+        <v>125072602</v>
       </c>
       <c r="B42" t="n">
-        <v>78842</v>
+        <v>78547</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4822,21 +4822,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4846,13 +4846,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473750</v>
+        <v>473742</v>
       </c>
       <c r="R42" t="n">
-        <v>6872492</v>
+        <v>6872438</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4908,10 +4908,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125075202</v>
+        <v>125073107</v>
       </c>
       <c r="B43" t="n">
-        <v>78455</v>
+        <v>78842</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4924,34 +4924,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473594</v>
+        <v>473750</v>
       </c>
       <c r="R43" t="n">
-        <v>6872603</v>
+        <v>6872492</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5010,10 +5010,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125073530</v>
+        <v>125075202</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5022,50 +5022,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473728</v>
+        <v>473594</v>
       </c>
       <c r="R44" t="n">
-        <v>6872500</v>
+        <v>6872603</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5121,10 +5112,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125073455</v>
+        <v>125073530</v>
       </c>
       <c r="B45" t="n">
-        <v>79399</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5133,38 +5124,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473712</v>
+        <v>473728</v>
       </c>
       <c r="R45" t="n">
-        <v>6872517</v>
+        <v>6872500</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5223,10 +5223,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125072602</v>
+        <v>125073455</v>
       </c>
       <c r="B46" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5239,21 +5239,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473742</v>
+        <v>473712</v>
       </c>
       <c r="R46" t="n">
-        <v>6872438</v>
+        <v>6872517</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5538,10 +5538,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125071546</v>
+        <v>125075295</v>
       </c>
       <c r="B49" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5550,41 +5550,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473832</v>
+        <v>473553</v>
       </c>
       <c r="R49" t="n">
-        <v>6872552</v>
+        <v>6872662</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5614,11 +5614,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5645,10 +5640,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125075295</v>
+        <v>125071546</v>
       </c>
       <c r="B50" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5657,41 +5652,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473553</v>
+        <v>473832</v>
       </c>
       <c r="R50" t="n">
-        <v>6872662</v>
+        <v>6872552</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5721,6 +5716,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5747,10 +5747,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125074741</v>
+        <v>125073936</v>
       </c>
       <c r="B51" t="n">
-        <v>79892</v>
+        <v>79399</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5763,34 +5763,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473756</v>
+        <v>473695</v>
       </c>
       <c r="R51" t="n">
-        <v>6872526</v>
+        <v>6872466</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5849,10 +5849,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125073936</v>
+        <v>125074741</v>
       </c>
       <c r="B52" t="n">
-        <v>79399</v>
+        <v>79892</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5865,34 +5865,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473695</v>
+        <v>473756</v>
       </c>
       <c r="R52" t="n">
-        <v>6872466</v>
+        <v>6872526</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6461,10 +6461,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125075336</v>
+        <v>125074047</v>
       </c>
       <c r="B58" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6477,37 +6477,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>473532</v>
+        <v>473665</v>
       </c>
       <c r="R58" t="n">
-        <v>6872688</v>
+        <v>6872487</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125074047</v>
+        <v>125075154</v>
       </c>
       <c r="B59" t="n">
         <v>78455</v>
@@ -6599,17 +6599,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473665</v>
+        <v>473625</v>
       </c>
       <c r="R59" t="n">
-        <v>6872487</v>
+        <v>6872585</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6665,10 +6665,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125075154</v>
+        <v>125072596</v>
       </c>
       <c r="B60" t="n">
-        <v>78455</v>
+        <v>78546</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6681,34 +6681,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473625</v>
+        <v>473742</v>
       </c>
       <c r="R60" t="n">
-        <v>6872585</v>
+        <v>6872438</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6767,10 +6767,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125072596</v>
+        <v>125075336</v>
       </c>
       <c r="B61" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6783,34 +6783,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473742</v>
+        <v>473532</v>
       </c>
       <c r="R61" t="n">
-        <v>6872438</v>
+        <v>6872688</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7073,10 +7073,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125075258</v>
+        <v>125072978</v>
       </c>
       <c r="B64" t="n">
-        <v>78455</v>
+        <v>79892</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7089,37 +7089,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>473585</v>
+        <v>473749</v>
       </c>
       <c r="R64" t="n">
-        <v>6872639</v>
+        <v>6872487</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7175,10 +7175,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125072978</v>
+        <v>125075258</v>
       </c>
       <c r="B65" t="n">
-        <v>79892</v>
+        <v>78455</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7191,37 +7191,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473749</v>
+        <v>473585</v>
       </c>
       <c r="R65" t="n">
-        <v>6872487</v>
+        <v>6872639</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7384,10 +7384,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125073833</v>
+        <v>125074681</v>
       </c>
       <c r="B67" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7396,38 +7396,47 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>473697</v>
+        <v>473765</v>
       </c>
       <c r="R67" t="n">
-        <v>6872466</v>
+        <v>6872521</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7486,10 +7495,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125074681</v>
+        <v>125073833</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7498,47 +7507,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>473765</v>
+        <v>473697</v>
       </c>
       <c r="R68" t="n">
-        <v>6872521</v>
+        <v>6872466</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124828676</v>
+        <v>124827660</v>
       </c>
       <c r="B16" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473614</v>
+        <v>473782</v>
       </c>
       <c r="R16" t="n">
-        <v>6872815</v>
+        <v>6872817</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124827660</v>
+        <v>124827491</v>
       </c>
       <c r="B17" t="n">
-        <v>78455</v>
+        <v>77738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,13 +2250,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473782</v>
+        <v>473801</v>
       </c>
       <c r="R17" t="n">
-        <v>6872817</v>
+        <v>6872850</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124827491</v>
+        <v>124828676</v>
       </c>
       <c r="B18" t="n">
-        <v>77738</v>
+        <v>78547</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473801</v>
+        <v>473614</v>
       </c>
       <c r="R18" t="n">
-        <v>6872850</v>
+        <v>6872815</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -5538,10 +5538,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125075295</v>
+        <v>125071546</v>
       </c>
       <c r="B49" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5550,41 +5550,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473553</v>
+        <v>473832</v>
       </c>
       <c r="R49" t="n">
-        <v>6872662</v>
+        <v>6872552</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5614,6 +5614,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5640,10 +5645,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125071546</v>
+        <v>125075295</v>
       </c>
       <c r="B50" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5652,41 +5657,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473832</v>
+        <v>473553</v>
       </c>
       <c r="R50" t="n">
-        <v>6872552</v>
+        <v>6872662</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5716,11 +5721,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6461,10 +6461,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125074047</v>
+        <v>125075336</v>
       </c>
       <c r="B58" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6477,37 +6477,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>473665</v>
+        <v>473532</v>
       </c>
       <c r="R58" t="n">
-        <v>6872487</v>
+        <v>6872688</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125075154</v>
+        <v>125074047</v>
       </c>
       <c r="B59" t="n">
         <v>78455</v>
@@ -6599,17 +6599,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473625</v>
+        <v>473665</v>
       </c>
       <c r="R59" t="n">
-        <v>6872585</v>
+        <v>6872487</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6665,10 +6665,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125072596</v>
+        <v>125075154</v>
       </c>
       <c r="B60" t="n">
-        <v>78546</v>
+        <v>78455</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6681,34 +6681,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473742</v>
+        <v>473625</v>
       </c>
       <c r="R60" t="n">
-        <v>6872438</v>
+        <v>6872585</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6767,10 +6767,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125075336</v>
+        <v>125072596</v>
       </c>
       <c r="B61" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6783,34 +6783,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473532</v>
+        <v>473742</v>
       </c>
       <c r="R61" t="n">
-        <v>6872688</v>
+        <v>6872438</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7073,10 +7073,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125072978</v>
+        <v>125075258</v>
       </c>
       <c r="B64" t="n">
-        <v>79892</v>
+        <v>78455</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7089,37 +7089,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>473749</v>
+        <v>473585</v>
       </c>
       <c r="R64" t="n">
-        <v>6872487</v>
+        <v>6872639</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7175,10 +7175,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125075258</v>
+        <v>125072978</v>
       </c>
       <c r="B65" t="n">
-        <v>78455</v>
+        <v>79892</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7191,37 +7191,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473585</v>
+        <v>473749</v>
       </c>
       <c r="R65" t="n">
-        <v>6872639</v>
+        <v>6872487</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7384,10 +7384,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125074681</v>
+        <v>125073833</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7396,47 +7396,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>473765</v>
+        <v>473697</v>
       </c>
       <c r="R67" t="n">
-        <v>6872521</v>
+        <v>6872466</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7495,10 +7486,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125073833</v>
+        <v>125074681</v>
       </c>
       <c r="B68" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7507,38 +7498,47 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>473697</v>
+        <v>473765</v>
       </c>
       <c r="R68" t="n">
-        <v>6872466</v>
+        <v>6872521</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124659240</v>
+        <v>124657817</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>78455</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473810</v>
+        <v>473891</v>
       </c>
       <c r="R2" t="n">
-        <v>6872485</v>
+        <v>6872741</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124657817</v>
+        <v>124658285</v>
       </c>
       <c r="B3" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473891</v>
+        <v>473876</v>
       </c>
       <c r="R3" t="n">
-        <v>6872741</v>
+        <v>6872637</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124658285</v>
+        <v>124658043</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>473876</v>
       </c>
       <c r="R4" t="n">
-        <v>6872637</v>
+        <v>6872692</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1083,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124659214</v>
+        <v>124659240</v>
       </c>
       <c r="B6" t="n">
         <v>79891</v>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473837</v>
+        <v>473810</v>
       </c>
       <c r="R6" t="n">
-        <v>6872441</v>
+        <v>6872485</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124658043</v>
+        <v>124659214</v>
       </c>
       <c r="B7" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473876</v>
+        <v>473837</v>
       </c>
       <c r="R7" t="n">
-        <v>6872692</v>
+        <v>6872441</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124828245</v>
+        <v>124827491</v>
       </c>
       <c r="B9" t="n">
-        <v>78546</v>
+        <v>77738</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473687</v>
+        <v>473801</v>
       </c>
       <c r="R9" t="n">
-        <v>6872750</v>
+        <v>6872850</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124829811</v>
+        <v>124828245</v>
       </c>
       <c r="B10" t="n">
-        <v>79926</v>
+        <v>78546</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473654</v>
+        <v>473687</v>
       </c>
       <c r="R10" t="n">
-        <v>6872997</v>
+        <v>6872750</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124827627</v>
+        <v>124827497</v>
       </c>
       <c r="B11" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473780</v>
+        <v>473801</v>
       </c>
       <c r="R11" t="n">
-        <v>6872856</v>
+        <v>6872850</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124827497</v>
+        <v>124828707</v>
       </c>
       <c r="B12" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473801</v>
+        <v>473614</v>
       </c>
       <c r="R12" t="n">
-        <v>6872850</v>
+        <v>6872815</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124828791</v>
+        <v>124828799</v>
       </c>
       <c r="B13" t="n">
-        <v>78194</v>
+        <v>77738</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473589</v>
+        <v>473591</v>
       </c>
       <c r="R13" t="n">
-        <v>6872813</v>
+        <v>6872817</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124826736</v>
+        <v>124826941</v>
       </c>
       <c r="B14" t="n">
         <v>78547</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473821</v>
+        <v>473804</v>
       </c>
       <c r="R14" t="n">
-        <v>6872738</v>
+        <v>6872761</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124827748</v>
+        <v>124827627</v>
       </c>
       <c r="B15" t="n">
         <v>78547</v>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473754</v>
+        <v>473780</v>
       </c>
       <c r="R15" t="n">
-        <v>6872803</v>
+        <v>6872856</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124827660</v>
+        <v>124828081</v>
       </c>
       <c r="B16" t="n">
-        <v>78455</v>
+        <v>79399</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473782</v>
+        <v>473705</v>
       </c>
       <c r="R16" t="n">
-        <v>6872817</v>
+        <v>6872721</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124827491</v>
+        <v>124828791</v>
       </c>
       <c r="B17" t="n">
-        <v>77738</v>
+        <v>78194</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,13 +2250,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473801</v>
+        <v>473589</v>
       </c>
       <c r="R17" t="n">
-        <v>6872850</v>
+        <v>6872813</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124828676</v>
+        <v>124829793</v>
       </c>
       <c r="B18" t="n">
-        <v>78547</v>
+        <v>79927</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473614</v>
+        <v>473654</v>
       </c>
       <c r="R18" t="n">
-        <v>6872815</v>
+        <v>6872997</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124826941</v>
+        <v>124829811</v>
       </c>
       <c r="B19" t="n">
-        <v>78547</v>
+        <v>79926</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473804</v>
+        <v>473654</v>
       </c>
       <c r="R19" t="n">
-        <v>6872761</v>
+        <v>6872997</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124828799</v>
+        <v>124827748</v>
       </c>
       <c r="B20" t="n">
-        <v>77738</v>
+        <v>78547</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473591</v>
+        <v>473754</v>
       </c>
       <c r="R20" t="n">
-        <v>6872817</v>
+        <v>6872803</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124828081</v>
+        <v>124826736</v>
       </c>
       <c r="B21" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473705</v>
+        <v>473821</v>
       </c>
       <c r="R21" t="n">
-        <v>6872721</v>
+        <v>6872738</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124829793</v>
+        <v>124827660</v>
       </c>
       <c r="B22" t="n">
-        <v>79927</v>
+        <v>78455</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,25 +2732,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473654</v>
+        <v>473782</v>
       </c>
       <c r="R22" t="n">
-        <v>6872997</v>
+        <v>6872817</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124828707</v>
+        <v>124828676</v>
       </c>
       <c r="B23" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2868,7 +2868,7 @@
         <v>6872815</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125073146</v>
+        <v>125075258</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,50 +2936,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473748</v>
+        <v>473585</v>
       </c>
       <c r="R24" t="n">
-        <v>6872493</v>
+        <v>6872639</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3035,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125074165</v>
+        <v>125076033</v>
       </c>
       <c r="B25" t="n">
-        <v>78455</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3051,34 +3042,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473690</v>
+        <v>473693</v>
       </c>
       <c r="R25" t="n">
-        <v>6872539</v>
+        <v>6872740</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3111,6 +3102,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3137,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125074811</v>
+        <v>125074731</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3149,38 +3145,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473732</v>
+        <v>473769</v>
       </c>
       <c r="R26" t="n">
-        <v>6872579</v>
+        <v>6872532</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3239,10 +3244,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125073338</v>
+        <v>125075336</v>
       </c>
       <c r="B27" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3255,37 +3260,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473722</v>
+        <v>473532</v>
       </c>
       <c r="R27" t="n">
-        <v>6872521</v>
+        <v>6872688</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3341,10 +3346,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125073430</v>
+        <v>125074134</v>
       </c>
       <c r="B28" t="n">
-        <v>57666</v>
+        <v>78455</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3357,21 +3362,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3381,10 +3386,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473712</v>
+        <v>473684</v>
       </c>
       <c r="R28" t="n">
-        <v>6872523</v>
+        <v>6872544</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3417,11 +3422,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3448,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125073474</v>
+        <v>125074741</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>79892</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3460,47 +3460,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473716</v>
+        <v>473756</v>
       </c>
       <c r="R29" t="n">
-        <v>6872520</v>
+        <v>6872526</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3559,10 +3550,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125075883</v>
+        <v>125073936</v>
       </c>
       <c r="B30" t="n">
-        <v>78455</v>
+        <v>79399</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3575,34 +3566,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473613</v>
+        <v>473695</v>
       </c>
       <c r="R30" t="n">
-        <v>6872761</v>
+        <v>6872466</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,10 +3652,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125075491</v>
+        <v>125075295</v>
       </c>
       <c r="B31" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3677,21 +3668,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3701,10 +3692,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473523</v>
+        <v>473553</v>
       </c>
       <c r="R31" t="n">
-        <v>6872722</v>
+        <v>6872662</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3763,10 +3754,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125076500</v>
+        <v>125076393</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3779,21 +3770,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3803,10 +3794,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473798</v>
+        <v>473731</v>
       </c>
       <c r="R32" t="n">
-        <v>6872597</v>
+        <v>6872691</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,6 +3830,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,10 +3861,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125076393</v>
+        <v>125072602</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>78547</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3881,34 +3877,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473731</v>
+        <v>473742</v>
       </c>
       <c r="R33" t="n">
-        <v>6872691</v>
+        <v>6872438</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,11 +3937,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3972,10 +3963,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125073578</v>
+        <v>125074165</v>
       </c>
       <c r="B34" t="n">
-        <v>98122</v>
+        <v>78455</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3984,50 +3975,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473736</v>
+        <v>473690</v>
       </c>
       <c r="R34" t="n">
-        <v>6872499</v>
+        <v>6872539</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4083,10 +4065,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125072916</v>
+        <v>125074318</v>
       </c>
       <c r="B35" t="n">
-        <v>79927</v>
+        <v>78455</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4095,41 +4077,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473748</v>
+        <v>473722</v>
       </c>
       <c r="R35" t="n">
-        <v>6872490</v>
+        <v>6872544</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4185,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125075710</v>
+        <v>125075505</v>
       </c>
       <c r="B36" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4201,21 +4183,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4225,13 +4207,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473570</v>
+        <v>473523</v>
       </c>
       <c r="R36" t="n">
-        <v>6872751</v>
+        <v>6872722</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4287,10 +4269,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125074318</v>
+        <v>125074232</v>
       </c>
       <c r="B37" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4303,37 +4285,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473722</v>
+        <v>473700</v>
       </c>
       <c r="R37" t="n">
-        <v>6872544</v>
+        <v>6872562</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4389,10 +4371,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125074731</v>
+        <v>125072596</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4401,47 +4383,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473769</v>
+        <v>473742</v>
       </c>
       <c r="R38" t="n">
-        <v>6872532</v>
+        <v>6872438</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4500,10 +4473,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125073052</v>
+        <v>125072827</v>
       </c>
       <c r="B39" t="n">
-        <v>79920</v>
+        <v>78546</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4512,25 +4485,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4540,10 +4513,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473748</v>
+        <v>473758</v>
       </c>
       <c r="R39" t="n">
-        <v>6872489</v>
+        <v>6872471</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4602,10 +4575,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125074232</v>
+        <v>125074811</v>
       </c>
       <c r="B40" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4618,34 +4591,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473700</v>
+        <v>473732</v>
       </c>
       <c r="R40" t="n">
-        <v>6872562</v>
+        <v>6872579</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4704,10 +4677,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125075630</v>
+        <v>125073255</v>
       </c>
       <c r="B41" t="n">
-        <v>79399</v>
+        <v>79892</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4720,37 +4693,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473566</v>
+        <v>473735</v>
       </c>
       <c r="R41" t="n">
-        <v>6872757</v>
+        <v>6872503</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4806,10 +4779,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125072602</v>
+        <v>125073833</v>
       </c>
       <c r="B42" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4822,21 +4795,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4846,10 +4819,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473742</v>
+        <v>473697</v>
       </c>
       <c r="R42" t="n">
-        <v>6872438</v>
+        <v>6872466</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4908,10 +4881,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125073107</v>
+        <v>125072978</v>
       </c>
       <c r="B43" t="n">
-        <v>78842</v>
+        <v>79892</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4924,21 +4897,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4948,13 +4921,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473750</v>
+        <v>473749</v>
       </c>
       <c r="R43" t="n">
-        <v>6872492</v>
+        <v>6872487</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5010,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125075202</v>
+        <v>125073267</v>
       </c>
       <c r="B44" t="n">
-        <v>78455</v>
+        <v>79920</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5022,38 +4995,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473594</v>
+        <v>473732</v>
       </c>
       <c r="R44" t="n">
-        <v>6872603</v>
+        <v>6872498</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5112,10 +5085,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125073530</v>
+        <v>125073455</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>79399</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5124,47 +5097,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473728</v>
+        <v>473712</v>
       </c>
       <c r="R45" t="n">
-        <v>6872500</v>
+        <v>6872517</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5223,7 +5187,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125073455</v>
+        <v>125075630</v>
       </c>
       <c r="B46" t="n">
         <v>79399</v>
@@ -5259,17 +5223,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473712</v>
+        <v>473566</v>
       </c>
       <c r="R46" t="n">
-        <v>6872517</v>
+        <v>6872757</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5325,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125072999</v>
+        <v>125073578</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>98122</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5337,41 +5301,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473747</v>
+        <v>473736</v>
       </c>
       <c r="R47" t="n">
-        <v>6872493</v>
+        <v>6872499</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5427,10 +5400,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125074664</v>
+        <v>125073107</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5439,50 +5412,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473761</v>
+        <v>473750</v>
       </c>
       <c r="R48" t="n">
-        <v>6872503</v>
+        <v>6872492</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5538,10 +5502,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125071546</v>
+        <v>125075491</v>
       </c>
       <c r="B49" t="n">
-        <v>56722</v>
+        <v>79428</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5550,41 +5514,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473832</v>
+        <v>473523</v>
       </c>
       <c r="R49" t="n">
-        <v>6872552</v>
+        <v>6872722</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5614,11 +5578,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5645,10 +5604,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125075295</v>
+        <v>125075202</v>
       </c>
       <c r="B50" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5661,21 +5620,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5685,10 +5644,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473553</v>
+        <v>473594</v>
       </c>
       <c r="R50" t="n">
-        <v>6872662</v>
+        <v>6872603</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5747,10 +5706,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125073936</v>
+        <v>125073146</v>
       </c>
       <c r="B51" t="n">
-        <v>79399</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5759,38 +5718,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473695</v>
+        <v>473748</v>
       </c>
       <c r="R51" t="n">
-        <v>6872466</v>
+        <v>6872493</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5849,10 +5817,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125074741</v>
+        <v>125073338</v>
       </c>
       <c r="B52" t="n">
-        <v>79892</v>
+        <v>79399</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5865,37 +5833,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473756</v>
+        <v>473722</v>
       </c>
       <c r="R52" t="n">
-        <v>6872526</v>
+        <v>6872521</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5951,10 +5919,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125075505</v>
+        <v>125072658</v>
       </c>
       <c r="B53" t="n">
-        <v>78455</v>
+        <v>78546</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5967,37 +5935,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473523</v>
+        <v>473760</v>
       </c>
       <c r="R53" t="n">
-        <v>6872722</v>
+        <v>6872467</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6053,10 +6021,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125073255</v>
+        <v>125074681</v>
       </c>
       <c r="B54" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6065,38 +6033,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473735</v>
+        <v>473765</v>
       </c>
       <c r="R54" t="n">
-        <v>6872503</v>
+        <v>6872521</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6155,7 +6132,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125072827</v>
+        <v>125075349</v>
       </c>
       <c r="B55" t="n">
         <v>78546</v>
@@ -6191,14 +6168,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473758</v>
+        <v>473530</v>
       </c>
       <c r="R55" t="n">
-        <v>6872471</v>
+        <v>6872681</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6257,10 +6234,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125073267</v>
+        <v>125073430</v>
       </c>
       <c r="B56" t="n">
-        <v>79920</v>
+        <v>57666</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6269,25 +6246,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6297,10 +6274,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473732</v>
+        <v>473712</v>
       </c>
       <c r="R56" t="n">
-        <v>6872498</v>
+        <v>6872523</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6333,6 +6310,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6359,10 +6341,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125075349</v>
+        <v>125074047</v>
       </c>
       <c r="B57" t="n">
-        <v>78546</v>
+        <v>78455</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6375,37 +6357,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473530</v>
+        <v>473665</v>
       </c>
       <c r="R57" t="n">
-        <v>6872681</v>
+        <v>6872487</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6461,10 +6443,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125075336</v>
+        <v>125075883</v>
       </c>
       <c r="B58" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6477,21 +6459,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6501,10 +6483,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>473532</v>
+        <v>473613</v>
       </c>
       <c r="R58" t="n">
-        <v>6872688</v>
+        <v>6872761</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6563,10 +6545,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125074047</v>
+        <v>125073474</v>
       </c>
       <c r="B59" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6575,41 +6557,50 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473665</v>
+        <v>473716</v>
       </c>
       <c r="R59" t="n">
-        <v>6872487</v>
+        <v>6872520</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6665,10 +6656,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125075154</v>
+        <v>125073052</v>
       </c>
       <c r="B60" t="n">
-        <v>78455</v>
+        <v>79920</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6677,38 +6668,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473625</v>
+        <v>473748</v>
       </c>
       <c r="R60" t="n">
-        <v>6872585</v>
+        <v>6872489</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6767,10 +6758,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125072596</v>
+        <v>125076500</v>
       </c>
       <c r="B61" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6783,34 +6774,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473742</v>
+        <v>473798</v>
       </c>
       <c r="R61" t="n">
-        <v>6872438</v>
+        <v>6872597</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6869,10 +6860,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125074134</v>
+        <v>125074664</v>
       </c>
       <c r="B62" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6881,41 +6872,50 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>473684</v>
+        <v>473761</v>
       </c>
       <c r="R62" t="n">
-        <v>6872544</v>
+        <v>6872503</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6971,10 +6971,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125072658</v>
+        <v>125072999</v>
       </c>
       <c r="B63" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6987,21 +6987,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7011,10 +7011,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>473760</v>
+        <v>473747</v>
       </c>
       <c r="R63" t="n">
-        <v>6872467</v>
+        <v>6872493</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7073,7 +7073,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125075258</v>
+        <v>125075154</v>
       </c>
       <c r="B64" t="n">
         <v>78455</v>
@@ -7113,13 +7113,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>473585</v>
+        <v>473625</v>
       </c>
       <c r="R64" t="n">
-        <v>6872639</v>
+        <v>6872585</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7175,10 +7175,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125072978</v>
+        <v>125071546</v>
       </c>
       <c r="B65" t="n">
-        <v>79892</v>
+        <v>56722</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7187,25 +7187,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473749</v>
+        <v>473832</v>
       </c>
       <c r="R65" t="n">
-        <v>6872487</v>
+        <v>6872552</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7251,6 +7251,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7277,10 +7282,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125076033</v>
+        <v>125075710</v>
       </c>
       <c r="B66" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7293,21 +7298,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7317,10 +7322,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>473693</v>
+        <v>473570</v>
       </c>
       <c r="R66" t="n">
-        <v>6872740</v>
+        <v>6872751</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7353,11 +7358,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7384,10 +7384,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125073833</v>
+        <v>125073530</v>
       </c>
       <c r="B67" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7396,38 +7396,47 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>473697</v>
+        <v>473728</v>
       </c>
       <c r="R67" t="n">
-        <v>6872466</v>
+        <v>6872500</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7486,10 +7495,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125074681</v>
+        <v>125072916</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7498,47 +7507,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>473765</v>
+        <v>473748</v>
       </c>
       <c r="R68" t="n">
-        <v>6872521</v>
+        <v>6872490</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124657817</v>
+        <v>124659240</v>
       </c>
       <c r="B2" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473891</v>
+        <v>473810</v>
       </c>
       <c r="R2" t="n">
-        <v>6872741</v>
+        <v>6872485</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124658285</v>
+        <v>124658043</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,7 +820,7 @@
         <v>473876</v>
       </c>
       <c r="R3" t="n">
-        <v>6872637</v>
+        <v>6872692</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124658043</v>
+        <v>124657817</v>
       </c>
       <c r="B4" t="n">
         <v>78455</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473876</v>
+        <v>473891</v>
       </c>
       <c r="R4" t="n">
-        <v>6872692</v>
+        <v>6872741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658172</v>
+        <v>124658285</v>
       </c>
       <c r="B5" t="n">
         <v>78547</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473877</v>
+        <v>473876</v>
       </c>
       <c r="R5" t="n">
-        <v>6872665</v>
+        <v>6872637</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124659240</v>
+        <v>124659214</v>
       </c>
       <c r="B6" t="n">
         <v>79891</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473810</v>
+        <v>473837</v>
       </c>
       <c r="R6" t="n">
-        <v>6872485</v>
+        <v>6872441</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124659214</v>
+        <v>124658443</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473837</v>
+        <v>473856</v>
       </c>
       <c r="R7" t="n">
-        <v>6872441</v>
+        <v>6872612</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124658443</v>
+        <v>124658172</v>
       </c>
       <c r="B8" t="n">
         <v>78547</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473856</v>
+        <v>473877</v>
       </c>
       <c r="R8" t="n">
-        <v>6872612</v>
+        <v>6872665</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124827491</v>
+        <v>124828791</v>
       </c>
       <c r="B9" t="n">
-        <v>77738</v>
+        <v>78194</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473801</v>
+        <v>473589</v>
       </c>
       <c r="R9" t="n">
-        <v>6872850</v>
+        <v>6872813</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124828245</v>
+        <v>124828799</v>
       </c>
       <c r="B10" t="n">
-        <v>78546</v>
+        <v>77738</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473687</v>
+        <v>473591</v>
       </c>
       <c r="R10" t="n">
-        <v>6872750</v>
+        <v>6872817</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124827497</v>
+        <v>124828081</v>
       </c>
       <c r="B11" t="n">
         <v>79399</v>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473801</v>
+        <v>473705</v>
       </c>
       <c r="R11" t="n">
-        <v>6872850</v>
+        <v>6872721</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124828707</v>
+        <v>124826736</v>
       </c>
       <c r="B12" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473614</v>
+        <v>473821</v>
       </c>
       <c r="R12" t="n">
-        <v>6872815</v>
+        <v>6872738</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124828799</v>
+        <v>124827660</v>
       </c>
       <c r="B13" t="n">
-        <v>77738</v>
+        <v>78455</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473591</v>
+        <v>473782</v>
       </c>
       <c r="R13" t="n">
         <v>6872817</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124826941</v>
+        <v>124827497</v>
       </c>
       <c r="B14" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473804</v>
+        <v>473801</v>
       </c>
       <c r="R14" t="n">
-        <v>6872761</v>
+        <v>6872850</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124827627</v>
+        <v>124828245</v>
       </c>
       <c r="B15" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473780</v>
+        <v>473687</v>
       </c>
       <c r="R15" t="n">
-        <v>6872856</v>
+        <v>6872750</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124828081</v>
+        <v>124828676</v>
       </c>
       <c r="B16" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473705</v>
+        <v>473614</v>
       </c>
       <c r="R16" t="n">
-        <v>6872721</v>
+        <v>6872815</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124828791</v>
+        <v>124828707</v>
       </c>
       <c r="B17" t="n">
-        <v>78194</v>
+        <v>78546</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,13 +2250,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473589</v>
+        <v>473614</v>
       </c>
       <c r="R17" t="n">
-        <v>6872813</v>
+        <v>6872815</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124829793</v>
+        <v>124827748</v>
       </c>
       <c r="B18" t="n">
-        <v>79927</v>
+        <v>78547</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473654</v>
+        <v>473754</v>
       </c>
       <c r="R18" t="n">
-        <v>6872997</v>
+        <v>6872803</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124827748</v>
+        <v>124827491</v>
       </c>
       <c r="B20" t="n">
-        <v>78547</v>
+        <v>77738</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473754</v>
+        <v>473801</v>
       </c>
       <c r="R20" t="n">
-        <v>6872803</v>
+        <v>6872850</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124826736</v>
+        <v>124829793</v>
       </c>
       <c r="B21" t="n">
-        <v>78547</v>
+        <v>79927</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473821</v>
+        <v>473654</v>
       </c>
       <c r="R21" t="n">
-        <v>6872738</v>
+        <v>6872997</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124827660</v>
+        <v>124827627</v>
       </c>
       <c r="B22" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473782</v>
+        <v>473780</v>
       </c>
       <c r="R22" t="n">
-        <v>6872817</v>
+        <v>6872856</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,7 +2822,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124828676</v>
+        <v>124826941</v>
       </c>
       <c r="B23" t="n">
         <v>78547</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473614</v>
+        <v>473804</v>
       </c>
       <c r="R23" t="n">
-        <v>6872815</v>
+        <v>6872761</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125075258</v>
+        <v>125075349</v>
       </c>
       <c r="B24" t="n">
-        <v>78455</v>
+        <v>78546</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,13 +2964,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473585</v>
+        <v>473530</v>
       </c>
       <c r="R24" t="n">
-        <v>6872639</v>
+        <v>6872681</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125076033</v>
+        <v>125074232</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>78547</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,34 +3042,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473693</v>
+        <v>473700</v>
       </c>
       <c r="R25" t="n">
-        <v>6872740</v>
+        <v>6872562</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3102,11 +3102,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3133,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125074731</v>
+        <v>125073052</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3145,47 +3140,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473769</v>
+        <v>473748</v>
       </c>
       <c r="R26" t="n">
-        <v>6872532</v>
+        <v>6872489</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3244,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125075336</v>
+        <v>125073578</v>
       </c>
       <c r="B27" t="n">
-        <v>78547</v>
+        <v>98122</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3256,41 +3242,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473532</v>
+        <v>473736</v>
       </c>
       <c r="R27" t="n">
-        <v>6872688</v>
+        <v>6872499</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3346,7 +3341,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125074134</v>
+        <v>125075505</v>
       </c>
       <c r="B28" t="n">
         <v>78455</v>
@@ -3382,14 +3377,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473684</v>
+        <v>473523</v>
       </c>
       <c r="R28" t="n">
-        <v>6872544</v>
+        <v>6872722</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3448,10 +3443,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125074741</v>
+        <v>125074134</v>
       </c>
       <c r="B29" t="n">
-        <v>79892</v>
+        <v>78455</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3464,37 +3459,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473756</v>
+        <v>473684</v>
       </c>
       <c r="R29" t="n">
-        <v>6872526</v>
+        <v>6872544</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3550,10 +3545,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125073936</v>
+        <v>125075710</v>
       </c>
       <c r="B30" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3566,34 +3561,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473695</v>
+        <v>473570</v>
       </c>
       <c r="R30" t="n">
-        <v>6872466</v>
+        <v>6872751</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3652,10 +3647,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125075295</v>
+        <v>125073530</v>
       </c>
       <c r="B31" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3664,41 +3659,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473553</v>
+        <v>473728</v>
       </c>
       <c r="R31" t="n">
-        <v>6872662</v>
+        <v>6872500</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3861,10 +3865,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125072602</v>
+        <v>125073146</v>
       </c>
       <c r="B33" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3873,38 +3877,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473742</v>
+        <v>473748</v>
       </c>
       <c r="R33" t="n">
-        <v>6872438</v>
+        <v>6872493</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3963,10 +3976,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125074165</v>
+        <v>125073936</v>
       </c>
       <c r="B34" t="n">
-        <v>78455</v>
+        <v>79399</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3979,21 +3992,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4003,10 +4016,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473690</v>
+        <v>473695</v>
       </c>
       <c r="R34" t="n">
-        <v>6872539</v>
+        <v>6872466</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4065,10 +4078,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125074318</v>
+        <v>125073474</v>
       </c>
       <c r="B35" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4077,41 +4090,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473722</v>
+        <v>473716</v>
       </c>
       <c r="R35" t="n">
-        <v>6872544</v>
+        <v>6872520</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4167,10 +4189,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125075505</v>
+        <v>125074811</v>
       </c>
       <c r="B36" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4183,21 +4205,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4207,13 +4229,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473523</v>
+        <v>473732</v>
       </c>
       <c r="R36" t="n">
-        <v>6872722</v>
+        <v>6872579</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4269,10 +4291,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125074232</v>
+        <v>125075258</v>
       </c>
       <c r="B37" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4285,37 +4307,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473700</v>
+        <v>473585</v>
       </c>
       <c r="R37" t="n">
-        <v>6872562</v>
+        <v>6872639</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4371,10 +4393,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125072596</v>
+        <v>125076033</v>
       </c>
       <c r="B38" t="n">
-        <v>78546</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4387,34 +4409,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473742</v>
+        <v>473693</v>
       </c>
       <c r="R38" t="n">
-        <v>6872438</v>
+        <v>6872740</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4447,6 +4469,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4473,10 +4500,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125072827</v>
+        <v>125075202</v>
       </c>
       <c r="B39" t="n">
-        <v>78546</v>
+        <v>78455</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4489,37 +4516,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473758</v>
+        <v>473594</v>
       </c>
       <c r="R39" t="n">
-        <v>6872471</v>
+        <v>6872603</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4575,10 +4602,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125074811</v>
+        <v>125073833</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4591,34 +4618,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473732</v>
+        <v>473697</v>
       </c>
       <c r="R40" t="n">
-        <v>6872579</v>
+        <v>6872466</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4677,10 +4704,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125073255</v>
+        <v>125074664</v>
       </c>
       <c r="B41" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4689,35 +4716,44 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473735</v>
+        <v>473761</v>
       </c>
       <c r="R41" t="n">
         <v>6872503</v>
@@ -4779,10 +4815,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125073833</v>
+        <v>125075336</v>
       </c>
       <c r="B42" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4795,34 +4831,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473697</v>
+        <v>473532</v>
       </c>
       <c r="R42" t="n">
-        <v>6872466</v>
+        <v>6872688</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4881,10 +4917,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125072978</v>
+        <v>125073455</v>
       </c>
       <c r="B43" t="n">
-        <v>79892</v>
+        <v>79399</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4897,21 +4933,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4921,10 +4957,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473749</v>
+        <v>473712</v>
       </c>
       <c r="R43" t="n">
-        <v>6872487</v>
+        <v>6872517</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,10 +5019,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125073267</v>
+        <v>125072602</v>
       </c>
       <c r="B44" t="n">
-        <v>79920</v>
+        <v>78547</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,25 +5031,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5023,13 +5059,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473732</v>
+        <v>473742</v>
       </c>
       <c r="R44" t="n">
-        <v>6872498</v>
+        <v>6872438</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5085,10 +5121,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125073455</v>
+        <v>125074731</v>
       </c>
       <c r="B45" t="n">
-        <v>79399</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,38 +5133,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473712</v>
+        <v>473769</v>
       </c>
       <c r="R45" t="n">
-        <v>6872517</v>
+        <v>6872532</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5187,10 +5232,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125075630</v>
+        <v>125075154</v>
       </c>
       <c r="B46" t="n">
-        <v>79399</v>
+        <v>78455</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5203,21 +5248,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5227,13 +5272,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473566</v>
+        <v>473625</v>
       </c>
       <c r="R46" t="n">
-        <v>6872757</v>
+        <v>6872585</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5289,10 +5334,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125073578</v>
+        <v>125072999</v>
       </c>
       <c r="B47" t="n">
-        <v>98122</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5301,50 +5346,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473736</v>
+        <v>473747</v>
       </c>
       <c r="R47" t="n">
-        <v>6872499</v>
+        <v>6872493</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5400,10 +5436,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125073107</v>
+        <v>125074741</v>
       </c>
       <c r="B48" t="n">
-        <v>78842</v>
+        <v>79892</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5416,37 +5452,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473750</v>
+        <v>473756</v>
       </c>
       <c r="R48" t="n">
-        <v>6872492</v>
+        <v>6872526</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5502,10 +5538,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125075491</v>
+        <v>125073107</v>
       </c>
       <c r="B49" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5518,34 +5554,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473523</v>
+        <v>473750</v>
       </c>
       <c r="R49" t="n">
-        <v>6872722</v>
+        <v>6872492</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5604,10 +5640,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125075202</v>
+        <v>125071546</v>
       </c>
       <c r="B50" t="n">
-        <v>78455</v>
+        <v>56722</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5616,41 +5652,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473594</v>
+        <v>473832</v>
       </c>
       <c r="R50" t="n">
-        <v>6872603</v>
+        <v>6872552</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5680,6 +5716,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5706,10 +5747,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125073146</v>
+        <v>125075630</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>79399</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5718,50 +5759,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473748</v>
+        <v>473566</v>
       </c>
       <c r="R51" t="n">
-        <v>6872493</v>
+        <v>6872757</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5817,10 +5849,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125073338</v>
+        <v>125074165</v>
       </c>
       <c r="B52" t="n">
-        <v>79399</v>
+        <v>78455</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5833,21 +5865,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5857,13 +5889,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473722</v>
+        <v>473690</v>
       </c>
       <c r="R52" t="n">
-        <v>6872521</v>
+        <v>6872539</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5919,10 +5951,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125072658</v>
+        <v>125075491</v>
       </c>
       <c r="B53" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5935,37 +5967,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473760</v>
+        <v>473523</v>
       </c>
       <c r="R53" t="n">
-        <v>6872467</v>
+        <v>6872722</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6021,10 +6053,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125074681</v>
+        <v>125072827</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6033,47 +6065,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473765</v>
+        <v>473758</v>
       </c>
       <c r="R54" t="n">
-        <v>6872521</v>
+        <v>6872471</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6132,10 +6155,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125075349</v>
+        <v>125074681</v>
       </c>
       <c r="B55" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6144,38 +6167,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473530</v>
+        <v>473765</v>
       </c>
       <c r="R55" t="n">
-        <v>6872681</v>
+        <v>6872521</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6234,10 +6266,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125073430</v>
+        <v>125073255</v>
       </c>
       <c r="B56" t="n">
-        <v>57666</v>
+        <v>79892</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6250,21 +6282,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6274,13 +6306,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473712</v>
+        <v>473735</v>
       </c>
       <c r="R56" t="n">
-        <v>6872523</v>
+        <v>6872503</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6310,11 +6342,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6341,7 +6368,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125074047</v>
+        <v>125075883</v>
       </c>
       <c r="B57" t="n">
         <v>78455</v>
@@ -6377,17 +6404,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473665</v>
+        <v>473613</v>
       </c>
       <c r="R57" t="n">
-        <v>6872487</v>
+        <v>6872761</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6443,10 +6470,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125075883</v>
+        <v>125072916</v>
       </c>
       <c r="B58" t="n">
-        <v>78455</v>
+        <v>79927</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6455,38 +6482,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>473613</v>
+        <v>473748</v>
       </c>
       <c r="R58" t="n">
-        <v>6872761</v>
+        <v>6872490</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6545,10 +6572,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125073474</v>
+        <v>125076500</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6557,47 +6584,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473716</v>
+        <v>473798</v>
       </c>
       <c r="R59" t="n">
-        <v>6872520</v>
+        <v>6872597</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6656,10 +6674,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125073052</v>
+        <v>125074318</v>
       </c>
       <c r="B60" t="n">
-        <v>79920</v>
+        <v>78455</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6668,41 +6686,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473748</v>
+        <v>473722</v>
       </c>
       <c r="R60" t="n">
-        <v>6872489</v>
+        <v>6872544</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6758,10 +6776,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125076500</v>
+        <v>125072978</v>
       </c>
       <c r="B61" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6774,34 +6792,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473798</v>
+        <v>473749</v>
       </c>
       <c r="R61" t="n">
-        <v>6872597</v>
+        <v>6872487</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6860,10 +6878,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125074664</v>
+        <v>125073267</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6872,50 +6890,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>473761</v>
+        <v>473732</v>
       </c>
       <c r="R62" t="n">
-        <v>6872503</v>
+        <v>6872498</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6971,10 +6980,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125072999</v>
+        <v>125075295</v>
       </c>
       <c r="B63" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6987,37 +6996,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>473747</v>
+        <v>473553</v>
       </c>
       <c r="R63" t="n">
-        <v>6872493</v>
+        <v>6872662</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7073,10 +7082,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125075154</v>
+        <v>125073430</v>
       </c>
       <c r="B64" t="n">
-        <v>78455</v>
+        <v>57666</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7089,37 +7098,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>473625</v>
+        <v>473712</v>
       </c>
       <c r="R64" t="n">
-        <v>6872585</v>
+        <v>6872523</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7149,6 +7158,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7175,10 +7189,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125071546</v>
+        <v>125072596</v>
       </c>
       <c r="B65" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7187,25 +7201,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7215,10 +7229,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473832</v>
+        <v>473742</v>
       </c>
       <c r="R65" t="n">
-        <v>6872552</v>
+        <v>6872438</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7251,11 +7265,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7282,10 +7291,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125075710</v>
+        <v>125072658</v>
       </c>
       <c r="B66" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7298,34 +7307,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>473570</v>
+        <v>473760</v>
       </c>
       <c r="R66" t="n">
-        <v>6872751</v>
+        <v>6872467</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7384,10 +7393,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125073530</v>
+        <v>125073338</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>79399</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7396,50 +7405,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>473728</v>
+        <v>473722</v>
       </c>
       <c r="R67" t="n">
-        <v>6872500</v>
+        <v>6872521</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7495,10 +7495,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125072916</v>
+        <v>125074047</v>
       </c>
       <c r="B68" t="n">
-        <v>79927</v>
+        <v>78455</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7507,25 +7507,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7535,13 +7535,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>473748</v>
+        <v>473665</v>
       </c>
       <c r="R68" t="n">
-        <v>6872490</v>
+        <v>6872487</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124658043</v>
+        <v>124658443</v>
       </c>
       <c r="B3" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473876</v>
+        <v>473856</v>
       </c>
       <c r="R3" t="n">
-        <v>6872692</v>
+        <v>6872612</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124657817</v>
+        <v>124659214</v>
       </c>
       <c r="B4" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473891</v>
+        <v>473837</v>
       </c>
       <c r="R4" t="n">
-        <v>6872741</v>
+        <v>6872441</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658285</v>
+        <v>124657817</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473876</v>
+        <v>473891</v>
       </c>
       <c r="R5" t="n">
-        <v>6872637</v>
+        <v>6872741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124659214</v>
+        <v>124658043</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>78455</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473837</v>
+        <v>473876</v>
       </c>
       <c r="R6" t="n">
-        <v>6872441</v>
+        <v>6872692</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1164,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124658443</v>
+        <v>124658285</v>
       </c>
       <c r="B7" t="n">
         <v>78547</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473856</v>
+        <v>473876</v>
       </c>
       <c r="R7" t="n">
-        <v>6872612</v>
+        <v>6872637</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124828799</v>
+        <v>124829811</v>
       </c>
       <c r="B10" t="n">
-        <v>77738</v>
+        <v>79926</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473591</v>
+        <v>473654</v>
       </c>
       <c r="R10" t="n">
-        <v>6872817</v>
+        <v>6872997</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124828081</v>
+        <v>124828245</v>
       </c>
       <c r="B11" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473705</v>
+        <v>473687</v>
       </c>
       <c r="R11" t="n">
-        <v>6872721</v>
+        <v>6872750</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124826736</v>
+        <v>124828081</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473821</v>
+        <v>473705</v>
       </c>
       <c r="R12" t="n">
-        <v>6872738</v>
+        <v>6872721</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124827660</v>
+        <v>124828707</v>
       </c>
       <c r="B13" t="n">
-        <v>78455</v>
+        <v>78546</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473782</v>
+        <v>473614</v>
       </c>
       <c r="R13" t="n">
-        <v>6872817</v>
+        <v>6872815</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124828245</v>
+        <v>124828799</v>
       </c>
       <c r="B15" t="n">
-        <v>78546</v>
+        <v>77738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473687</v>
+        <v>473591</v>
       </c>
       <c r="R15" t="n">
-        <v>6872750</v>
+        <v>6872817</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124828676</v>
+        <v>124829793</v>
       </c>
       <c r="B16" t="n">
-        <v>78547</v>
+        <v>79927</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473614</v>
+        <v>473654</v>
       </c>
       <c r="R16" t="n">
-        <v>6872815</v>
+        <v>6872997</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124828707</v>
+        <v>124828676</v>
       </c>
       <c r="B17" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2256,7 +2256,7 @@
         <v>6872815</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124827748</v>
+        <v>124826941</v>
       </c>
       <c r="B18" t="n">
         <v>78547</v>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473754</v>
+        <v>473804</v>
       </c>
       <c r="R18" t="n">
-        <v>6872803</v>
+        <v>6872761</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124829811</v>
+        <v>124827491</v>
       </c>
       <c r="B19" t="n">
-        <v>79926</v>
+        <v>77738</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,13 +2454,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473654</v>
+        <v>473801</v>
       </c>
       <c r="R19" t="n">
-        <v>6872997</v>
+        <v>6872850</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124827491</v>
+        <v>124827660</v>
       </c>
       <c r="B20" t="n">
-        <v>77738</v>
+        <v>78455</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473801</v>
+        <v>473782</v>
       </c>
       <c r="R20" t="n">
-        <v>6872850</v>
+        <v>6872817</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124829793</v>
+        <v>124826736</v>
       </c>
       <c r="B21" t="n">
-        <v>79927</v>
+        <v>78547</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473654</v>
+        <v>473821</v>
       </c>
       <c r="R21" t="n">
-        <v>6872997</v>
+        <v>6872738</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2822,7 +2822,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124826941</v>
+        <v>124827748</v>
       </c>
       <c r="B23" t="n">
         <v>78547</v>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473804</v>
+        <v>473754</v>
       </c>
       <c r="R23" t="n">
-        <v>6872761</v>
+        <v>6872803</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125075349</v>
+        <v>125074318</v>
       </c>
       <c r="B24" t="n">
-        <v>78546</v>
+        <v>78455</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,13 +2964,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473530</v>
+        <v>473722</v>
       </c>
       <c r="R24" t="n">
-        <v>6872681</v>
+        <v>6872544</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125074232</v>
+        <v>125073338</v>
       </c>
       <c r="B25" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,13 +3066,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473700</v>
+        <v>473722</v>
       </c>
       <c r="R25" t="n">
-        <v>6872562</v>
+        <v>6872521</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125073052</v>
+        <v>125073430</v>
       </c>
       <c r="B26" t="n">
-        <v>79920</v>
+        <v>57666</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,25 +3140,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,13 +3168,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473748</v>
+        <v>473712</v>
       </c>
       <c r="R26" t="n">
-        <v>6872489</v>
+        <v>6872523</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3204,6 +3204,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3230,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125073578</v>
+        <v>125074811</v>
       </c>
       <c r="B27" t="n">
-        <v>98122</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,50 +3247,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473736</v>
+        <v>473732</v>
       </c>
       <c r="R27" t="n">
-        <v>6872499</v>
+        <v>6872579</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3341,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125075505</v>
+        <v>125075630</v>
       </c>
       <c r="B28" t="n">
-        <v>78455</v>
+        <v>79399</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3357,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3381,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473523</v>
+        <v>473566</v>
       </c>
       <c r="R28" t="n">
-        <v>6872722</v>
+        <v>6872757</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3443,7 +3439,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125074134</v>
+        <v>125075154</v>
       </c>
       <c r="B29" t="n">
         <v>78455</v>
@@ -3479,17 +3475,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473684</v>
+        <v>473625</v>
       </c>
       <c r="R29" t="n">
-        <v>6872544</v>
+        <v>6872585</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3545,10 +3541,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125075710</v>
+        <v>125074047</v>
       </c>
       <c r="B30" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3561,37 +3557,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473570</v>
+        <v>473665</v>
       </c>
       <c r="R30" t="n">
-        <v>6872751</v>
+        <v>6872487</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3647,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125073530</v>
+        <v>125075202</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3659,50 +3655,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473728</v>
+        <v>473594</v>
       </c>
       <c r="R31" t="n">
-        <v>6872500</v>
+        <v>6872603</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3758,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125076393</v>
+        <v>125074731</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3770,38 +3757,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473731</v>
+        <v>473769</v>
       </c>
       <c r="R32" t="n">
-        <v>6872691</v>
+        <v>6872532</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3834,11 +3830,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,7 +3856,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125073146</v>
+        <v>125074664</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -3900,7 +3891,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3910,14 +3901,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473748</v>
+        <v>473761</v>
       </c>
       <c r="R33" t="n">
-        <v>6872493</v>
+        <v>6872503</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3976,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125073936</v>
+        <v>125073530</v>
       </c>
       <c r="B34" t="n">
-        <v>79399</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3988,38 +3979,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473695</v>
+        <v>473728</v>
       </c>
       <c r="R34" t="n">
-        <v>6872466</v>
+        <v>6872500</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4189,10 +4189,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125074811</v>
+        <v>125073267</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4201,41 +4201,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
         <v>473732</v>
       </c>
       <c r="R36" t="n">
-        <v>6872579</v>
+        <v>6872498</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125075258</v>
+        <v>125072978</v>
       </c>
       <c r="B37" t="n">
-        <v>78455</v>
+        <v>79892</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4307,37 +4307,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473585</v>
+        <v>473749</v>
       </c>
       <c r="R37" t="n">
-        <v>6872639</v>
+        <v>6872487</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125076033</v>
+        <v>125075491</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>79428</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4433,13 +4433,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473693</v>
+        <v>473523</v>
       </c>
       <c r="R38" t="n">
-        <v>6872740</v>
+        <v>6872722</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4469,11 +4469,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4500,10 +4495,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125075202</v>
+        <v>125073936</v>
       </c>
       <c r="B39" t="n">
-        <v>78455</v>
+        <v>79399</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4516,37 +4511,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473594</v>
+        <v>473695</v>
       </c>
       <c r="R39" t="n">
-        <v>6872603</v>
+        <v>6872466</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4602,10 +4597,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125073833</v>
+        <v>125074741</v>
       </c>
       <c r="B40" t="n">
-        <v>78455</v>
+        <v>79892</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4618,34 +4613,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473697</v>
+        <v>473756</v>
       </c>
       <c r="R40" t="n">
-        <v>6872466</v>
+        <v>6872526</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4704,7 +4699,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125074664</v>
+        <v>125073146</v>
       </c>
       <c r="B41" t="n">
         <v>98101</v>
@@ -4739,7 +4734,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4749,14 +4744,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473761</v>
+        <v>473748</v>
       </c>
       <c r="R41" t="n">
-        <v>6872503</v>
+        <v>6872493</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4815,7 +4810,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125075336</v>
+        <v>125074232</v>
       </c>
       <c r="B42" t="n">
         <v>78547</v>
@@ -4851,14 +4846,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473532</v>
+        <v>473700</v>
       </c>
       <c r="R42" t="n">
-        <v>6872688</v>
+        <v>6872562</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4917,10 +4912,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125073455</v>
+        <v>125072827</v>
       </c>
       <c r="B43" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4933,21 +4928,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4957,10 +4952,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473712</v>
+        <v>473758</v>
       </c>
       <c r="R43" t="n">
-        <v>6872517</v>
+        <v>6872471</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5019,10 +5014,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125072602</v>
+        <v>125072596</v>
       </c>
       <c r="B44" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5035,21 +5030,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5121,10 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125074731</v>
+        <v>125072658</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5133,47 +5128,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473769</v>
+        <v>473760</v>
       </c>
       <c r="R45" t="n">
-        <v>6872532</v>
+        <v>6872467</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5232,10 +5218,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125075154</v>
+        <v>125076500</v>
       </c>
       <c r="B46" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5248,21 +5234,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5272,10 +5258,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473625</v>
+        <v>473798</v>
       </c>
       <c r="R46" t="n">
-        <v>6872585</v>
+        <v>6872597</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5334,10 +5320,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125072999</v>
+        <v>125074165</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>78455</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5350,21 +5336,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5374,10 +5360,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473747</v>
+        <v>473690</v>
       </c>
       <c r="R47" t="n">
-        <v>6872493</v>
+        <v>6872539</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5436,10 +5422,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125074741</v>
+        <v>125073578</v>
       </c>
       <c r="B48" t="n">
-        <v>79892</v>
+        <v>98122</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5448,41 +5434,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473756</v>
+        <v>473736</v>
       </c>
       <c r="R48" t="n">
-        <v>6872526</v>
+        <v>6872499</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5538,10 +5533,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125073107</v>
+        <v>125074134</v>
       </c>
       <c r="B49" t="n">
-        <v>78842</v>
+        <v>78455</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5554,21 +5549,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5578,10 +5573,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473750</v>
+        <v>473684</v>
       </c>
       <c r="R49" t="n">
-        <v>6872492</v>
+        <v>6872544</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5640,10 +5635,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125071546</v>
+        <v>125076393</v>
       </c>
       <c r="B50" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5652,38 +5647,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473832</v>
+        <v>473731</v>
       </c>
       <c r="R50" t="n">
-        <v>6872552</v>
+        <v>6872691</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,7 +5715,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Spillning under barrgles tall.</t>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5747,10 +5742,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125075630</v>
+        <v>125073255</v>
       </c>
       <c r="B51" t="n">
-        <v>79399</v>
+        <v>79892</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5763,37 +5758,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473566</v>
+        <v>473735</v>
       </c>
       <c r="R51" t="n">
-        <v>6872757</v>
+        <v>6872503</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5849,10 +5844,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125074165</v>
+        <v>125075710</v>
       </c>
       <c r="B52" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5865,34 +5860,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473690</v>
+        <v>473570</v>
       </c>
       <c r="R52" t="n">
-        <v>6872539</v>
+        <v>6872751</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5951,10 +5946,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125075491</v>
+        <v>125073107</v>
       </c>
       <c r="B53" t="n">
-        <v>79428</v>
+        <v>78842</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5967,34 +5962,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473523</v>
+        <v>473750</v>
       </c>
       <c r="R53" t="n">
-        <v>6872722</v>
+        <v>6872492</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6053,10 +6048,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125072827</v>
+        <v>125075505</v>
       </c>
       <c r="B54" t="n">
-        <v>78546</v>
+        <v>78455</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6069,37 +6064,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473758</v>
+        <v>473523</v>
       </c>
       <c r="R54" t="n">
-        <v>6872471</v>
+        <v>6872722</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6155,10 +6150,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125074681</v>
+        <v>125072602</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6167,47 +6162,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473765</v>
+        <v>473742</v>
       </c>
       <c r="R55" t="n">
-        <v>6872521</v>
+        <v>6872438</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6266,10 +6252,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125073255</v>
+        <v>125073052</v>
       </c>
       <c r="B56" t="n">
-        <v>79892</v>
+        <v>79920</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6278,25 +6264,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6306,10 +6292,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473735</v>
+        <v>473748</v>
       </c>
       <c r="R56" t="n">
-        <v>6872503</v>
+        <v>6872489</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6368,10 +6354,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125075883</v>
+        <v>125075349</v>
       </c>
       <c r="B57" t="n">
-        <v>78455</v>
+        <v>78546</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6384,21 +6370,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6408,10 +6394,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473613</v>
+        <v>473530</v>
       </c>
       <c r="R57" t="n">
-        <v>6872761</v>
+        <v>6872681</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6470,10 +6456,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125072916</v>
+        <v>125072999</v>
       </c>
       <c r="B58" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6482,25 +6468,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6510,10 +6496,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>473748</v>
+        <v>473747</v>
       </c>
       <c r="R58" t="n">
-        <v>6872490</v>
+        <v>6872493</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6572,10 +6558,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125076500</v>
+        <v>125073833</v>
       </c>
       <c r="B59" t="n">
-        <v>79891</v>
+        <v>78455</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6588,34 +6574,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473798</v>
+        <v>473697</v>
       </c>
       <c r="R59" t="n">
-        <v>6872597</v>
+        <v>6872466</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6674,10 +6660,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125074318</v>
+        <v>125075295</v>
       </c>
       <c r="B60" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6690,21 +6676,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6714,10 +6700,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473722</v>
+        <v>473553</v>
       </c>
       <c r="R60" t="n">
-        <v>6872544</v>
+        <v>6872662</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6776,10 +6762,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125072978</v>
+        <v>125072916</v>
       </c>
       <c r="B61" t="n">
-        <v>79892</v>
+        <v>79927</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6788,25 +6774,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6816,10 +6802,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473749</v>
+        <v>473748</v>
       </c>
       <c r="R61" t="n">
-        <v>6872487</v>
+        <v>6872490</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6878,10 +6864,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125073267</v>
+        <v>125075258</v>
       </c>
       <c r="B62" t="n">
-        <v>79920</v>
+        <v>78455</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6890,38 +6876,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>473732</v>
+        <v>473585</v>
       </c>
       <c r="R62" t="n">
-        <v>6872498</v>
+        <v>6872639</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6980,10 +6966,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125075295</v>
+        <v>125076033</v>
       </c>
       <c r="B63" t="n">
-        <v>78547</v>
+        <v>57513</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6996,21 +6982,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7020,13 +7006,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>473553</v>
+        <v>473693</v>
       </c>
       <c r="R63" t="n">
-        <v>6872662</v>
+        <v>6872740</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7056,6 +7042,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7082,10 +7073,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125073430</v>
+        <v>125074681</v>
       </c>
       <c r="B64" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7094,41 +7085,50 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>473712</v>
+        <v>473765</v>
       </c>
       <c r="R64" t="n">
-        <v>6872523</v>
+        <v>6872521</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7158,11 +7158,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7189,10 +7184,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125072596</v>
+        <v>125075336</v>
       </c>
       <c r="B65" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7205,34 +7200,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473742</v>
+        <v>473532</v>
       </c>
       <c r="R65" t="n">
-        <v>6872438</v>
+        <v>6872688</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7291,10 +7286,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125072658</v>
+        <v>125071546</v>
       </c>
       <c r="B66" t="n">
-        <v>78546</v>
+        <v>56722</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7303,25 +7298,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7331,10 +7326,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>473760</v>
+        <v>473832</v>
       </c>
       <c r="R66" t="n">
-        <v>6872467</v>
+        <v>6872552</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7367,6 +7362,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7393,7 +7393,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125073338</v>
+        <v>125073455</v>
       </c>
       <c r="B67" t="n">
         <v>79399</v>
@@ -7433,13 +7433,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>473722</v>
+        <v>473712</v>
       </c>
       <c r="R67" t="n">
-        <v>6872521</v>
+        <v>6872517</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125074047</v>
+        <v>125075883</v>
       </c>
       <c r="B68" t="n">
         <v>78455</v>
@@ -7531,17 +7531,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>473665</v>
+        <v>473613</v>
       </c>
       <c r="R68" t="n">
-        <v>6872487</v>
+        <v>6872761</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124659240</v>
+        <v>124658043</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>78455</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473810</v>
+        <v>473876</v>
       </c>
       <c r="R2" t="n">
-        <v>6872485</v>
+        <v>6872692</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124658443</v>
+        <v>124657817</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473856</v>
+        <v>473891</v>
       </c>
       <c r="R3" t="n">
-        <v>6872612</v>
+        <v>6872741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124659214</v>
+        <v>124658443</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473837</v>
+        <v>473856</v>
       </c>
       <c r="R4" t="n">
-        <v>6872441</v>
+        <v>6872612</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124657817</v>
+        <v>124658285</v>
       </c>
       <c r="B5" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473891</v>
+        <v>473876</v>
       </c>
       <c r="R5" t="n">
-        <v>6872741</v>
+        <v>6872637</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124658043</v>
+        <v>124658172</v>
       </c>
       <c r="B6" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473876</v>
+        <v>473877</v>
       </c>
       <c r="R6" t="n">
-        <v>6872692</v>
+        <v>6872665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124658285</v>
+        <v>124659214</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473876</v>
+        <v>473837</v>
       </c>
       <c r="R7" t="n">
-        <v>6872637</v>
+        <v>6872441</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124658172</v>
+        <v>124659240</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473877</v>
+        <v>473810</v>
       </c>
       <c r="R8" t="n">
-        <v>6872665</v>
+        <v>6872485</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125074741</v>
+        <v>125073146</v>
       </c>
       <c r="B40" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4609,38 +4609,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473756</v>
+        <v>473748</v>
       </c>
       <c r="R40" t="n">
-        <v>6872526</v>
+        <v>6872493</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4699,10 +4708,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125073146</v>
+        <v>125074232</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4711,47 +4720,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473748</v>
+        <v>473700</v>
       </c>
       <c r="R41" t="n">
-        <v>6872493</v>
+        <v>6872562</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4810,10 +4810,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125074232</v>
+        <v>125074741</v>
       </c>
       <c r="B42" t="n">
-        <v>78547</v>
+        <v>79892</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4826,34 +4826,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473700</v>
+        <v>473756</v>
       </c>
       <c r="R42" t="n">
-        <v>6872562</v>
+        <v>6872526</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5014,10 +5014,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125072596</v>
+        <v>125073578</v>
       </c>
       <c r="B44" t="n">
-        <v>78546</v>
+        <v>98122</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5026,41 +5026,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473742</v>
+        <v>473736</v>
       </c>
       <c r="R44" t="n">
-        <v>6872438</v>
+        <v>6872499</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5116,7 +5125,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125072658</v>
+        <v>125072596</v>
       </c>
       <c r="B45" t="n">
         <v>78546</v>
@@ -5156,10 +5165,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473760</v>
+        <v>473742</v>
       </c>
       <c r="R45" t="n">
-        <v>6872467</v>
+        <v>6872438</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,10 +5227,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125076500</v>
+        <v>125072658</v>
       </c>
       <c r="B46" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5234,34 +5243,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473798</v>
+        <v>473760</v>
       </c>
       <c r="R46" t="n">
-        <v>6872597</v>
+        <v>6872467</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5320,10 +5329,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125074165</v>
+        <v>125076500</v>
       </c>
       <c r="B47" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5336,34 +5345,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473690</v>
+        <v>473798</v>
       </c>
       <c r="R47" t="n">
-        <v>6872539</v>
+        <v>6872597</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5422,10 +5431,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125073578</v>
+        <v>125074165</v>
       </c>
       <c r="B48" t="n">
-        <v>98122</v>
+        <v>78455</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5434,50 +5443,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473736</v>
+        <v>473690</v>
       </c>
       <c r="R48" t="n">
-        <v>6872499</v>
+        <v>6872539</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124658043</v>
+        <v>124658285</v>
       </c>
       <c r="B2" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,7 +718,7 @@
         <v>473876</v>
       </c>
       <c r="R2" t="n">
-        <v>6872692</v>
+        <v>6872637</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124658443</v>
+        <v>124659240</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473856</v>
+        <v>473810</v>
       </c>
       <c r="R4" t="n">
-        <v>6872612</v>
+        <v>6872485</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658285</v>
+        <v>124658043</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,7 +1024,7 @@
         <v>473876</v>
       </c>
       <c r="R5" t="n">
-        <v>6872637</v>
+        <v>6872692</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124658172</v>
+        <v>124658443</v>
       </c>
       <c r="B6" t="n">
         <v>78547</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473877</v>
+        <v>473856</v>
       </c>
       <c r="R6" t="n">
-        <v>6872665</v>
+        <v>6872612</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124659240</v>
+        <v>124658172</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473810</v>
+        <v>473877</v>
       </c>
       <c r="R8" t="n">
-        <v>6872485</v>
+        <v>6872665</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124828791</v>
+        <v>124827627</v>
       </c>
       <c r="B9" t="n">
-        <v>78194</v>
+        <v>78547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473589</v>
+        <v>473780</v>
       </c>
       <c r="R9" t="n">
-        <v>6872813</v>
+        <v>6872856</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124829811</v>
+        <v>124828799</v>
       </c>
       <c r="B10" t="n">
-        <v>79926</v>
+        <v>77738</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473654</v>
+        <v>473591</v>
       </c>
       <c r="R10" t="n">
-        <v>6872997</v>
+        <v>6872817</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124828081</v>
+        <v>124829811</v>
       </c>
       <c r="B12" t="n">
-        <v>79399</v>
+        <v>79926</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473705</v>
+        <v>473654</v>
       </c>
       <c r="R12" t="n">
-        <v>6872721</v>
+        <v>6872997</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124827497</v>
+        <v>124828676</v>
       </c>
       <c r="B14" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473801</v>
+        <v>473614</v>
       </c>
       <c r="R14" t="n">
-        <v>6872850</v>
+        <v>6872815</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124828799</v>
+        <v>124827491</v>
       </c>
       <c r="B15" t="n">
         <v>77738</v>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473591</v>
+        <v>473801</v>
       </c>
       <c r="R15" t="n">
-        <v>6872817</v>
+        <v>6872850</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124829793</v>
+        <v>124827660</v>
       </c>
       <c r="B16" t="n">
-        <v>79927</v>
+        <v>78455</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473654</v>
+        <v>473782</v>
       </c>
       <c r="R16" t="n">
-        <v>6872997</v>
+        <v>6872817</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,7 +2210,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124828676</v>
+        <v>124827748</v>
       </c>
       <c r="B17" t="n">
         <v>78547</v>
@@ -2250,13 +2250,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473614</v>
+        <v>473754</v>
       </c>
       <c r="R17" t="n">
-        <v>6872815</v>
+        <v>6872803</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124826941</v>
+        <v>124827497</v>
       </c>
       <c r="B18" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473804</v>
+        <v>473801</v>
       </c>
       <c r="R18" t="n">
-        <v>6872761</v>
+        <v>6872850</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124827491</v>
+        <v>124829793</v>
       </c>
       <c r="B19" t="n">
-        <v>77738</v>
+        <v>79927</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,13 +2454,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473801</v>
+        <v>473654</v>
       </c>
       <c r="R19" t="n">
-        <v>6872850</v>
+        <v>6872997</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124827660</v>
+        <v>124826736</v>
       </c>
       <c r="B20" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473782</v>
+        <v>473821</v>
       </c>
       <c r="R20" t="n">
-        <v>6872817</v>
+        <v>6872738</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,7 +2618,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124826736</v>
+        <v>124826941</v>
       </c>
       <c r="B21" t="n">
         <v>78547</v>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473821</v>
+        <v>473804</v>
       </c>
       <c r="R21" t="n">
-        <v>6872738</v>
+        <v>6872761</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124827627</v>
+        <v>124828791</v>
       </c>
       <c r="B22" t="n">
-        <v>78547</v>
+        <v>78194</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473780</v>
+        <v>473589</v>
       </c>
       <c r="R22" t="n">
-        <v>6872856</v>
+        <v>6872813</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124827748</v>
+        <v>124828081</v>
       </c>
       <c r="B23" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473754</v>
+        <v>473705</v>
       </c>
       <c r="R23" t="n">
-        <v>6872803</v>
+        <v>6872721</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125074318</v>
+        <v>125073052</v>
       </c>
       <c r="B24" t="n">
-        <v>78455</v>
+        <v>79920</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,41 +2936,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473722</v>
+        <v>473748</v>
       </c>
       <c r="R24" t="n">
-        <v>6872544</v>
+        <v>6872489</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125073338</v>
+        <v>125075883</v>
       </c>
       <c r="B25" t="n">
-        <v>79399</v>
+        <v>78455</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,37 +3042,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473722</v>
+        <v>473613</v>
       </c>
       <c r="R25" t="n">
-        <v>6872521</v>
+        <v>6872761</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125073430</v>
+        <v>125074165</v>
       </c>
       <c r="B26" t="n">
-        <v>57666</v>
+        <v>78455</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,13 +3168,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473712</v>
+        <v>473690</v>
       </c>
       <c r="R26" t="n">
-        <v>6872523</v>
+        <v>6872539</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3204,11 +3204,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3235,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125074811</v>
+        <v>125076500</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,21 +3246,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473732</v>
+        <v>473798</v>
       </c>
       <c r="R27" t="n">
-        <v>6872579</v>
+        <v>6872597</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3337,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125075630</v>
+        <v>125072999</v>
       </c>
       <c r="B28" t="n">
-        <v>79399</v>
+        <v>79891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3353,37 +3348,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473566</v>
+        <v>473747</v>
       </c>
       <c r="R28" t="n">
-        <v>6872757</v>
+        <v>6872493</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3439,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125075154</v>
+        <v>125073936</v>
       </c>
       <c r="B29" t="n">
-        <v>78455</v>
+        <v>79399</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3455,34 +3450,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473625</v>
+        <v>473695</v>
       </c>
       <c r="R29" t="n">
-        <v>6872585</v>
+        <v>6872466</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3541,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125074047</v>
+        <v>125075295</v>
       </c>
       <c r="B30" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3557,34 +3552,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473665</v>
+        <v>473553</v>
       </c>
       <c r="R30" t="n">
-        <v>6872487</v>
+        <v>6872662</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3643,7 +3638,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125075202</v>
+        <v>125075505</v>
       </c>
       <c r="B31" t="n">
         <v>78455</v>
@@ -3683,10 +3678,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473594</v>
+        <v>473523</v>
       </c>
       <c r="R31" t="n">
-        <v>6872603</v>
+        <v>6872722</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3745,10 +3740,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125074731</v>
+        <v>125073338</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>79399</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3757,50 +3752,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473769</v>
+        <v>473722</v>
       </c>
       <c r="R32" t="n">
-        <v>6872532</v>
+        <v>6872521</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3856,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125074664</v>
+        <v>125072978</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>79892</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3868,47 +3854,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473761</v>
+        <v>473749</v>
       </c>
       <c r="R33" t="n">
-        <v>6872503</v>
+        <v>6872487</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,10 +3944,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125073530</v>
+        <v>125072596</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3979,47 +3956,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473728</v>
+        <v>473742</v>
       </c>
       <c r="R34" t="n">
-        <v>6872500</v>
+        <v>6872438</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4078,10 +4046,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125073474</v>
+        <v>125075258</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4090,50 +4058,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473716</v>
+        <v>473585</v>
       </c>
       <c r="R35" t="n">
-        <v>6872520</v>
+        <v>6872639</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4189,10 +4148,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125073267</v>
+        <v>125073430</v>
       </c>
       <c r="B36" t="n">
-        <v>79920</v>
+        <v>57666</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4201,25 +4160,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4229,10 +4188,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473732</v>
+        <v>473712</v>
       </c>
       <c r="R36" t="n">
-        <v>6872498</v>
+        <v>6872523</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4265,6 +4224,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4291,10 +4255,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125072978</v>
+        <v>125074731</v>
       </c>
       <c r="B37" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4303,38 +4267,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473749</v>
+        <v>473769</v>
       </c>
       <c r="R37" t="n">
-        <v>6872487</v>
+        <v>6872532</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4393,10 +4366,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125075491</v>
+        <v>125074664</v>
       </c>
       <c r="B38" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4405,41 +4378,50 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473523</v>
+        <v>473761</v>
       </c>
       <c r="R38" t="n">
-        <v>6872722</v>
+        <v>6872503</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4495,7 +4477,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125073936</v>
+        <v>125075630</v>
       </c>
       <c r="B39" t="n">
         <v>79399</v>
@@ -4531,17 +4513,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473695</v>
+        <v>473566</v>
       </c>
       <c r="R39" t="n">
-        <v>6872466</v>
+        <v>6872757</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4597,10 +4579,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125073146</v>
+        <v>125073255</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>79892</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4609,47 +4591,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473748</v>
+        <v>473735</v>
       </c>
       <c r="R40" t="n">
-        <v>6872493</v>
+        <v>6872503</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4708,10 +4681,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125074232</v>
+        <v>125074741</v>
       </c>
       <c r="B41" t="n">
-        <v>78547</v>
+        <v>79892</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4724,34 +4697,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473700</v>
+        <v>473756</v>
       </c>
       <c r="R41" t="n">
-        <v>6872562</v>
+        <v>6872526</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4810,10 +4783,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125074741</v>
+        <v>125076393</v>
       </c>
       <c r="B42" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4826,21 +4799,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4850,10 +4823,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473756</v>
+        <v>473731</v>
       </c>
       <c r="R42" t="n">
-        <v>6872526</v>
+        <v>6872691</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4886,6 +4859,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4912,10 +4890,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125072827</v>
+        <v>125071546</v>
       </c>
       <c r="B43" t="n">
-        <v>78546</v>
+        <v>56722</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4924,25 +4902,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4952,10 +4930,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473758</v>
+        <v>473832</v>
       </c>
       <c r="R43" t="n">
-        <v>6872471</v>
+        <v>6872552</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4988,6 +4966,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5014,10 +4997,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125073578</v>
+        <v>125073267</v>
       </c>
       <c r="B44" t="n">
-        <v>98122</v>
+        <v>79920</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5030,43 +5013,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473736</v>
+        <v>473732</v>
       </c>
       <c r="R44" t="n">
-        <v>6872499</v>
+        <v>6872498</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5125,10 +5099,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125072596</v>
+        <v>125074232</v>
       </c>
       <c r="B45" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5141,21 +5115,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5165,10 +5139,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473742</v>
+        <v>473700</v>
       </c>
       <c r="R45" t="n">
-        <v>6872438</v>
+        <v>6872562</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5227,10 +5201,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125072658</v>
+        <v>125074047</v>
       </c>
       <c r="B46" t="n">
-        <v>78546</v>
+        <v>78455</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5243,21 +5217,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5267,13 +5241,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473760</v>
+        <v>473665</v>
       </c>
       <c r="R46" t="n">
-        <v>6872467</v>
+        <v>6872487</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5329,10 +5303,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125076500</v>
+        <v>125072916</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5341,38 +5315,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473798</v>
+        <v>473748</v>
       </c>
       <c r="R47" t="n">
-        <v>6872597</v>
+        <v>6872490</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5431,10 +5405,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125074165</v>
+        <v>125074811</v>
       </c>
       <c r="B48" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5447,34 +5421,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473690</v>
+        <v>473732</v>
       </c>
       <c r="R48" t="n">
-        <v>6872539</v>
+        <v>6872579</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5533,10 +5507,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125074134</v>
+        <v>125075491</v>
       </c>
       <c r="B49" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5549,34 +5523,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473684</v>
+        <v>473523</v>
       </c>
       <c r="R49" t="n">
-        <v>6872544</v>
+        <v>6872722</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5635,10 +5609,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125076393</v>
+        <v>125075349</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>78546</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5651,21 +5625,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5675,10 +5649,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473731</v>
+        <v>473530</v>
       </c>
       <c r="R50" t="n">
-        <v>6872691</v>
+        <v>6872681</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5711,11 +5685,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5742,10 +5711,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125073255</v>
+        <v>125075202</v>
       </c>
       <c r="B51" t="n">
-        <v>79892</v>
+        <v>78455</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5758,37 +5727,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473735</v>
+        <v>473594</v>
       </c>
       <c r="R51" t="n">
-        <v>6872503</v>
+        <v>6872603</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5844,10 +5813,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125075710</v>
+        <v>125073530</v>
       </c>
       <c r="B52" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5856,38 +5825,47 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473570</v>
+        <v>473728</v>
       </c>
       <c r="R52" t="n">
-        <v>6872751</v>
+        <v>6872500</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5946,10 +5924,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125073107</v>
+        <v>125073146</v>
       </c>
       <c r="B53" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5958,41 +5936,50 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473750</v>
+        <v>473748</v>
       </c>
       <c r="R53" t="n">
-        <v>6872492</v>
+        <v>6872493</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6048,10 +6035,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125075505</v>
+        <v>125073455</v>
       </c>
       <c r="B54" t="n">
-        <v>78455</v>
+        <v>79399</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6064,37 +6051,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473523</v>
+        <v>473712</v>
       </c>
       <c r="R54" t="n">
-        <v>6872722</v>
+        <v>6872517</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6150,10 +6137,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125072602</v>
+        <v>125073474</v>
       </c>
       <c r="B55" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6162,38 +6149,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473742</v>
+        <v>473716</v>
       </c>
       <c r="R55" t="n">
-        <v>6872438</v>
+        <v>6872520</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6252,10 +6248,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125073052</v>
+        <v>125075336</v>
       </c>
       <c r="B56" t="n">
-        <v>79920</v>
+        <v>78547</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6264,38 +6260,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473748</v>
+        <v>473532</v>
       </c>
       <c r="R56" t="n">
-        <v>6872489</v>
+        <v>6872688</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6354,7 +6350,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125075349</v>
+        <v>125072658</v>
       </c>
       <c r="B57" t="n">
         <v>78546</v>
@@ -6390,14 +6386,14 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473530</v>
+        <v>473760</v>
       </c>
       <c r="R57" t="n">
-        <v>6872681</v>
+        <v>6872467</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6456,10 +6452,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125072999</v>
+        <v>125072827</v>
       </c>
       <c r="B58" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6472,21 +6468,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6496,10 +6492,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>473747</v>
+        <v>473758</v>
       </c>
       <c r="R58" t="n">
-        <v>6872493</v>
+        <v>6872471</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6558,10 +6554,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125073833</v>
+        <v>125073578</v>
       </c>
       <c r="B59" t="n">
-        <v>78455</v>
+        <v>98122</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6570,41 +6566,50 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473697</v>
+        <v>473736</v>
       </c>
       <c r="R59" t="n">
-        <v>6872466</v>
+        <v>6872499</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6660,10 +6665,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125075295</v>
+        <v>125075710</v>
       </c>
       <c r="B60" t="n">
-        <v>78547</v>
+        <v>79428</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6676,21 +6681,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6700,13 +6705,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473553</v>
+        <v>473570</v>
       </c>
       <c r="R60" t="n">
-        <v>6872662</v>
+        <v>6872751</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6762,10 +6767,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125072916</v>
+        <v>125073107</v>
       </c>
       <c r="B61" t="n">
-        <v>79927</v>
+        <v>78842</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6774,25 +6779,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6802,13 +6807,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473748</v>
+        <v>473750</v>
       </c>
       <c r="R61" t="n">
-        <v>6872490</v>
+        <v>6872492</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6864,10 +6869,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125075258</v>
+        <v>125072602</v>
       </c>
       <c r="B62" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6880,37 +6885,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>473585</v>
+        <v>473742</v>
       </c>
       <c r="R62" t="n">
-        <v>6872639</v>
+        <v>6872438</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6966,10 +6971,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125076033</v>
+        <v>125075154</v>
       </c>
       <c r="B63" t="n">
-        <v>57513</v>
+        <v>78455</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6982,21 +6987,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7006,10 +7011,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>473693</v>
+        <v>473625</v>
       </c>
       <c r="R63" t="n">
-        <v>6872740</v>
+        <v>6872585</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7042,11 +7047,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7073,10 +7073,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125074681</v>
+        <v>125076033</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7085,47 +7085,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>473765</v>
+        <v>473693</v>
       </c>
       <c r="R64" t="n">
-        <v>6872521</v>
+        <v>6872740</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7158,6 +7149,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7184,10 +7180,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125075336</v>
+        <v>125074318</v>
       </c>
       <c r="B65" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7200,21 +7196,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7224,13 +7220,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473532</v>
+        <v>473722</v>
       </c>
       <c r="R65" t="n">
-        <v>6872688</v>
+        <v>6872544</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7286,10 +7282,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125071546</v>
+        <v>125073833</v>
       </c>
       <c r="B66" t="n">
-        <v>56722</v>
+        <v>78455</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7298,25 +7294,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7326,10 +7322,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>473832</v>
+        <v>473697</v>
       </c>
       <c r="R66" t="n">
-        <v>6872552</v>
+        <v>6872466</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7362,11 +7358,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7393,10 +7384,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125073455</v>
+        <v>125074681</v>
       </c>
       <c r="B67" t="n">
-        <v>79399</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7405,38 +7396,47 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>473712</v>
+        <v>473765</v>
       </c>
       <c r="R67" t="n">
-        <v>6872517</v>
+        <v>6872521</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7495,7 +7495,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125075883</v>
+        <v>125074134</v>
       </c>
       <c r="B68" t="n">
         <v>78455</v>
@@ -7531,17 +7531,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>473613</v>
+        <v>473684</v>
       </c>
       <c r="R68" t="n">
-        <v>6872761</v>
+        <v>6872544</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124828707</v>
+        <v>124828676</v>
       </c>
       <c r="B13" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1848,7 +1848,7 @@
         <v>6872815</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124828676</v>
+        <v>124828707</v>
       </c>
       <c r="B14" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1950,7 +1950,7 @@
         <v>6872815</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124826941</v>
+        <v>124828791</v>
       </c>
       <c r="B21" t="n">
-        <v>78547</v>
+        <v>78194</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473804</v>
+        <v>473589</v>
       </c>
       <c r="R21" t="n">
-        <v>6872761</v>
+        <v>6872813</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124828791</v>
+        <v>124826941</v>
       </c>
       <c r="B22" t="n">
-        <v>78194</v>
+        <v>78547</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473589</v>
+        <v>473804</v>
       </c>
       <c r="R22" t="n">
-        <v>6872813</v>
+        <v>6872761</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125073052</v>
+        <v>125075883</v>
       </c>
       <c r="B24" t="n">
-        <v>79920</v>
+        <v>78455</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2936,38 +2936,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473748</v>
+        <v>473613</v>
       </c>
       <c r="R24" t="n">
-        <v>6872489</v>
+        <v>6872761</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125075883</v>
+        <v>125073052</v>
       </c>
       <c r="B25" t="n">
-        <v>78455</v>
+        <v>79920</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,38 +3038,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473613</v>
+        <v>473748</v>
       </c>
       <c r="R25" t="n">
-        <v>6872761</v>
+        <v>6872489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125074165</v>
+        <v>125076500</v>
       </c>
       <c r="B26" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,34 +3144,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473690</v>
+        <v>473798</v>
       </c>
       <c r="R26" t="n">
-        <v>6872539</v>
+        <v>6872597</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125076500</v>
+        <v>125072999</v>
       </c>
       <c r="B27" t="n">
         <v>79891</v>
@@ -3266,14 +3266,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473798</v>
+        <v>473747</v>
       </c>
       <c r="R27" t="n">
-        <v>6872597</v>
+        <v>6872493</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125072999</v>
+        <v>125073936</v>
       </c>
       <c r="B28" t="n">
-        <v>79891</v>
+        <v>79399</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,21 +3348,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473747</v>
+        <v>473695</v>
       </c>
       <c r="R28" t="n">
-        <v>6872493</v>
+        <v>6872466</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125073936</v>
+        <v>125074165</v>
       </c>
       <c r="B29" t="n">
-        <v>79399</v>
+        <v>78455</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473695</v>
+        <v>473690</v>
       </c>
       <c r="R29" t="n">
-        <v>6872466</v>
+        <v>6872539</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125073338</v>
+        <v>125075258</v>
       </c>
       <c r="B32" t="n">
-        <v>79399</v>
+        <v>78455</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3756,34 +3756,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473722</v>
+        <v>473585</v>
       </c>
       <c r="R32" t="n">
-        <v>6872521</v>
+        <v>6872639</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125072596</v>
+        <v>125073430</v>
       </c>
       <c r="B34" t="n">
-        <v>78546</v>
+        <v>57666</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3984,13 +3984,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473742</v>
+        <v>473712</v>
       </c>
       <c r="R34" t="n">
-        <v>6872438</v>
+        <v>6872523</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4020,6 +4020,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4046,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125075258</v>
+        <v>125074731</v>
       </c>
       <c r="B35" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4058,41 +4063,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473585</v>
+        <v>473769</v>
       </c>
       <c r="R35" t="n">
-        <v>6872639</v>
+        <v>6872532</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4148,10 +4162,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125073430</v>
+        <v>125074664</v>
       </c>
       <c r="B36" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4160,41 +4174,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473712</v>
+        <v>473761</v>
       </c>
       <c r="R36" t="n">
-        <v>6872523</v>
+        <v>6872503</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4224,11 +4247,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4255,10 +4273,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125074731</v>
+        <v>125073338</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>79399</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4267,50 +4285,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473769</v>
+        <v>473722</v>
       </c>
       <c r="R37" t="n">
-        <v>6872532</v>
+        <v>6872521</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4366,10 +4375,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125074664</v>
+        <v>125072596</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4378,47 +4387,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473761</v>
+        <v>473742</v>
       </c>
       <c r="R38" t="n">
-        <v>6872503</v>
+        <v>6872438</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5099,10 +5099,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125074232</v>
+        <v>125074047</v>
       </c>
       <c r="B45" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5115,21 +5115,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5139,13 +5139,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473700</v>
+        <v>473665</v>
       </c>
       <c r="R45" t="n">
-        <v>6872562</v>
+        <v>6872487</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5201,10 +5201,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125074047</v>
+        <v>125072916</v>
       </c>
       <c r="B46" t="n">
-        <v>78455</v>
+        <v>79927</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5213,25 +5213,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473665</v>
+        <v>473748</v>
       </c>
       <c r="R46" t="n">
-        <v>6872487</v>
+        <v>6872490</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5303,10 +5303,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125072916</v>
+        <v>125074811</v>
       </c>
       <c r="B47" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5315,38 +5315,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473748</v>
+        <v>473732</v>
       </c>
       <c r="R47" t="n">
-        <v>6872490</v>
+        <v>6872579</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5405,10 +5405,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125074811</v>
+        <v>125074232</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5421,34 +5421,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473732</v>
+        <v>473700</v>
       </c>
       <c r="R48" t="n">
-        <v>6872579</v>
+        <v>6872562</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6350,10 +6350,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125072658</v>
+        <v>125073578</v>
       </c>
       <c r="B57" t="n">
-        <v>78546</v>
+        <v>98122</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6362,41 +6362,50 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473760</v>
+        <v>473736</v>
       </c>
       <c r="R57" t="n">
-        <v>6872467</v>
+        <v>6872499</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6452,7 +6461,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125072827</v>
+        <v>125072658</v>
       </c>
       <c r="B58" t="n">
         <v>78546</v>
@@ -6492,10 +6501,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>473758</v>
+        <v>473760</v>
       </c>
       <c r="R58" t="n">
-        <v>6872471</v>
+        <v>6872467</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6554,10 +6563,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125073578</v>
+        <v>125072827</v>
       </c>
       <c r="B59" t="n">
-        <v>98122</v>
+        <v>78546</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6566,50 +6575,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473736</v>
+        <v>473758</v>
       </c>
       <c r="R59" t="n">
-        <v>6872499</v>
+        <v>6872471</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6665,10 +6665,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125075710</v>
+        <v>125072602</v>
       </c>
       <c r="B60" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6681,34 +6681,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473570</v>
+        <v>473742</v>
       </c>
       <c r="R60" t="n">
-        <v>6872751</v>
+        <v>6872438</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6767,10 +6767,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125073107</v>
+        <v>125075710</v>
       </c>
       <c r="B61" t="n">
-        <v>78842</v>
+        <v>79428</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6783,37 +6783,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473750</v>
+        <v>473570</v>
       </c>
       <c r="R61" t="n">
-        <v>6872492</v>
+        <v>6872751</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6869,10 +6869,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125072602</v>
+        <v>125073107</v>
       </c>
       <c r="B62" t="n">
-        <v>78547</v>
+        <v>78842</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6885,21 +6885,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6909,13 +6909,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>473742</v>
+        <v>473750</v>
       </c>
       <c r="R62" t="n">
-        <v>6872438</v>
+        <v>6872492</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124658285</v>
+        <v>124659214</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473876</v>
+        <v>473837</v>
       </c>
       <c r="R2" t="n">
-        <v>6872637</v>
+        <v>6872441</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124657817</v>
+        <v>124659240</v>
       </c>
       <c r="B3" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473891</v>
+        <v>473810</v>
       </c>
       <c r="R3" t="n">
-        <v>6872741</v>
+        <v>6872485</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124659240</v>
+        <v>124658443</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473810</v>
+        <v>473856</v>
       </c>
       <c r="R4" t="n">
-        <v>6872485</v>
+        <v>6872612</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124658443</v>
+        <v>124657817</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473856</v>
+        <v>473891</v>
       </c>
       <c r="R6" t="n">
-        <v>6872612</v>
+        <v>6872741</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124659214</v>
+        <v>124658172</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473837</v>
+        <v>473877</v>
       </c>
       <c r="R7" t="n">
-        <v>6872441</v>
+        <v>6872665</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124658172</v>
+        <v>124658285</v>
       </c>
       <c r="B8" t="n">
         <v>78547</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473877</v>
+        <v>473876</v>
       </c>
       <c r="R8" t="n">
-        <v>6872665</v>
+        <v>6872637</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124827627</v>
+        <v>124829811</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>79926</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473780</v>
+        <v>473654</v>
       </c>
       <c r="R9" t="n">
-        <v>6872856</v>
+        <v>6872997</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124828799</v>
+        <v>124827627</v>
       </c>
       <c r="B10" t="n">
-        <v>77738</v>
+        <v>78547</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473591</v>
+        <v>473780</v>
       </c>
       <c r="R10" t="n">
-        <v>6872817</v>
+        <v>6872856</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124828245</v>
+        <v>124827491</v>
       </c>
       <c r="B11" t="n">
-        <v>78546</v>
+        <v>77738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473687</v>
+        <v>473801</v>
       </c>
       <c r="R11" t="n">
-        <v>6872750</v>
+        <v>6872850</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124829811</v>
+        <v>124826736</v>
       </c>
       <c r="B12" t="n">
-        <v>79926</v>
+        <v>78547</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473654</v>
+        <v>473821</v>
       </c>
       <c r="R12" t="n">
-        <v>6872997</v>
+        <v>6872738</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124828676</v>
+        <v>124826941</v>
       </c>
       <c r="B13" t="n">
         <v>78547</v>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473614</v>
+        <v>473804</v>
       </c>
       <c r="R13" t="n">
-        <v>6872815</v>
+        <v>6872761</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124828707</v>
+        <v>124827748</v>
       </c>
       <c r="B14" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473614</v>
+        <v>473754</v>
       </c>
       <c r="R14" t="n">
-        <v>6872815</v>
+        <v>6872803</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2006,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124827491</v>
+        <v>124828799</v>
       </c>
       <c r="B15" t="n">
         <v>77738</v>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473801</v>
+        <v>473591</v>
       </c>
       <c r="R15" t="n">
-        <v>6872850</v>
+        <v>6872817</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124827660</v>
+        <v>124828707</v>
       </c>
       <c r="B16" t="n">
-        <v>78455</v>
+        <v>78546</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473782</v>
+        <v>473614</v>
       </c>
       <c r="R16" t="n">
-        <v>6872817</v>
+        <v>6872815</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124827748</v>
+        <v>124828791</v>
       </c>
       <c r="B17" t="n">
-        <v>78547</v>
+        <v>78194</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,13 +2250,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473754</v>
+        <v>473589</v>
       </c>
       <c r="R17" t="n">
-        <v>6872803</v>
+        <v>6872813</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124827497</v>
+        <v>124828676</v>
       </c>
       <c r="B18" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473801</v>
+        <v>473614</v>
       </c>
       <c r="R18" t="n">
-        <v>6872850</v>
+        <v>6872815</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124829793</v>
+        <v>124827660</v>
       </c>
       <c r="B19" t="n">
-        <v>79927</v>
+        <v>78455</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473654</v>
+        <v>473782</v>
       </c>
       <c r="R19" t="n">
-        <v>6872997</v>
+        <v>6872817</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124826736</v>
+        <v>124828245</v>
       </c>
       <c r="B20" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473821</v>
+        <v>473687</v>
       </c>
       <c r="R20" t="n">
-        <v>6872738</v>
+        <v>6872750</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124828791</v>
+        <v>124828081</v>
       </c>
       <c r="B21" t="n">
-        <v>78194</v>
+        <v>79399</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473589</v>
+        <v>473705</v>
       </c>
       <c r="R21" t="n">
-        <v>6872813</v>
+        <v>6872721</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124826941</v>
+        <v>124829793</v>
       </c>
       <c r="B22" t="n">
-        <v>78547</v>
+        <v>79927</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,25 +2732,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473804</v>
+        <v>473654</v>
       </c>
       <c r="R22" t="n">
-        <v>6872761</v>
+        <v>6872997</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2822,7 +2822,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124828081</v>
+        <v>124827497</v>
       </c>
       <c r="B23" t="n">
         <v>79399</v>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473705</v>
+        <v>473801</v>
       </c>
       <c r="R23" t="n">
-        <v>6872721</v>
+        <v>6872850</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125075883</v>
+        <v>125072827</v>
       </c>
       <c r="B24" t="n">
-        <v>78455</v>
+        <v>78546</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,34 +2940,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473613</v>
+        <v>473758</v>
       </c>
       <c r="R24" t="n">
-        <v>6872761</v>
+        <v>6872471</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125073052</v>
+        <v>125074318</v>
       </c>
       <c r="B25" t="n">
-        <v>79920</v>
+        <v>78455</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,41 +3038,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473748</v>
+        <v>473722</v>
       </c>
       <c r="R25" t="n">
-        <v>6872489</v>
+        <v>6872544</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125076500</v>
+        <v>125072602</v>
       </c>
       <c r="B26" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,34 +3144,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473798</v>
+        <v>473742</v>
       </c>
       <c r="R26" t="n">
-        <v>6872597</v>
+        <v>6872438</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125072999</v>
+        <v>125075349</v>
       </c>
       <c r="B27" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,34 +3246,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473747</v>
+        <v>473530</v>
       </c>
       <c r="R27" t="n">
-        <v>6872493</v>
+        <v>6872681</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125073936</v>
+        <v>125073455</v>
       </c>
       <c r="B28" t="n">
         <v>79399</v>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473695</v>
+        <v>473712</v>
       </c>
       <c r="R28" t="n">
-        <v>6872466</v>
+        <v>6872517</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125074165</v>
+        <v>125076500</v>
       </c>
       <c r="B29" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,34 +3450,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473690</v>
+        <v>473798</v>
       </c>
       <c r="R29" t="n">
-        <v>6872539</v>
+        <v>6872597</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125075295</v>
+        <v>125075505</v>
       </c>
       <c r="B30" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,21 +3552,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473553</v>
+        <v>473523</v>
       </c>
       <c r="R30" t="n">
-        <v>6872662</v>
+        <v>6872722</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125075505</v>
+        <v>125073833</v>
       </c>
       <c r="B31" t="n">
         <v>78455</v>
@@ -3674,17 +3674,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473523</v>
+        <v>473697</v>
       </c>
       <c r="R31" t="n">
-        <v>6872722</v>
+        <v>6872466</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125075258</v>
+        <v>125072978</v>
       </c>
       <c r="B32" t="n">
-        <v>78455</v>
+        <v>79892</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3756,37 +3756,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473585</v>
+        <v>473749</v>
       </c>
       <c r="R32" t="n">
-        <v>6872639</v>
+        <v>6872487</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125072978</v>
+        <v>125073936</v>
       </c>
       <c r="B33" t="n">
-        <v>79892</v>
+        <v>79399</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3858,21 +3858,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473749</v>
+        <v>473695</v>
       </c>
       <c r="R33" t="n">
-        <v>6872487</v>
+        <v>6872466</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125073430</v>
+        <v>125075154</v>
       </c>
       <c r="B34" t="n">
-        <v>57666</v>
+        <v>78455</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3960,37 +3960,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473712</v>
+        <v>473625</v>
       </c>
       <c r="R34" t="n">
-        <v>6872523</v>
+        <v>6872585</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4020,11 +4020,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4051,7 +4046,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125074731</v>
+        <v>125073146</v>
       </c>
       <c r="B35" t="n">
         <v>98101</v>
@@ -4096,14 +4091,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473769</v>
+        <v>473748</v>
       </c>
       <c r="R35" t="n">
-        <v>6872532</v>
+        <v>6872493</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4162,10 +4157,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125074664</v>
+        <v>125075710</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>79428</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4174,47 +4169,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473761</v>
+        <v>473570</v>
       </c>
       <c r="R36" t="n">
-        <v>6872503</v>
+        <v>6872751</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4273,10 +4259,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125073338</v>
+        <v>125073530</v>
       </c>
       <c r="B37" t="n">
-        <v>79399</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4285,41 +4271,50 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473722</v>
+        <v>473728</v>
       </c>
       <c r="R37" t="n">
-        <v>6872521</v>
+        <v>6872500</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4375,10 +4370,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125072596</v>
+        <v>125075202</v>
       </c>
       <c r="B38" t="n">
-        <v>78546</v>
+        <v>78455</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4391,37 +4386,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473742</v>
+        <v>473594</v>
       </c>
       <c r="R38" t="n">
-        <v>6872438</v>
+        <v>6872603</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4477,10 +4472,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125075630</v>
+        <v>125073578</v>
       </c>
       <c r="B39" t="n">
-        <v>79399</v>
+        <v>98122</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4489,38 +4484,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473566</v>
+        <v>473736</v>
       </c>
       <c r="R39" t="n">
-        <v>6872757</v>
+        <v>6872499</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4579,10 +4583,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125073255</v>
+        <v>125075336</v>
       </c>
       <c r="B40" t="n">
-        <v>79892</v>
+        <v>78547</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4595,34 +4599,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473735</v>
+        <v>473532</v>
       </c>
       <c r="R40" t="n">
-        <v>6872503</v>
+        <v>6872688</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4681,10 +4685,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125074741</v>
+        <v>125075630</v>
       </c>
       <c r="B41" t="n">
-        <v>79892</v>
+        <v>79399</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4697,21 +4701,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4721,13 +4725,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473756</v>
+        <v>473566</v>
       </c>
       <c r="R41" t="n">
-        <v>6872526</v>
+        <v>6872757</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4783,10 +4787,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125076393</v>
+        <v>125073474</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4795,38 +4799,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473731</v>
+        <v>473716</v>
       </c>
       <c r="R42" t="n">
-        <v>6872691</v>
+        <v>6872520</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4859,11 +4872,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4997,10 +5005,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125073267</v>
+        <v>125072658</v>
       </c>
       <c r="B44" t="n">
-        <v>79920</v>
+        <v>78546</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5009,25 +5017,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5037,13 +5045,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473732</v>
+        <v>473760</v>
       </c>
       <c r="R44" t="n">
-        <v>6872498</v>
+        <v>6872467</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5099,7 +5107,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125074047</v>
+        <v>125075883</v>
       </c>
       <c r="B45" t="n">
         <v>78455</v>
@@ -5135,17 +5143,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473665</v>
+        <v>473613</v>
       </c>
       <c r="R45" t="n">
-        <v>6872487</v>
+        <v>6872761</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5201,10 +5209,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125072916</v>
+        <v>125073430</v>
       </c>
       <c r="B46" t="n">
-        <v>79927</v>
+        <v>57666</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5213,25 +5221,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5241,13 +5249,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473748</v>
+        <v>473712</v>
       </c>
       <c r="R46" t="n">
-        <v>6872490</v>
+        <v>6872523</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5277,6 +5285,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5303,10 +5316,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125074811</v>
+        <v>125074731</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5315,38 +5328,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473732</v>
+        <v>473769</v>
       </c>
       <c r="R47" t="n">
-        <v>6872579</v>
+        <v>6872532</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5405,10 +5427,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125074232</v>
+        <v>125073267</v>
       </c>
       <c r="B48" t="n">
-        <v>78547</v>
+        <v>79920</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5417,25 +5439,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5445,13 +5467,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473700</v>
+        <v>473732</v>
       </c>
       <c r="R48" t="n">
-        <v>6872562</v>
+        <v>6872498</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5507,10 +5529,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125075491</v>
+        <v>125074811</v>
       </c>
       <c r="B49" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5523,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5547,13 +5569,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473523</v>
+        <v>473732</v>
       </c>
       <c r="R49" t="n">
-        <v>6872722</v>
+        <v>6872579</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5609,10 +5631,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125075349</v>
+        <v>125074741</v>
       </c>
       <c r="B50" t="n">
-        <v>78546</v>
+        <v>79892</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5625,21 +5647,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5649,10 +5671,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473530</v>
+        <v>473756</v>
       </c>
       <c r="R50" t="n">
-        <v>6872681</v>
+        <v>6872526</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5711,10 +5733,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125075202</v>
+        <v>125074664</v>
       </c>
       <c r="B51" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5723,41 +5745,50 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473594</v>
+        <v>473761</v>
       </c>
       <c r="R51" t="n">
-        <v>6872603</v>
+        <v>6872503</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5813,10 +5844,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125073530</v>
+        <v>125074232</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5825,47 +5856,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473728</v>
+        <v>473700</v>
       </c>
       <c r="R52" t="n">
-        <v>6872500</v>
+        <v>6872562</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5924,10 +5946,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125073146</v>
+        <v>125075295</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5936,50 +5958,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473748</v>
+        <v>473553</v>
       </c>
       <c r="R53" t="n">
-        <v>6872493</v>
+        <v>6872662</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6035,10 +6048,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125073455</v>
+        <v>125072596</v>
       </c>
       <c r="B54" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6051,21 +6064,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6075,10 +6088,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473712</v>
+        <v>473742</v>
       </c>
       <c r="R54" t="n">
-        <v>6872517</v>
+        <v>6872438</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6137,10 +6150,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125073474</v>
+        <v>125074165</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6149,47 +6162,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473716</v>
+        <v>473690</v>
       </c>
       <c r="R55" t="n">
-        <v>6872520</v>
+        <v>6872539</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6248,10 +6252,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125075336</v>
+        <v>125074681</v>
       </c>
       <c r="B56" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6260,38 +6264,47 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473532</v>
+        <v>473765</v>
       </c>
       <c r="R56" t="n">
-        <v>6872688</v>
+        <v>6872521</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6350,10 +6363,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125073578</v>
+        <v>125073338</v>
       </c>
       <c r="B57" t="n">
-        <v>98122</v>
+        <v>79399</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6362,47 +6375,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473736</v>
+        <v>473722</v>
       </c>
       <c r="R57" t="n">
-        <v>6872499</v>
+        <v>6872521</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6461,10 +6465,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125072658</v>
+        <v>125073052</v>
       </c>
       <c r="B58" t="n">
-        <v>78546</v>
+        <v>79920</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6473,25 +6477,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6501,10 +6505,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>473760</v>
+        <v>473748</v>
       </c>
       <c r="R58" t="n">
-        <v>6872467</v>
+        <v>6872489</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6563,10 +6567,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125072827</v>
+        <v>125072916</v>
       </c>
       <c r="B59" t="n">
-        <v>78546</v>
+        <v>79927</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6575,25 +6579,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6603,10 +6607,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473758</v>
+        <v>473748</v>
       </c>
       <c r="R59" t="n">
-        <v>6872471</v>
+        <v>6872490</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6665,10 +6669,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125072602</v>
+        <v>125075258</v>
       </c>
       <c r="B60" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6681,37 +6685,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473742</v>
+        <v>473585</v>
       </c>
       <c r="R60" t="n">
-        <v>6872438</v>
+        <v>6872639</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6767,10 +6771,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125075710</v>
+        <v>125073255</v>
       </c>
       <c r="B61" t="n">
-        <v>79428</v>
+        <v>79892</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6783,34 +6787,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473570</v>
+        <v>473735</v>
       </c>
       <c r="R61" t="n">
-        <v>6872751</v>
+        <v>6872503</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6869,10 +6873,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125073107</v>
+        <v>125076393</v>
       </c>
       <c r="B62" t="n">
-        <v>78842</v>
+        <v>57513</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6885,37 +6889,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>473750</v>
+        <v>473731</v>
       </c>
       <c r="R62" t="n">
-        <v>6872492</v>
+        <v>6872691</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6945,6 +6949,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6971,10 +6980,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125075154</v>
+        <v>125076033</v>
       </c>
       <c r="B63" t="n">
-        <v>78455</v>
+        <v>57513</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6987,21 +6996,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7011,10 +7020,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>473625</v>
+        <v>473693</v>
       </c>
       <c r="R63" t="n">
-        <v>6872585</v>
+        <v>6872740</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7047,6 +7056,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7073,10 +7087,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125076033</v>
+        <v>125074134</v>
       </c>
       <c r="B64" t="n">
-        <v>57513</v>
+        <v>78455</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7089,37 +7103,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>473693</v>
+        <v>473684</v>
       </c>
       <c r="R64" t="n">
-        <v>6872740</v>
+        <v>6872544</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7149,11 +7163,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7180,10 +7189,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125074318</v>
+        <v>125075491</v>
       </c>
       <c r="B65" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7196,21 +7205,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7220,10 +7229,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473722</v>
+        <v>473523</v>
       </c>
       <c r="R65" t="n">
-        <v>6872544</v>
+        <v>6872722</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7282,10 +7291,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125073833</v>
+        <v>125072999</v>
       </c>
       <c r="B66" t="n">
-        <v>78455</v>
+        <v>79891</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7298,21 +7307,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7322,10 +7331,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>473697</v>
+        <v>473747</v>
       </c>
       <c r="R66" t="n">
-        <v>6872466</v>
+        <v>6872493</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7384,10 +7393,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125074681</v>
+        <v>125073107</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7396,50 +7405,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>473765</v>
+        <v>473750</v>
       </c>
       <c r="R67" t="n">
-        <v>6872521</v>
+        <v>6872492</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125074134</v>
+        <v>125074047</v>
       </c>
       <c r="B68" t="n">
         <v>78455</v>
@@ -7535,10 +7535,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>473684</v>
+        <v>473665</v>
       </c>
       <c r="R68" t="n">
-        <v>6872544</v>
+        <v>6872487</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124659214</v>
+        <v>124658443</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>78684</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473837</v>
+        <v>473856</v>
       </c>
       <c r="R2" t="n">
-        <v>6872441</v>
+        <v>6872612</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124659240</v>
+        <v>124658172</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78684</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473810</v>
+        <v>473877</v>
       </c>
       <c r="R3" t="n">
-        <v>6872485</v>
+        <v>6872665</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124658443</v>
+        <v>124659240</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>80028</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473856</v>
+        <v>473810</v>
       </c>
       <c r="R4" t="n">
-        <v>6872612</v>
+        <v>6872485</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124658043</v>
+        <v>124659214</v>
       </c>
       <c r="B5" t="n">
-        <v>78455</v>
+        <v>80028</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473876</v>
+        <v>473837</v>
       </c>
       <c r="R5" t="n">
-        <v>6872692</v>
+        <v>6872441</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,7 +1086,7 @@
         <v>124657817</v>
       </c>
       <c r="B6" t="n">
-        <v>78455</v>
+        <v>78592</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124658172</v>
+        <v>124658043</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>78592</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473877</v>
+        <v>473876</v>
       </c>
       <c r="R7" t="n">
-        <v>6872665</v>
+        <v>6872692</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,7 +1295,7 @@
         <v>124658285</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>78684</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124829811</v>
+        <v>124829793</v>
       </c>
       <c r="B9" t="n">
-        <v>79926</v>
+        <v>80064</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124827627</v>
+        <v>124828707</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>78683</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473780</v>
+        <v>473614</v>
       </c>
       <c r="R10" t="n">
-        <v>6872856</v>
+        <v>6872815</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124827491</v>
+        <v>124826736</v>
       </c>
       <c r="B11" t="n">
-        <v>77738</v>
+        <v>78684</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473801</v>
+        <v>473821</v>
       </c>
       <c r="R11" t="n">
-        <v>6872850</v>
+        <v>6872738</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124826736</v>
+        <v>124829811</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>80063</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473821</v>
+        <v>473654</v>
       </c>
       <c r="R12" t="n">
-        <v>6872738</v>
+        <v>6872997</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124826941</v>
+        <v>124827748</v>
       </c>
       <c r="B13" t="n">
-        <v>78547</v>
+        <v>78684</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473804</v>
+        <v>473754</v>
       </c>
       <c r="R13" t="n">
-        <v>6872761</v>
+        <v>6872803</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124827748</v>
+        <v>124828799</v>
       </c>
       <c r="B14" t="n">
-        <v>78547</v>
+        <v>77874</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473754</v>
+        <v>473591</v>
       </c>
       <c r="R14" t="n">
-        <v>6872803</v>
+        <v>6872817</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124828799</v>
+        <v>124828245</v>
       </c>
       <c r="B15" t="n">
-        <v>77738</v>
+        <v>78683</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473591</v>
+        <v>473687</v>
       </c>
       <c r="R15" t="n">
-        <v>6872817</v>
+        <v>6872750</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124828707</v>
+        <v>124827627</v>
       </c>
       <c r="B16" t="n">
-        <v>78546</v>
+        <v>78684</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473614</v>
+        <v>473780</v>
       </c>
       <c r="R16" t="n">
-        <v>6872815</v>
+        <v>6872856</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124828791</v>
+        <v>124828676</v>
       </c>
       <c r="B17" t="n">
-        <v>78194</v>
+        <v>78684</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473589</v>
+        <v>473614</v>
       </c>
       <c r="R17" t="n">
-        <v>6872813</v>
+        <v>6872815</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124828676</v>
+        <v>124827660</v>
       </c>
       <c r="B18" t="n">
-        <v>78547</v>
+        <v>78592</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473614</v>
+        <v>473782</v>
       </c>
       <c r="R18" t="n">
-        <v>6872815</v>
+        <v>6872817</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124827660</v>
+        <v>124828791</v>
       </c>
       <c r="B19" t="n">
-        <v>78455</v>
+        <v>78331</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473782</v>
+        <v>473589</v>
       </c>
       <c r="R19" t="n">
-        <v>6872817</v>
+        <v>6872813</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124828245</v>
+        <v>124826941</v>
       </c>
       <c r="B20" t="n">
-        <v>78546</v>
+        <v>78684</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473687</v>
+        <v>473804</v>
       </c>
       <c r="R20" t="n">
-        <v>6872750</v>
+        <v>6872761</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124828081</v>
+        <v>124827497</v>
       </c>
       <c r="B21" t="n">
-        <v>79399</v>
+        <v>79536</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473705</v>
+        <v>473801</v>
       </c>
       <c r="R21" t="n">
-        <v>6872721</v>
+        <v>6872850</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124829793</v>
+        <v>124827491</v>
       </c>
       <c r="B22" t="n">
-        <v>79927</v>
+        <v>77874</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,25 +2732,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,13 +2760,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473654</v>
+        <v>473801</v>
       </c>
       <c r="R22" t="n">
-        <v>6872997</v>
+        <v>6872850</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124827497</v>
+        <v>124828081</v>
       </c>
       <c r="B23" t="n">
-        <v>79399</v>
+        <v>79536</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473801</v>
+        <v>473705</v>
       </c>
       <c r="R23" t="n">
-        <v>6872850</v>
+        <v>6872721</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125072827</v>
+        <v>125075710</v>
       </c>
       <c r="B24" t="n">
-        <v>78546</v>
+        <v>79565</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,34 +2940,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473758</v>
+        <v>473570</v>
       </c>
       <c r="R24" t="n">
-        <v>6872471</v>
+        <v>6872751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125074318</v>
+        <v>125075258</v>
       </c>
       <c r="B25" t="n">
-        <v>78455</v>
+        <v>78592</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473722</v>
+        <v>473585</v>
       </c>
       <c r="R25" t="n">
-        <v>6872544</v>
+        <v>6872639</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125072602</v>
+        <v>125075630</v>
       </c>
       <c r="B26" t="n">
-        <v>78547</v>
+        <v>79536</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,37 +3144,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473742</v>
+        <v>473566</v>
       </c>
       <c r="R26" t="n">
-        <v>6872438</v>
+        <v>6872757</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125075349</v>
+        <v>125073052</v>
       </c>
       <c r="B27" t="n">
-        <v>78546</v>
+        <v>80057</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,38 +3242,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473530</v>
+        <v>473748</v>
       </c>
       <c r="R27" t="n">
-        <v>6872681</v>
+        <v>6872489</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125073455</v>
+        <v>125075349</v>
       </c>
       <c r="B28" t="n">
-        <v>79399</v>
+        <v>78683</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,34 +3348,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473712</v>
+        <v>473530</v>
       </c>
       <c r="R28" t="n">
-        <v>6872517</v>
+        <v>6872681</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125076500</v>
+        <v>125072999</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3470,14 +3470,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473798</v>
+        <v>473747</v>
       </c>
       <c r="R29" t="n">
-        <v>6872597</v>
+        <v>6872493</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125075505</v>
+        <v>125072916</v>
       </c>
       <c r="B30" t="n">
-        <v>78455</v>
+        <v>80064</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3548,41 +3548,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473523</v>
+        <v>473748</v>
       </c>
       <c r="R30" t="n">
-        <v>6872722</v>
+        <v>6872490</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125073833</v>
+        <v>125071546</v>
       </c>
       <c r="B31" t="n">
-        <v>78455</v>
+        <v>56836</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3650,25 +3650,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473697</v>
+        <v>473832</v>
       </c>
       <c r="R31" t="n">
-        <v>6872466</v>
+        <v>6872552</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3714,6 +3714,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3740,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125072978</v>
+        <v>125072596</v>
       </c>
       <c r="B32" t="n">
-        <v>79892</v>
+        <v>78683</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3756,21 +3761,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3780,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473749</v>
+        <v>473742</v>
       </c>
       <c r="R32" t="n">
-        <v>6872487</v>
+        <v>6872438</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3842,10 +3847,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125073936</v>
+        <v>125073455</v>
       </c>
       <c r="B33" t="n">
-        <v>79399</v>
+        <v>79536</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3882,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473695</v>
+        <v>473712</v>
       </c>
       <c r="R33" t="n">
-        <v>6872466</v>
+        <v>6872517</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3944,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125075154</v>
+        <v>125074165</v>
       </c>
       <c r="B34" t="n">
-        <v>78455</v>
+        <v>78592</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3980,14 +3985,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473625</v>
+        <v>473690</v>
       </c>
       <c r="R34" t="n">
-        <v>6872585</v>
+        <v>6872539</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4046,10 +4051,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125073146</v>
+        <v>125074681</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4081,7 +4086,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4091,14 +4096,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473748</v>
+        <v>473765</v>
       </c>
       <c r="R35" t="n">
-        <v>6872493</v>
+        <v>6872521</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4157,10 +4162,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125075710</v>
+        <v>125073255</v>
       </c>
       <c r="B36" t="n">
-        <v>79428</v>
+        <v>80029</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4173,34 +4178,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473570</v>
+        <v>473735</v>
       </c>
       <c r="R36" t="n">
-        <v>6872751</v>
+        <v>6872503</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4259,10 +4264,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125073530</v>
+        <v>125075295</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>78684</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4271,50 +4276,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473728</v>
+        <v>473553</v>
       </c>
       <c r="R37" t="n">
-        <v>6872500</v>
+        <v>6872662</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4370,10 +4366,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125075202</v>
+        <v>125075154</v>
       </c>
       <c r="B38" t="n">
-        <v>78455</v>
+        <v>78592</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4410,13 +4406,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473594</v>
+        <v>473625</v>
       </c>
       <c r="R38" t="n">
-        <v>6872603</v>
+        <v>6872585</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4472,10 +4468,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125073578</v>
+        <v>125074741</v>
       </c>
       <c r="B39" t="n">
-        <v>98122</v>
+        <v>80029</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4484,50 +4480,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473736</v>
+        <v>473756</v>
       </c>
       <c r="R39" t="n">
-        <v>6872499</v>
+        <v>6872526</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4583,10 +4570,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125075336</v>
+        <v>125075202</v>
       </c>
       <c r="B40" t="n">
-        <v>78547</v>
+        <v>78592</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4599,21 +4586,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4623,13 +4610,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473532</v>
+        <v>473594</v>
       </c>
       <c r="R40" t="n">
-        <v>6872688</v>
+        <v>6872603</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4685,10 +4672,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125075630</v>
+        <v>125074134</v>
       </c>
       <c r="B41" t="n">
-        <v>79399</v>
+        <v>78592</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4701,34 +4688,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473566</v>
+        <v>473684</v>
       </c>
       <c r="R41" t="n">
-        <v>6872757</v>
+        <v>6872544</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4787,10 +4774,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125073474</v>
+        <v>125073430</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>57793</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4799,50 +4786,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473716</v>
+        <v>473712</v>
       </c>
       <c r="R42" t="n">
-        <v>6872520</v>
+        <v>6872523</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4872,6 +4850,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4898,10 +4881,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125071546</v>
+        <v>125074318</v>
       </c>
       <c r="B43" t="n">
-        <v>56722</v>
+        <v>78592</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4910,41 +4893,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473832</v>
+        <v>473722</v>
       </c>
       <c r="R43" t="n">
-        <v>6872552</v>
+        <v>6872544</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4974,11 +4957,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5005,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125072658</v>
+        <v>125075505</v>
       </c>
       <c r="B44" t="n">
-        <v>78546</v>
+        <v>78592</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5021,37 +4999,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473760</v>
+        <v>473523</v>
       </c>
       <c r="R44" t="n">
-        <v>6872467</v>
+        <v>6872722</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5107,10 +5085,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125075883</v>
+        <v>125074811</v>
       </c>
       <c r="B45" t="n">
-        <v>78455</v>
+        <v>78947</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5123,21 +5101,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5147,10 +5125,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473613</v>
+        <v>473732</v>
       </c>
       <c r="R45" t="n">
-        <v>6872761</v>
+        <v>6872579</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5209,10 +5187,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125073430</v>
+        <v>125073530</v>
       </c>
       <c r="B46" t="n">
-        <v>57666</v>
+        <v>98269</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5221,41 +5199,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473712</v>
+        <v>473728</v>
       </c>
       <c r="R46" t="n">
-        <v>6872523</v>
+        <v>6872500</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5285,11 +5272,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5316,10 +5298,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125074731</v>
+        <v>125076393</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5328,47 +5310,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473769</v>
+        <v>473731</v>
       </c>
       <c r="R47" t="n">
-        <v>6872532</v>
+        <v>6872691</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5401,6 +5374,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5427,10 +5405,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125073267</v>
+        <v>125074047</v>
       </c>
       <c r="B48" t="n">
-        <v>79920</v>
+        <v>78592</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5439,25 +5417,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5467,10 +5445,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473732</v>
+        <v>473665</v>
       </c>
       <c r="R48" t="n">
-        <v>6872498</v>
+        <v>6872487</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5529,10 +5507,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125074811</v>
+        <v>125073578</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>98290</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5541,41 +5519,50 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473732</v>
+        <v>473736</v>
       </c>
       <c r="R49" t="n">
-        <v>6872579</v>
+        <v>6872499</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5631,10 +5618,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125074741</v>
+        <v>125073936</v>
       </c>
       <c r="B50" t="n">
-        <v>79892</v>
+        <v>79536</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5647,34 +5634,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473756</v>
+        <v>473695</v>
       </c>
       <c r="R50" t="n">
-        <v>6872526</v>
+        <v>6872466</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5733,10 +5720,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125074664</v>
+        <v>125075491</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>79565</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5745,50 +5732,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473761</v>
+        <v>473523</v>
       </c>
       <c r="R51" t="n">
-        <v>6872503</v>
+        <v>6872722</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5844,10 +5822,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125074232</v>
+        <v>125076033</v>
       </c>
       <c r="B52" t="n">
-        <v>78547</v>
+        <v>57635</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5860,34 +5838,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473700</v>
+        <v>473693</v>
       </c>
       <c r="R52" t="n">
-        <v>6872562</v>
+        <v>6872740</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5920,6 +5898,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5946,10 +5929,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125075295</v>
+        <v>125073267</v>
       </c>
       <c r="B53" t="n">
-        <v>78547</v>
+        <v>80057</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5958,38 +5941,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473553</v>
+        <v>473732</v>
       </c>
       <c r="R53" t="n">
-        <v>6872662</v>
+        <v>6872498</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6048,10 +6031,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125072596</v>
+        <v>125072827</v>
       </c>
       <c r="B54" t="n">
-        <v>78546</v>
+        <v>78683</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6088,10 +6071,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473742</v>
+        <v>473758</v>
       </c>
       <c r="R54" t="n">
-        <v>6872438</v>
+        <v>6872471</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6150,10 +6133,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125074165</v>
+        <v>125072602</v>
       </c>
       <c r="B55" t="n">
-        <v>78455</v>
+        <v>78684</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6166,21 +6149,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6190,10 +6173,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473690</v>
+        <v>473742</v>
       </c>
       <c r="R55" t="n">
-        <v>6872539</v>
+        <v>6872438</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6252,10 +6235,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125074681</v>
+        <v>125072978</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>80029</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6264,47 +6247,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473765</v>
+        <v>473749</v>
       </c>
       <c r="R56" t="n">
-        <v>6872521</v>
+        <v>6872487</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6363,10 +6337,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125073338</v>
+        <v>125073474</v>
       </c>
       <c r="B57" t="n">
-        <v>79399</v>
+        <v>98269</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6375,41 +6349,50 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473722</v>
+        <v>473716</v>
       </c>
       <c r="R57" t="n">
-        <v>6872521</v>
+        <v>6872520</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6465,10 +6448,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125073052</v>
+        <v>125073146</v>
       </c>
       <c r="B58" t="n">
-        <v>79920</v>
+        <v>98269</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6477,28 +6460,37 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
@@ -6508,7 +6500,7 @@
         <v>473748</v>
       </c>
       <c r="R58" t="n">
-        <v>6872489</v>
+        <v>6872493</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6567,10 +6559,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125072916</v>
+        <v>125072658</v>
       </c>
       <c r="B59" t="n">
-        <v>79927</v>
+        <v>78683</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6579,25 +6571,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6607,10 +6599,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473748</v>
+        <v>473760</v>
       </c>
       <c r="R59" t="n">
-        <v>6872490</v>
+        <v>6872467</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6669,10 +6661,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125075258</v>
+        <v>125073107</v>
       </c>
       <c r="B60" t="n">
-        <v>78455</v>
+        <v>78979</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6685,34 +6677,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473585</v>
+        <v>473750</v>
       </c>
       <c r="R60" t="n">
-        <v>6872639</v>
+        <v>6872492</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6771,10 +6763,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125073255</v>
+        <v>125073833</v>
       </c>
       <c r="B61" t="n">
-        <v>79892</v>
+        <v>78592</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6787,21 +6779,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6811,10 +6803,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473735</v>
+        <v>473697</v>
       </c>
       <c r="R61" t="n">
-        <v>6872503</v>
+        <v>6872466</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6873,10 +6865,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125076393</v>
+        <v>125073338</v>
       </c>
       <c r="B62" t="n">
-        <v>57513</v>
+        <v>79536</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6889,37 +6881,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>473731</v>
+        <v>473722</v>
       </c>
       <c r="R62" t="n">
-        <v>6872691</v>
+        <v>6872521</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6949,11 +6941,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6980,10 +6967,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125076033</v>
+        <v>125074232</v>
       </c>
       <c r="B63" t="n">
-        <v>57513</v>
+        <v>78684</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6996,34 +6983,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>473693</v>
+        <v>473700</v>
       </c>
       <c r="R63" t="n">
-        <v>6872740</v>
+        <v>6872562</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7056,11 +7043,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7087,10 +7069,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125074134</v>
+        <v>125074664</v>
       </c>
       <c r="B64" t="n">
-        <v>78455</v>
+        <v>98269</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7099,41 +7081,50 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>473684</v>
+        <v>473761</v>
       </c>
       <c r="R64" t="n">
-        <v>6872544</v>
+        <v>6872503</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7189,10 +7180,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125075491</v>
+        <v>125075883</v>
       </c>
       <c r="B65" t="n">
-        <v>79428</v>
+        <v>78592</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7205,21 +7196,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7229,13 +7220,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473523</v>
+        <v>473613</v>
       </c>
       <c r="R65" t="n">
-        <v>6872722</v>
+        <v>6872761</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7291,10 +7282,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125072999</v>
+        <v>125076500</v>
       </c>
       <c r="B66" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7327,14 +7318,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>473747</v>
+        <v>473798</v>
       </c>
       <c r="R66" t="n">
-        <v>6872493</v>
+        <v>6872597</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7393,10 +7384,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125073107</v>
+        <v>125074731</v>
       </c>
       <c r="B67" t="n">
-        <v>78842</v>
+        <v>98269</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7405,41 +7396,50 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>473750</v>
+        <v>473769</v>
       </c>
       <c r="R67" t="n">
-        <v>6872492</v>
+        <v>6872532</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7495,10 +7495,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125074047</v>
+        <v>125075336</v>
       </c>
       <c r="B68" t="n">
-        <v>78455</v>
+        <v>78684</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7511,37 +7511,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>473665</v>
+        <v>473532</v>
       </c>
       <c r="R68" t="n">
-        <v>6872487</v>
+        <v>6872688</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124828791</v>
+        <v>124826941</v>
       </c>
       <c r="B19" t="n">
-        <v>78331</v>
+        <v>78684</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473589</v>
+        <v>473804</v>
       </c>
       <c r="R19" t="n">
-        <v>6872813</v>
+        <v>6872761</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124826941</v>
+        <v>124828791</v>
       </c>
       <c r="B20" t="n">
-        <v>78684</v>
+        <v>78331</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473804</v>
+        <v>473589</v>
       </c>
       <c r="R20" t="n">
-        <v>6872761</v>
+        <v>6872813</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124827497</v>
+        <v>124827491</v>
       </c>
       <c r="B21" t="n">
-        <v>79536</v>
+        <v>77874</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124827491</v>
+        <v>124827497</v>
       </c>
       <c r="B22" t="n">
-        <v>77874</v>
+        <v>79536</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125075710</v>
+        <v>125075258</v>
       </c>
       <c r="B24" t="n">
-        <v>79565</v>
+        <v>78592</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,13 +2964,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473570</v>
+        <v>473585</v>
       </c>
       <c r="R24" t="n">
-        <v>6872751</v>
+        <v>6872639</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125075258</v>
+        <v>125075630</v>
       </c>
       <c r="B25" t="n">
-        <v>78592</v>
+        <v>79536</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473585</v>
+        <v>473566</v>
       </c>
       <c r="R25" t="n">
-        <v>6872639</v>
+        <v>6872757</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125075630</v>
+        <v>125075710</v>
       </c>
       <c r="B26" t="n">
-        <v>79536</v>
+        <v>79565</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,13 +3168,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473566</v>
+        <v>473570</v>
       </c>
       <c r="R26" t="n">
-        <v>6872757</v>
+        <v>6872751</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -5507,10 +5507,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125073578</v>
+        <v>125075491</v>
       </c>
       <c r="B49" t="n">
-        <v>98290</v>
+        <v>79565</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5519,47 +5519,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473736</v>
+        <v>473523</v>
       </c>
       <c r="R49" t="n">
-        <v>6872499</v>
+        <v>6872722</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5618,10 +5609,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125073936</v>
+        <v>125073578</v>
       </c>
       <c r="B50" t="n">
-        <v>79536</v>
+        <v>98290</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5630,41 +5621,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473695</v>
+        <v>473736</v>
       </c>
       <c r="R50" t="n">
-        <v>6872466</v>
+        <v>6872499</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5720,10 +5720,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125075491</v>
+        <v>125073936</v>
       </c>
       <c r="B51" t="n">
-        <v>79565</v>
+        <v>79536</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5736,37 +5736,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473523</v>
+        <v>473695</v>
       </c>
       <c r="R51" t="n">
-        <v>6872722</v>
+        <v>6872466</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6559,10 +6559,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125072658</v>
+        <v>125073107</v>
       </c>
       <c r="B59" t="n">
-        <v>78683</v>
+        <v>78979</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6575,21 +6575,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6599,13 +6599,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473760</v>
+        <v>473750</v>
       </c>
       <c r="R59" t="n">
-        <v>6872467</v>
+        <v>6872492</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6661,10 +6661,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125073107</v>
+        <v>125072658</v>
       </c>
       <c r="B60" t="n">
-        <v>78979</v>
+        <v>78683</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6677,21 +6677,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6701,13 +6701,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473750</v>
+        <v>473760</v>
       </c>
       <c r="R60" t="n">
-        <v>6872492</v>
+        <v>6872467</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6763,10 +6763,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125073833</v>
+        <v>125073338</v>
       </c>
       <c r="B61" t="n">
-        <v>78592</v>
+        <v>79536</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6779,21 +6779,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6803,13 +6803,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473697</v>
+        <v>473722</v>
       </c>
       <c r="R61" t="n">
-        <v>6872466</v>
+        <v>6872521</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6865,10 +6865,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125073338</v>
+        <v>125074232</v>
       </c>
       <c r="B62" t="n">
-        <v>79536</v>
+        <v>78684</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6905,13 +6905,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>473722</v>
+        <v>473700</v>
       </c>
       <c r="R62" t="n">
-        <v>6872521</v>
+        <v>6872562</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6967,10 +6967,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125074232</v>
+        <v>125073833</v>
       </c>
       <c r="B63" t="n">
-        <v>78684</v>
+        <v>78592</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6983,21 +6983,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>473700</v>
+        <v>473697</v>
       </c>
       <c r="R63" t="n">
-        <v>6872562</v>
+        <v>6872466</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124829793</v>
+        <v>124827748</v>
       </c>
       <c r="B9" t="n">
-        <v>80064</v>
+        <v>78684</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473654</v>
+        <v>473754</v>
       </c>
       <c r="R9" t="n">
-        <v>6872997</v>
+        <v>6872803</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124826736</v>
+        <v>124827627</v>
       </c>
       <c r="B11" t="n">
         <v>78684</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473821</v>
+        <v>473780</v>
       </c>
       <c r="R11" t="n">
-        <v>6872738</v>
+        <v>6872856</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124829811</v>
+        <v>124827497</v>
       </c>
       <c r="B12" t="n">
-        <v>80063</v>
+        <v>79536</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473654</v>
+        <v>473801</v>
       </c>
       <c r="R12" t="n">
-        <v>6872997</v>
+        <v>6872850</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124827748</v>
+        <v>124829811</v>
       </c>
       <c r="B13" t="n">
-        <v>78684</v>
+        <v>80063</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473754</v>
+        <v>473654</v>
       </c>
       <c r="R13" t="n">
-        <v>6872803</v>
+        <v>6872997</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124828799</v>
+        <v>124827660</v>
       </c>
       <c r="B14" t="n">
-        <v>77874</v>
+        <v>78592</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473591</v>
+        <v>473782</v>
       </c>
       <c r="R14" t="n">
         <v>6872817</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124828245</v>
+        <v>124826736</v>
       </c>
       <c r="B15" t="n">
-        <v>78683</v>
+        <v>78684</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473687</v>
+        <v>473821</v>
       </c>
       <c r="R15" t="n">
-        <v>6872750</v>
+        <v>6872738</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124827627</v>
+        <v>124829793</v>
       </c>
       <c r="B16" t="n">
-        <v>78684</v>
+        <v>80064</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473780</v>
+        <v>473654</v>
       </c>
       <c r="R16" t="n">
-        <v>6872856</v>
+        <v>6872997</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,7 +2210,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124828676</v>
+        <v>124826941</v>
       </c>
       <c r="B17" t="n">
         <v>78684</v>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473614</v>
+        <v>473804</v>
       </c>
       <c r="R17" t="n">
-        <v>6872815</v>
+        <v>6872761</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124827660</v>
+        <v>124828245</v>
       </c>
       <c r="B18" t="n">
-        <v>78592</v>
+        <v>78683</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,13 +2352,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473782</v>
+        <v>473687</v>
       </c>
       <c r="R18" t="n">
-        <v>6872817</v>
+        <v>6872750</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124826941</v>
+        <v>124828081</v>
       </c>
       <c r="B19" t="n">
-        <v>78684</v>
+        <v>79536</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473804</v>
+        <v>473705</v>
       </c>
       <c r="R19" t="n">
-        <v>6872761</v>
+        <v>6872721</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124828791</v>
+        <v>124828676</v>
       </c>
       <c r="B20" t="n">
-        <v>78331</v>
+        <v>78684</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473589</v>
+        <v>473614</v>
       </c>
       <c r="R20" t="n">
-        <v>6872813</v>
+        <v>6872815</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124827491</v>
+        <v>124828791</v>
       </c>
       <c r="B21" t="n">
-        <v>77874</v>
+        <v>78331</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473801</v>
+        <v>473589</v>
       </c>
       <c r="R21" t="n">
-        <v>6872850</v>
+        <v>6872813</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124827497</v>
+        <v>124827491</v>
       </c>
       <c r="B22" t="n">
-        <v>79536</v>
+        <v>77874</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124828081</v>
+        <v>124828799</v>
       </c>
       <c r="B23" t="n">
-        <v>79536</v>
+        <v>77874</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473705</v>
+        <v>473591</v>
       </c>
       <c r="R23" t="n">
-        <v>6872721</v>
+        <v>6872817</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125075258</v>
+        <v>125075336</v>
       </c>
       <c r="B24" t="n">
-        <v>78592</v>
+        <v>78684</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,13 +2964,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473585</v>
+        <v>473532</v>
       </c>
       <c r="R24" t="n">
-        <v>6872639</v>
+        <v>6872688</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125075630</v>
+        <v>125075491</v>
       </c>
       <c r="B25" t="n">
-        <v>79536</v>
+        <v>79565</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473566</v>
+        <v>473523</v>
       </c>
       <c r="R25" t="n">
-        <v>6872757</v>
+        <v>6872722</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125073052</v>
+        <v>125073578</v>
       </c>
       <c r="B27" t="n">
-        <v>80057</v>
+        <v>98290</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,37 +3246,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473748</v>
+        <v>473736</v>
       </c>
       <c r="R27" t="n">
-        <v>6872489</v>
+        <v>6872499</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3332,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125075349</v>
+        <v>125073474</v>
       </c>
       <c r="B28" t="n">
-        <v>78683</v>
+        <v>98269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,38 +3353,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473530</v>
+        <v>473716</v>
       </c>
       <c r="R28" t="n">
-        <v>6872681</v>
+        <v>6872520</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3434,10 +3452,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125072999</v>
+        <v>125073455</v>
       </c>
       <c r="B29" t="n">
-        <v>80028</v>
+        <v>79536</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,21 +3468,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3474,10 +3492,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473747</v>
+        <v>473712</v>
       </c>
       <c r="R29" t="n">
-        <v>6872493</v>
+        <v>6872517</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,10 +3554,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125072916</v>
+        <v>125074741</v>
       </c>
       <c r="B30" t="n">
-        <v>80064</v>
+        <v>80029</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3548,38 +3566,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473748</v>
+        <v>473756</v>
       </c>
       <c r="R30" t="n">
-        <v>6872490</v>
+        <v>6872526</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,10 +3656,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125071546</v>
+        <v>125074047</v>
       </c>
       <c r="B31" t="n">
-        <v>56836</v>
+        <v>78592</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3650,25 +3668,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3678,13 +3696,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473832</v>
+        <v>473665</v>
       </c>
       <c r="R31" t="n">
-        <v>6872552</v>
+        <v>6872487</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3714,11 +3732,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3745,10 +3758,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125072596</v>
+        <v>125073107</v>
       </c>
       <c r="B32" t="n">
-        <v>78683</v>
+        <v>78979</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3761,21 +3774,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,13 +3798,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473742</v>
+        <v>473750</v>
       </c>
       <c r="R32" t="n">
-        <v>6872438</v>
+        <v>6872492</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3847,10 +3860,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125073455</v>
+        <v>125074165</v>
       </c>
       <c r="B33" t="n">
-        <v>79536</v>
+        <v>78592</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3863,21 +3876,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3887,10 +3900,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473712</v>
+        <v>473690</v>
       </c>
       <c r="R33" t="n">
-        <v>6872517</v>
+        <v>6872539</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,10 +3962,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125074165</v>
+        <v>125072827</v>
       </c>
       <c r="B34" t="n">
-        <v>78592</v>
+        <v>78683</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3965,21 +3978,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3989,10 +4002,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473690</v>
+        <v>473758</v>
       </c>
       <c r="R34" t="n">
-        <v>6872539</v>
+        <v>6872471</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4051,7 +4064,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125074681</v>
+        <v>125074664</v>
       </c>
       <c r="B35" t="n">
         <v>98269</v>
@@ -4086,7 +4099,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4100,10 +4113,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473765</v>
+        <v>473761</v>
       </c>
       <c r="R35" t="n">
-        <v>6872521</v>
+        <v>6872503</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4162,10 +4175,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125073255</v>
+        <v>125075630</v>
       </c>
       <c r="B36" t="n">
-        <v>80029</v>
+        <v>79536</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4178,37 +4191,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473735</v>
+        <v>473566</v>
       </c>
       <c r="R36" t="n">
-        <v>6872503</v>
+        <v>6872757</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4264,10 +4277,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125075295</v>
+        <v>125072999</v>
       </c>
       <c r="B37" t="n">
-        <v>78684</v>
+        <v>80028</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4280,37 +4293,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473553</v>
+        <v>473747</v>
       </c>
       <c r="R37" t="n">
-        <v>6872662</v>
+        <v>6872493</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4366,10 +4379,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125075154</v>
+        <v>125073430</v>
       </c>
       <c r="B38" t="n">
-        <v>78592</v>
+        <v>57793</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4382,37 +4395,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473625</v>
+        <v>473712</v>
       </c>
       <c r="R38" t="n">
-        <v>6872585</v>
+        <v>6872523</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4442,6 +4455,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4468,10 +4486,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125074741</v>
+        <v>125073530</v>
       </c>
       <c r="B39" t="n">
-        <v>80029</v>
+        <v>98269</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4480,38 +4498,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473756</v>
+        <v>473728</v>
       </c>
       <c r="R39" t="n">
-        <v>6872526</v>
+        <v>6872500</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4570,10 +4597,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125075202</v>
+        <v>125075349</v>
       </c>
       <c r="B40" t="n">
-        <v>78592</v>
+        <v>78683</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4586,21 +4613,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4610,13 +4637,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473594</v>
+        <v>473530</v>
       </c>
       <c r="R40" t="n">
-        <v>6872603</v>
+        <v>6872681</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4672,7 +4699,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125074134</v>
+        <v>125075883</v>
       </c>
       <c r="B41" t="n">
         <v>78592</v>
@@ -4708,17 +4735,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473684</v>
+        <v>473613</v>
       </c>
       <c r="R41" t="n">
-        <v>6872544</v>
+        <v>6872761</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4774,10 +4801,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125073430</v>
+        <v>125074232</v>
       </c>
       <c r="B42" t="n">
-        <v>57793</v>
+        <v>78684</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4790,21 +4817,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4814,13 +4841,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473712</v>
+        <v>473700</v>
       </c>
       <c r="R42" t="n">
-        <v>6872523</v>
+        <v>6872562</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4850,11 +4877,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4881,10 +4903,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125074318</v>
+        <v>125074681</v>
       </c>
       <c r="B43" t="n">
-        <v>78592</v>
+        <v>98269</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4893,41 +4915,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473722</v>
+        <v>473765</v>
       </c>
       <c r="R43" t="n">
-        <v>6872544</v>
+        <v>6872521</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4983,10 +5014,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125075505</v>
+        <v>125073267</v>
       </c>
       <c r="B44" t="n">
-        <v>78592</v>
+        <v>80057</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,38 +5026,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473523</v>
+        <v>473732</v>
       </c>
       <c r="R44" t="n">
-        <v>6872722</v>
+        <v>6872498</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5085,10 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125074811</v>
+        <v>125072658</v>
       </c>
       <c r="B45" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5101,34 +5132,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473732</v>
+        <v>473760</v>
       </c>
       <c r="R45" t="n">
-        <v>6872579</v>
+        <v>6872467</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5187,10 +5218,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125073530</v>
+        <v>125076500</v>
       </c>
       <c r="B46" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5199,47 +5230,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473728</v>
+        <v>473798</v>
       </c>
       <c r="R46" t="n">
-        <v>6872500</v>
+        <v>6872597</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5298,10 +5320,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125076393</v>
+        <v>125075505</v>
       </c>
       <c r="B47" t="n">
-        <v>57635</v>
+        <v>78592</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5314,21 +5336,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5338,13 +5360,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473731</v>
+        <v>473523</v>
       </c>
       <c r="R47" t="n">
-        <v>6872691</v>
+        <v>6872722</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5374,11 +5396,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5405,10 +5422,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125074047</v>
+        <v>125071546</v>
       </c>
       <c r="B48" t="n">
-        <v>78592</v>
+        <v>56836</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5417,25 +5434,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5445,13 +5462,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473665</v>
+        <v>473832</v>
       </c>
       <c r="R48" t="n">
-        <v>6872487</v>
+        <v>6872552</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5481,6 +5498,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5507,10 +5529,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125075491</v>
+        <v>125073052</v>
       </c>
       <c r="B49" t="n">
-        <v>79565</v>
+        <v>80057</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5519,41 +5541,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473523</v>
+        <v>473748</v>
       </c>
       <c r="R49" t="n">
-        <v>6872722</v>
+        <v>6872489</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5609,10 +5631,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125073578</v>
+        <v>125075154</v>
       </c>
       <c r="B50" t="n">
-        <v>98290</v>
+        <v>78592</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5621,50 +5643,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473736</v>
+        <v>473625</v>
       </c>
       <c r="R50" t="n">
-        <v>6872499</v>
+        <v>6872585</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5720,10 +5733,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125073936</v>
+        <v>125075202</v>
       </c>
       <c r="B51" t="n">
-        <v>79536</v>
+        <v>78592</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5736,37 +5749,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473695</v>
+        <v>473594</v>
       </c>
       <c r="R51" t="n">
-        <v>6872466</v>
+        <v>6872603</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5822,10 +5835,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125076033</v>
+        <v>125074134</v>
       </c>
       <c r="B52" t="n">
-        <v>57635</v>
+        <v>78592</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5838,37 +5851,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473693</v>
+        <v>473684</v>
       </c>
       <c r="R52" t="n">
-        <v>6872740</v>
+        <v>6872544</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5898,11 +5911,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5929,10 +5937,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125073267</v>
+        <v>125075295</v>
       </c>
       <c r="B53" t="n">
-        <v>80057</v>
+        <v>78684</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5941,38 +5949,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473732</v>
+        <v>473553</v>
       </c>
       <c r="R53" t="n">
-        <v>6872498</v>
+        <v>6872662</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6031,10 +6039,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125072827</v>
+        <v>125073833</v>
       </c>
       <c r="B54" t="n">
-        <v>78683</v>
+        <v>78592</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6047,21 +6055,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6071,10 +6079,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473758</v>
+        <v>473697</v>
       </c>
       <c r="R54" t="n">
-        <v>6872471</v>
+        <v>6872466</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6133,10 +6141,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125072602</v>
+        <v>125074811</v>
       </c>
       <c r="B55" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6149,34 +6157,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473742</v>
+        <v>473732</v>
       </c>
       <c r="R55" t="n">
-        <v>6872438</v>
+        <v>6872579</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6235,10 +6243,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125072978</v>
+        <v>125074318</v>
       </c>
       <c r="B56" t="n">
-        <v>80029</v>
+        <v>78592</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6251,37 +6259,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473749</v>
+        <v>473722</v>
       </c>
       <c r="R56" t="n">
-        <v>6872487</v>
+        <v>6872544</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6337,10 +6345,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125073474</v>
+        <v>125073338</v>
       </c>
       <c r="B57" t="n">
-        <v>98269</v>
+        <v>79536</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6349,50 +6357,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473716</v>
+        <v>473722</v>
       </c>
       <c r="R57" t="n">
-        <v>6872520</v>
+        <v>6872521</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6448,10 +6447,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125073146</v>
+        <v>125073936</v>
       </c>
       <c r="B58" t="n">
-        <v>98269</v>
+        <v>79536</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6460,47 +6459,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>473748</v>
+        <v>473695</v>
       </c>
       <c r="R58" t="n">
-        <v>6872493</v>
+        <v>6872466</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6559,10 +6549,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125073107</v>
+        <v>125072602</v>
       </c>
       <c r="B59" t="n">
-        <v>78979</v>
+        <v>78684</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6575,21 +6565,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6599,13 +6589,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473750</v>
+        <v>473742</v>
       </c>
       <c r="R59" t="n">
-        <v>6872492</v>
+        <v>6872438</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6661,10 +6651,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125072658</v>
+        <v>125073146</v>
       </c>
       <c r="B60" t="n">
-        <v>78683</v>
+        <v>98269</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6673,38 +6663,47 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473760</v>
+        <v>473748</v>
       </c>
       <c r="R60" t="n">
-        <v>6872467</v>
+        <v>6872493</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6763,10 +6762,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125073338</v>
+        <v>125072596</v>
       </c>
       <c r="B61" t="n">
-        <v>79536</v>
+        <v>78683</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6779,21 +6778,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6803,13 +6802,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473722</v>
+        <v>473742</v>
       </c>
       <c r="R61" t="n">
-        <v>6872521</v>
+        <v>6872438</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6865,10 +6864,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125074232</v>
+        <v>125072978</v>
       </c>
       <c r="B62" t="n">
-        <v>78684</v>
+        <v>80029</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6881,21 +6880,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6905,10 +6904,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>473700</v>
+        <v>473749</v>
       </c>
       <c r="R62" t="n">
-        <v>6872562</v>
+        <v>6872487</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6967,10 +6966,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125073833</v>
+        <v>125073255</v>
       </c>
       <c r="B63" t="n">
-        <v>78592</v>
+        <v>80029</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6983,21 +6982,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7007,10 +7006,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>473697</v>
+        <v>473735</v>
       </c>
       <c r="R63" t="n">
-        <v>6872466</v>
+        <v>6872503</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7069,10 +7068,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125074664</v>
+        <v>125072916</v>
       </c>
       <c r="B64" t="n">
-        <v>98269</v>
+        <v>80064</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7081,47 +7080,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>473761</v>
+        <v>473748</v>
       </c>
       <c r="R64" t="n">
-        <v>6872503</v>
+        <v>6872490</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7180,10 +7170,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125075883</v>
+        <v>125074731</v>
       </c>
       <c r="B65" t="n">
-        <v>78592</v>
+        <v>98269</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7192,38 +7182,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473613</v>
+        <v>473769</v>
       </c>
       <c r="R65" t="n">
-        <v>6872761</v>
+        <v>6872532</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7282,10 +7281,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125076500</v>
+        <v>125075258</v>
       </c>
       <c r="B66" t="n">
-        <v>80028</v>
+        <v>78592</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7298,21 +7297,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7322,13 +7321,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>473798</v>
+        <v>473585</v>
       </c>
       <c r="R66" t="n">
-        <v>6872597</v>
+        <v>6872639</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7384,10 +7383,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125074731</v>
+        <v>125076033</v>
       </c>
       <c r="B67" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7396,47 +7395,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>473769</v>
+        <v>473693</v>
       </c>
       <c r="R67" t="n">
-        <v>6872532</v>
+        <v>6872740</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7469,6 +7459,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7495,10 +7490,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125075336</v>
+        <v>125076393</v>
       </c>
       <c r="B68" t="n">
-        <v>78684</v>
+        <v>57635</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7511,21 +7506,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7535,10 +7530,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>473532</v>
+        <v>473731</v>
       </c>
       <c r="R68" t="n">
-        <v>6872688</v>
+        <v>6872691</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7571,6 +7566,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124828707</v>
+        <v>124827627</v>
       </c>
       <c r="B10" t="n">
-        <v>78683</v>
+        <v>78684</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473614</v>
+        <v>473780</v>
       </c>
       <c r="R10" t="n">
-        <v>6872815</v>
+        <v>6872856</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124827627</v>
+        <v>124828707</v>
       </c>
       <c r="B11" t="n">
-        <v>78684</v>
+        <v>78683</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473780</v>
+        <v>473614</v>
       </c>
       <c r="R11" t="n">
-        <v>6872856</v>
+        <v>6872815</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -4175,10 +4175,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125075630</v>
+        <v>125073530</v>
       </c>
       <c r="B36" t="n">
-        <v>79536</v>
+        <v>98269</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4187,41 +4187,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473566</v>
+        <v>473728</v>
       </c>
       <c r="R36" t="n">
-        <v>6872757</v>
+        <v>6872500</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4379,10 +4388,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125073430</v>
+        <v>125075630</v>
       </c>
       <c r="B38" t="n">
-        <v>57793</v>
+        <v>79536</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4395,34 +4404,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473712</v>
+        <v>473566</v>
       </c>
       <c r="R38" t="n">
-        <v>6872523</v>
+        <v>6872757</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4455,11 +4464,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4486,10 +4490,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125073530</v>
+        <v>125073430</v>
       </c>
       <c r="B39" t="n">
-        <v>98269</v>
+        <v>57793</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4498,50 +4502,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473728</v>
+        <v>473712</v>
       </c>
       <c r="R39" t="n">
-        <v>6872500</v>
+        <v>6872523</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4571,6 +4566,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4597,10 +4597,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125075349</v>
+        <v>125075883</v>
       </c>
       <c r="B40" t="n">
-        <v>78683</v>
+        <v>78592</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473530</v>
+        <v>473613</v>
       </c>
       <c r="R40" t="n">
-        <v>6872681</v>
+        <v>6872761</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125075883</v>
+        <v>125074232</v>
       </c>
       <c r="B41" t="n">
-        <v>78592</v>
+        <v>78684</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4715,34 +4715,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473613</v>
+        <v>473700</v>
       </c>
       <c r="R41" t="n">
-        <v>6872761</v>
+        <v>6872562</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4801,10 +4801,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125074232</v>
+        <v>125075349</v>
       </c>
       <c r="B42" t="n">
-        <v>78684</v>
+        <v>78683</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4817,34 +4817,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473700</v>
+        <v>473530</v>
       </c>
       <c r="R42" t="n">
-        <v>6872562</v>
+        <v>6872681</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -4597,10 +4597,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125075883</v>
+        <v>125075349</v>
       </c>
       <c r="B40" t="n">
-        <v>78592</v>
+        <v>78683</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473613</v>
+        <v>473530</v>
       </c>
       <c r="R40" t="n">
-        <v>6872761</v>
+        <v>6872681</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125074232</v>
+        <v>125075883</v>
       </c>
       <c r="B41" t="n">
-        <v>78684</v>
+        <v>78592</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4715,34 +4715,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473700</v>
+        <v>473613</v>
       </c>
       <c r="R41" t="n">
-        <v>6872562</v>
+        <v>6872761</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4801,10 +4801,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125075349</v>
+        <v>125074232</v>
       </c>
       <c r="B42" t="n">
-        <v>78683</v>
+        <v>78684</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4817,34 +4817,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473530</v>
+        <v>473700</v>
       </c>
       <c r="R42" t="n">
-        <v>6872681</v>
+        <v>6872562</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4903,10 +4903,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125074681</v>
+        <v>125073267</v>
       </c>
       <c r="B43" t="n">
-        <v>98269</v>
+        <v>80057</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4915,50 +4915,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473765</v>
+        <v>473732</v>
       </c>
       <c r="R43" t="n">
-        <v>6872521</v>
+        <v>6872498</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5014,10 +5005,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125073267</v>
+        <v>125072658</v>
       </c>
       <c r="B44" t="n">
-        <v>80057</v>
+        <v>78683</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5026,25 +5017,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5054,13 +5045,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473732</v>
+        <v>473760</v>
       </c>
       <c r="R44" t="n">
-        <v>6872498</v>
+        <v>6872467</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5116,10 +5107,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125072658</v>
+        <v>125074681</v>
       </c>
       <c r="B45" t="n">
-        <v>78683</v>
+        <v>98269</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5128,38 +5119,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473760</v>
+        <v>473765</v>
       </c>
       <c r="R45" t="n">
-        <v>6872467</v>
+        <v>6872521</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6549,10 +6549,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125072602</v>
+        <v>125072596</v>
       </c>
       <c r="B59" t="n">
-        <v>78684</v>
+        <v>78683</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6565,21 +6565,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6651,10 +6651,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125073146</v>
+        <v>125072602</v>
       </c>
       <c r="B60" t="n">
-        <v>98269</v>
+        <v>78684</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6663,47 +6663,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473748</v>
+        <v>473742</v>
       </c>
       <c r="R60" t="n">
-        <v>6872493</v>
+        <v>6872438</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6762,10 +6753,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125072596</v>
+        <v>125073146</v>
       </c>
       <c r="B61" t="n">
-        <v>78683</v>
+        <v>98269</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6774,38 +6765,47 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473742</v>
+        <v>473748</v>
       </c>
       <c r="R61" t="n">
-        <v>6872438</v>
+        <v>6872493</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7281,10 +7281,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125075258</v>
+        <v>125076033</v>
       </c>
       <c r="B66" t="n">
-        <v>78592</v>
+        <v>57635</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7297,21 +7297,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7321,13 +7321,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>473585</v>
+        <v>473693</v>
       </c>
       <c r="R66" t="n">
-        <v>6872639</v>
+        <v>6872740</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7357,6 +7357,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7383,7 +7388,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125076033</v>
+        <v>125076393</v>
       </c>
       <c r="B67" t="n">
         <v>57635</v>
@@ -7423,10 +7428,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>473693</v>
+        <v>473731</v>
       </c>
       <c r="R67" t="n">
-        <v>6872740</v>
+        <v>6872691</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7490,10 +7495,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125076393</v>
+        <v>125075258</v>
       </c>
       <c r="B68" t="n">
-        <v>57635</v>
+        <v>78592</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7506,21 +7511,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7530,13 +7535,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>473731</v>
+        <v>473585</v>
       </c>
       <c r="R68" t="n">
-        <v>6872691</v>
+        <v>6872639</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7566,11 +7571,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -1394,15 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124827748</v>
+        <v>124828791</v>
       </c>
       <c r="B9" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473754</v>
+        <v>473589</v>
       </c>
       <c r="R9" t="n">
-        <v>6872803</v>
+        <v>6872813</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,16 +1491,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124827627</v>
+        <v>124826941</v>
       </c>
       <c r="B10" t="n">
         <v>78684</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1536,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473780</v>
+        <v>473804</v>
       </c>
       <c r="R10" t="n">
-        <v>6872856</v>
+        <v>6872761</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,15 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124828707</v>
+        <v>124827660</v>
       </c>
       <c r="B11" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1599,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,13 +1623,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473614</v>
+        <v>473782</v>
       </c>
       <c r="R11" t="n">
-        <v>6872815</v>
+        <v>6872817</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,37 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124827497</v>
+        <v>124829793</v>
       </c>
       <c r="B12" t="n">
-        <v>79536</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,13 +1720,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473801</v>
+        <v>473654</v>
       </c>
       <c r="R12" t="n">
-        <v>6872850</v>
+        <v>6872997</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1802,37 +1782,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124829811</v>
+        <v>124828676</v>
       </c>
       <c r="B13" t="n">
-        <v>80063</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78684</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473654</v>
+        <v>473614</v>
       </c>
       <c r="R13" t="n">
-        <v>6872997</v>
+        <v>6872815</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,15 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124827660</v>
+        <v>124828245</v>
       </c>
       <c r="B14" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78683</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,13 +1914,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473782</v>
+        <v>473687</v>
       </c>
       <c r="R14" t="n">
-        <v>6872817</v>
+        <v>6872750</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2006,37 +1976,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124826736</v>
+        <v>124829811</v>
       </c>
       <c r="B15" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80063</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473821</v>
+        <v>473654</v>
       </c>
       <c r="R15" t="n">
-        <v>6872738</v>
+        <v>6872997</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,37 +2073,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124829793</v>
+        <v>124826736</v>
       </c>
       <c r="B16" t="n">
-        <v>80064</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78684</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473654</v>
+        <v>473821</v>
       </c>
       <c r="R16" t="n">
-        <v>6872997</v>
+        <v>6872738</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,15 +2170,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124826941</v>
+        <v>124827491</v>
       </c>
       <c r="B17" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77874</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,21 +2181,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,13 +2205,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473804</v>
+        <v>473801</v>
       </c>
       <c r="R17" t="n">
-        <v>6872761</v>
+        <v>6872850</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2312,16 +2267,11 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124828245</v>
+        <v>124828707</v>
       </c>
       <c r="B18" t="n">
         <v>78683</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2352,10 +2302,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473687</v>
+        <v>473614</v>
       </c>
       <c r="R18" t="n">
-        <v>6872750</v>
+        <v>6872815</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2414,15 +2364,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124828081</v>
+        <v>124827627</v>
       </c>
       <c r="B19" t="n">
-        <v>79536</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78684</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,21 +2375,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2399,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473705</v>
+        <v>473780</v>
       </c>
       <c r="R19" t="n">
-        <v>6872721</v>
+        <v>6872856</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,15 +2461,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124828676</v>
+        <v>124827497</v>
       </c>
       <c r="B20" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79536</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2532,21 +2472,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,13 +2496,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473614</v>
+        <v>473801</v>
       </c>
       <c r="R20" t="n">
-        <v>6872815</v>
+        <v>6872850</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2618,15 +2558,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124828791</v>
+        <v>124828799</v>
       </c>
       <c r="B21" t="n">
-        <v>78331</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77874</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2634,21 +2569,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473589</v>
+        <v>473591</v>
       </c>
       <c r="R21" t="n">
-        <v>6872813</v>
+        <v>6872817</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2720,15 +2655,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124827491</v>
+        <v>124827748</v>
       </c>
       <c r="B22" t="n">
-        <v>77874</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78684</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2736,21 +2666,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2760,10 +2690,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473801</v>
+        <v>473754</v>
       </c>
       <c r="R22" t="n">
-        <v>6872850</v>
+        <v>6872803</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2822,15 +2752,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124828799</v>
+        <v>124828081</v>
       </c>
       <c r="B23" t="n">
-        <v>77874</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79536</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2838,21 +2763,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473591</v>
+        <v>473705</v>
       </c>
       <c r="R23" t="n">
-        <v>6872817</v>
+        <v>6872721</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2924,15 +2849,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125075336</v>
+        <v>125072602</v>
       </c>
       <c r="B24" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2960,14 +2880,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473532</v>
+        <v>473742</v>
       </c>
       <c r="R24" t="n">
-        <v>6872688</v>
+        <v>6872438</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,15 +2946,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125075491</v>
+        <v>125075258</v>
       </c>
       <c r="B25" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78634</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,21 +2957,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473523</v>
+        <v>473585</v>
       </c>
       <c r="R25" t="n">
-        <v>6872722</v>
+        <v>6872639</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3128,15 +3043,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125075710</v>
+        <v>125076393</v>
       </c>
       <c r="B26" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3054,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3078,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473570</v>
+        <v>473731</v>
       </c>
       <c r="R26" t="n">
-        <v>6872751</v>
+        <v>6872691</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3204,6 +3114,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3230,62 +3145,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125073578</v>
+        <v>125075336</v>
       </c>
       <c r="B27" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473736</v>
+        <v>473532</v>
       </c>
       <c r="R27" t="n">
-        <v>6872499</v>
+        <v>6872688</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3341,59 +3242,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125073474</v>
+        <v>125074741</v>
       </c>
       <c r="B28" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80071</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473716</v>
+        <v>473756</v>
       </c>
       <c r="R28" t="n">
-        <v>6872520</v>
+        <v>6872526</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3452,15 +3339,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125073455</v>
+        <v>125073107</v>
       </c>
       <c r="B29" t="n">
-        <v>79536</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78999</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3468,21 +3350,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3492,13 +3374,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473712</v>
+        <v>473750</v>
       </c>
       <c r="R29" t="n">
-        <v>6872517</v>
+        <v>6872492</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3554,53 +3436,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125074741</v>
+        <v>125073267</v>
       </c>
       <c r="B30" t="n">
-        <v>80029</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473756</v>
+        <v>473732</v>
       </c>
       <c r="R30" t="n">
-        <v>6872526</v>
+        <v>6872498</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3656,53 +3533,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125074047</v>
+        <v>125073474</v>
       </c>
       <c r="B31" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473665</v>
+        <v>473716</v>
       </c>
       <c r="R31" t="n">
-        <v>6872487</v>
+        <v>6872520</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3758,50 +3639,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125073107</v>
+        <v>125073578</v>
       </c>
       <c r="B32" t="n">
-        <v>78979</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473750</v>
+        <v>473736</v>
       </c>
       <c r="R32" t="n">
-        <v>6872492</v>
+        <v>6872499</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3860,15 +3745,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125074165</v>
+        <v>125073833</v>
       </c>
       <c r="B33" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78634</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3900,10 +3780,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473690</v>
+        <v>473697</v>
       </c>
       <c r="R33" t="n">
-        <v>6872539</v>
+        <v>6872466</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3965,12 +3845,7 @@
         <v>125072827</v>
       </c>
       <c r="B34" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4064,62 +3939,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125074664</v>
+        <v>125074318</v>
       </c>
       <c r="B35" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78634</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473761</v>
+        <v>473722</v>
       </c>
       <c r="R35" t="n">
-        <v>6872503</v>
+        <v>6872544</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4175,59 +4036,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125073530</v>
+        <v>125075710</v>
       </c>
       <c r="B36" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473728</v>
+        <v>473570</v>
       </c>
       <c r="R36" t="n">
-        <v>6872500</v>
+        <v>6872751</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4286,15 +4133,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125072999</v>
+        <v>125073338</v>
       </c>
       <c r="B37" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79556</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4302,21 +4144,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4326,13 +4168,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473747</v>
+        <v>473722</v>
       </c>
       <c r="R37" t="n">
-        <v>6872493</v>
+        <v>6872521</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4388,15 +4230,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125075630</v>
+        <v>125075883</v>
       </c>
       <c r="B38" t="n">
-        <v>79536</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78634</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4404,21 +4241,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4428,13 +4265,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473566</v>
+        <v>473613</v>
       </c>
       <c r="R38" t="n">
-        <v>6872757</v>
+        <v>6872761</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4490,15 +4327,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125073430</v>
+        <v>125075202</v>
       </c>
       <c r="B39" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4506,34 +4338,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473712</v>
+        <v>473594</v>
       </c>
       <c r="R39" t="n">
-        <v>6872523</v>
+        <v>6872603</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4566,11 +4398,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4597,15 +4424,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125075349</v>
+        <v>125075505</v>
       </c>
       <c r="B40" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78634</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4613,21 +4435,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4637,13 +4459,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473530</v>
+        <v>473523</v>
       </c>
       <c r="R40" t="n">
-        <v>6872681</v>
+        <v>6872722</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4699,15 +4521,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125075883</v>
+        <v>125072978</v>
       </c>
       <c r="B41" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80071</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4715,34 +4532,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473613</v>
+        <v>473749</v>
       </c>
       <c r="R41" t="n">
-        <v>6872761</v>
+        <v>6872487</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4801,50 +4618,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125074232</v>
+        <v>125074731</v>
       </c>
       <c r="B42" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473700</v>
+        <v>473769</v>
       </c>
       <c r="R42" t="n">
-        <v>6872562</v>
+        <v>6872532</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4903,53 +4724,57 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125073267</v>
+        <v>125073530</v>
       </c>
       <c r="B43" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473732</v>
+        <v>473728</v>
       </c>
       <c r="R43" t="n">
-        <v>6872498</v>
+        <v>6872500</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5005,15 +4830,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125072658</v>
+        <v>125076500</v>
       </c>
       <c r="B44" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5021,34 +4841,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473760</v>
+        <v>473798</v>
       </c>
       <c r="R44" t="n">
-        <v>6872467</v>
+        <v>6872597</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5107,59 +4927,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125074681</v>
+        <v>125073255</v>
       </c>
       <c r="B45" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80071</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473765</v>
+        <v>473735</v>
       </c>
       <c r="R45" t="n">
-        <v>6872521</v>
+        <v>6872503</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,15 +5024,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125076500</v>
+        <v>125076033</v>
       </c>
       <c r="B46" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5234,21 +5035,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5258,10 +5059,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473798</v>
+        <v>473693</v>
       </c>
       <c r="R46" t="n">
-        <v>6872597</v>
+        <v>6872740</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5294,6 +5095,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5320,15 +5126,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125075505</v>
+        <v>125075630</v>
       </c>
       <c r="B47" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79556</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5336,21 +5137,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5360,10 +5161,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473523</v>
+        <v>473566</v>
       </c>
       <c r="R47" t="n">
-        <v>6872722</v>
+        <v>6872757</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5422,37 +5223,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125071546</v>
+        <v>125073430</v>
       </c>
       <c r="B48" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5462,13 +5258,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473832</v>
+        <v>473712</v>
       </c>
       <c r="R48" t="n">
-        <v>6872552</v>
+        <v>6872523</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5502,7 +5298,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Spillning under barrgles tall.</t>
+          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5529,15 +5325,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125073052</v>
+        <v>125072916</v>
       </c>
       <c r="B49" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80106</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,21 +5336,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5572,7 +5363,7 @@
         <v>473748</v>
       </c>
       <c r="R49" t="n">
-        <v>6872489</v>
+        <v>6872490</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5631,50 +5422,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125075154</v>
+        <v>125074681</v>
       </c>
       <c r="B50" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473625</v>
+        <v>473765</v>
       </c>
       <c r="R50" t="n">
-        <v>6872585</v>
+        <v>6872521</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5733,53 +5528,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125075202</v>
+        <v>125074664</v>
       </c>
       <c r="B51" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473594</v>
+        <v>473761</v>
       </c>
       <c r="R51" t="n">
-        <v>6872603</v>
+        <v>6872503</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5838,12 +5637,7 @@
         <v>125074134</v>
       </c>
       <c r="B52" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78634</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5937,53 +5731,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125075295</v>
+        <v>125071546</v>
       </c>
       <c r="B53" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473553</v>
+        <v>473832</v>
       </c>
       <c r="R53" t="n">
-        <v>6872662</v>
+        <v>6872552</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6013,6 +5802,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6039,15 +5833,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125073833</v>
+        <v>125073936</v>
       </c>
       <c r="B54" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79556</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6055,21 +5844,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6079,7 +5868,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473697</v>
+        <v>473695</v>
       </c>
       <c r="R54" t="n">
         <v>6872466</v>
@@ -6141,15 +5930,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125074811</v>
+        <v>125072658</v>
       </c>
       <c r="B55" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6157,34 +5941,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473732</v>
+        <v>473760</v>
       </c>
       <c r="R55" t="n">
-        <v>6872579</v>
+        <v>6872467</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6243,15 +6027,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125074318</v>
+        <v>125075349</v>
       </c>
       <c r="B56" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6259,21 +6038,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6283,13 +6062,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473722</v>
+        <v>473530</v>
       </c>
       <c r="R56" t="n">
-        <v>6872544</v>
+        <v>6872681</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6345,15 +6124,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125073338</v>
+        <v>125074047</v>
       </c>
       <c r="B57" t="n">
-        <v>79536</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78634</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6361,21 +6135,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6385,10 +6159,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473722</v>
+        <v>473665</v>
       </c>
       <c r="R57" t="n">
-        <v>6872521</v>
+        <v>6872487</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6447,50 +6221,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125073936</v>
+        <v>125073146</v>
       </c>
       <c r="B58" t="n">
-        <v>79536</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>473695</v>
+        <v>473748</v>
       </c>
       <c r="R58" t="n">
-        <v>6872466</v>
+        <v>6872493</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6552,12 +6330,7 @@
         <v>125072596</v>
       </c>
       <c r="B59" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6651,37 +6424,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125072602</v>
+        <v>125073052</v>
       </c>
       <c r="B60" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6691,10 +6459,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473742</v>
+        <v>473748</v>
       </c>
       <c r="R60" t="n">
-        <v>6872438</v>
+        <v>6872489</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6753,62 +6521,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125073146</v>
+        <v>125075491</v>
       </c>
       <c r="B61" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79585</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473748</v>
+        <v>473523</v>
       </c>
       <c r="R61" t="n">
-        <v>6872493</v>
+        <v>6872722</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6864,15 +6618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125072978</v>
+        <v>125074811</v>
       </c>
       <c r="B62" t="n">
-        <v>80029</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6880,34 +6629,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>473749</v>
+        <v>473732</v>
       </c>
       <c r="R62" t="n">
-        <v>6872487</v>
+        <v>6872579</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6966,15 +6715,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125073255</v>
+        <v>125072999</v>
       </c>
       <c r="B63" t="n">
-        <v>80029</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6982,21 +6726,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7006,10 +6750,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>473735</v>
+        <v>473747</v>
       </c>
       <c r="R63" t="n">
-        <v>6872503</v>
+        <v>6872493</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7068,37 +6812,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125072916</v>
+        <v>125073455</v>
       </c>
       <c r="B64" t="n">
-        <v>80064</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79556</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7108,10 +6847,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>473748</v>
+        <v>473712</v>
       </c>
       <c r="R64" t="n">
-        <v>6872490</v>
+        <v>6872517</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7170,59 +6909,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125074731</v>
+        <v>125074232</v>
       </c>
       <c r="B65" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473769</v>
+        <v>473700</v>
       </c>
       <c r="R65" t="n">
-        <v>6872532</v>
+        <v>6872562</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7281,15 +7006,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125076033</v>
+        <v>125074165</v>
       </c>
       <c r="B66" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78634</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7297,34 +7017,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>473693</v>
+        <v>473690</v>
       </c>
       <c r="R66" t="n">
-        <v>6872740</v>
+        <v>6872539</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7357,11 +7077,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7388,15 +7103,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125076393</v>
+        <v>125075154</v>
       </c>
       <c r="B67" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78634</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7404,21 +7114,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7428,10 +7138,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>473731</v>
+        <v>473625</v>
       </c>
       <c r="R67" t="n">
-        <v>6872691</v>
+        <v>6872585</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7464,11 +7174,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7495,15 +7200,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125075258</v>
+        <v>125075295</v>
       </c>
       <c r="B68" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7511,21 +7211,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7535,10 +7235,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>473585</v>
+        <v>473553</v>
       </c>
       <c r="R68" t="n">
-        <v>6872639</v>
+        <v>6872662</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7295,6 +7295,355 @@
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128666766</v>
+      </c>
+      <c r="B69" t="n">
+        <v>92760</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>473756</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6872629</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128667709</v>
+      </c>
+      <c r="B70" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>473762</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6872800</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128666711</v>
+      </c>
+      <c r="B71" t="n">
+        <v>80192</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>473783</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6872634</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -7300,7 +7300,7 @@
         <v>128666766</v>
       </c>
       <c r="B69" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>128667709</v>
       </c>
       <c r="B70" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -7300,7 +7300,7 @@
         <v>128666766</v>
       </c>
       <c r="B69" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>128667709</v>
       </c>
       <c r="B70" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>128666711</v>
       </c>
       <c r="B71" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -7300,7 +7300,7 @@
         <v>128666766</v>
       </c>
       <c r="B69" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>128667709</v>
       </c>
       <c r="B70" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -7300,7 +7300,7 @@
         <v>128666766</v>
       </c>
       <c r="B69" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>128667709</v>
       </c>
       <c r="B70" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>128666711</v>
       </c>
       <c r="B71" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -7300,7 +7300,7 @@
         <v>128666766</v>
       </c>
       <c r="B69" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>128667709</v>
       </c>
       <c r="B70" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>128666711</v>
       </c>
       <c r="B71" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -7300,7 +7300,7 @@
         <v>128666766</v>
       </c>
       <c r="B69" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>128667709</v>
       </c>
       <c r="B70" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -7300,7 +7300,7 @@
         <v>128666766</v>
       </c>
       <c r="B69" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>128667709</v>
       </c>
       <c r="B70" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>128666711</v>
       </c>
       <c r="B71" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -7300,7 +7300,7 @@
         <v>128666766</v>
       </c>
       <c r="B69" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>128667709</v>
       </c>
       <c r="B70" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>128666711</v>
       </c>
       <c r="B71" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -7300,7 +7300,7 @@
         <v>128666766</v>
       </c>
       <c r="B69" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>128667709</v>
       </c>
       <c r="B70" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>128666711</v>
       </c>
       <c r="B71" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -7300,7 +7300,7 @@
         <v>128666766</v>
       </c>
       <c r="B69" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>128667709</v>
       </c>
       <c r="B70" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>128666711</v>
       </c>
       <c r="B71" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -7300,7 +7300,7 @@
         <v>128666766</v>
       </c>
       <c r="B69" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>128667709</v>
       </c>
       <c r="B70" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>128666711</v>
       </c>
       <c r="B71" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124658443</v>
+        <v>125073107</v>
       </c>
       <c r="B2" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473856</v>
+        <v>473750</v>
       </c>
       <c r="R2" t="n">
-        <v>6872612</v>
+        <v>6872492</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124658172</v>
+        <v>124657817</v>
       </c>
       <c r="B3" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473877</v>
+        <v>473891</v>
       </c>
       <c r="R3" t="n">
-        <v>6872665</v>
+        <v>6872741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124659240</v>
+        <v>124658043</v>
       </c>
       <c r="B4" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473810</v>
+        <v>473876</v>
       </c>
       <c r="R4" t="n">
-        <v>6872485</v>
+        <v>6872692</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Extremt stenbundet område med mycket död ved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124659214</v>
+        <v>124658099</v>
       </c>
       <c r="B5" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473837</v>
+        <v>473890</v>
       </c>
       <c r="R5" t="n">
-        <v>6872441</v>
+        <v>6872676</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124657817</v>
+        <v>124827660</v>
       </c>
       <c r="B6" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473891</v>
+        <v>473782</v>
       </c>
       <c r="R6" t="n">
-        <v>6872741</v>
+        <v>6872817</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124658043</v>
+        <v>125073833</v>
       </c>
       <c r="B7" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,14 +1196,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473876</v>
+        <v>473697</v>
       </c>
       <c r="R7" t="n">
-        <v>6872692</v>
+        <v>6872466</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,17 +1230,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Extremt stenbundet område med mycket död ved.</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124658285</v>
+        <v>125074047</v>
       </c>
       <c r="B8" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,37 +1273,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473876</v>
+        <v>473665</v>
       </c>
       <c r="R8" t="n">
-        <v>6872637</v>
+        <v>6872487</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1362,12 +1327,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124828791</v>
+        <v>125074134</v>
       </c>
       <c r="B9" t="n">
-        <v>78331</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,37 +1370,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473589</v>
+        <v>473684</v>
       </c>
       <c r="R9" t="n">
-        <v>6872813</v>
+        <v>6872544</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1459,12 +1424,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124826941</v>
+        <v>125074165</v>
       </c>
       <c r="B10" t="n">
-        <v>78684</v>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1502,34 +1467,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473804</v>
+        <v>473690</v>
       </c>
       <c r="R10" t="n">
-        <v>6872761</v>
+        <v>6872539</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,12 +1521,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1588,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124827660</v>
+        <v>125074318</v>
       </c>
       <c r="B11" t="n">
-        <v>78592</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1623,13 +1588,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473782</v>
+        <v>473722</v>
       </c>
       <c r="R11" t="n">
-        <v>6872817</v>
+        <v>6872544</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1653,12 +1618,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124829793</v>
+        <v>125075154</v>
       </c>
       <c r="B12" t="n">
-        <v>80064</v>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473654</v>
+        <v>473625</v>
       </c>
       <c r="R12" t="n">
-        <v>6872997</v>
+        <v>6872585</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,12 +1715,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124828676</v>
+        <v>125075202</v>
       </c>
       <c r="B13" t="n">
-        <v>78684</v>
+        <v>78993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,13 +1782,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473614</v>
+        <v>473594</v>
       </c>
       <c r="R13" t="n">
-        <v>6872815</v>
+        <v>6872603</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1847,12 +1812,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124828245</v>
+        <v>125075258</v>
       </c>
       <c r="B14" t="n">
-        <v>78683</v>
+        <v>78993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473687</v>
+        <v>473585</v>
       </c>
       <c r="R14" t="n">
-        <v>6872750</v>
+        <v>6872639</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1944,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124829811</v>
+        <v>125075505</v>
       </c>
       <c r="B15" t="n">
-        <v>80063</v>
+        <v>78993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,13 +1976,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473654</v>
+        <v>473523</v>
       </c>
       <c r="R15" t="n">
-        <v>6872997</v>
+        <v>6872722</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2041,12 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2073,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124826736</v>
+        <v>125075883</v>
       </c>
       <c r="B16" t="n">
-        <v>78684</v>
+        <v>78993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2084,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2108,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473821</v>
+        <v>473613</v>
       </c>
       <c r="R16" t="n">
-        <v>6872738</v>
+        <v>6872761</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2138,12 +2103,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2170,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124827491</v>
+        <v>124658818</v>
       </c>
       <c r="B17" t="n">
-        <v>77874</v>
+        <v>79406</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2181,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6487</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2205,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473801</v>
+        <v>473855</v>
       </c>
       <c r="R17" t="n">
-        <v>6872850</v>
+        <v>6872547</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2235,12 +2200,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2267,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124828707</v>
+        <v>125072978</v>
       </c>
       <c r="B18" t="n">
-        <v>78683</v>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2278,37 +2243,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473614</v>
+        <v>473749</v>
       </c>
       <c r="R18" t="n">
-        <v>6872815</v>
+        <v>6872487</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2332,12 +2297,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2364,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124827627</v>
+        <v>125073255</v>
       </c>
       <c r="B19" t="n">
-        <v>78684</v>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2375,34 +2340,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473780</v>
+        <v>473735</v>
       </c>
       <c r="R19" t="n">
-        <v>6872856</v>
+        <v>6872503</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2429,12 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2461,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124827497</v>
+        <v>125074741</v>
       </c>
       <c r="B20" t="n">
-        <v>79536</v>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2472,21 +2437,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2496,13 +2461,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473801</v>
+        <v>473756</v>
       </c>
       <c r="R20" t="n">
-        <v>6872850</v>
+        <v>6872526</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2526,12 +2491,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2558,10 +2523,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124828799</v>
+        <v>128667709</v>
       </c>
       <c r="B21" t="n">
-        <v>77874</v>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2569,34 +2534,48 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473591</v>
+        <v>473762</v>
       </c>
       <c r="R21" t="n">
-        <v>6872817</v>
+        <v>6872800</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2623,12 +2602,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2655,10 +2644,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124827748</v>
+        <v>128666766</v>
       </c>
       <c r="B22" t="n">
-        <v>78684</v>
+        <v>93209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2666,37 +2655,51 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473754</v>
+        <v>473756</v>
       </c>
       <c r="R22" t="n">
-        <v>6872803</v>
+        <v>6872629</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2720,12 +2723,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2752,32 +2765,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124828081</v>
+        <v>125074811</v>
       </c>
       <c r="B23" t="n">
-        <v>79536</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2800,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473705</v>
+        <v>473732</v>
       </c>
       <c r="R23" t="n">
-        <v>6872721</v>
+        <v>6872579</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2817,12 +2830,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2849,10 +2862,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125072602</v>
+        <v>124828791</v>
       </c>
       <c r="B24" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2860,34 +2873,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473742</v>
+        <v>473589</v>
       </c>
       <c r="R24" t="n">
-        <v>6872438</v>
+        <v>6872813</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2914,12 +2927,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2946,10 +2959,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125075258</v>
+        <v>124828245</v>
       </c>
       <c r="B25" t="n">
-        <v>78634</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2957,21 +2970,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2994,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473585</v>
+        <v>473687</v>
       </c>
       <c r="R25" t="n">
-        <v>6872639</v>
+        <v>6872750</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3011,12 +3024,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3043,10 +3056,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125076393</v>
+        <v>124828707</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3054,21 +3067,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3078,13 +3091,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473731</v>
+        <v>473614</v>
       </c>
       <c r="R26" t="n">
-        <v>6872691</v>
+        <v>6872815</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3108,17 +3121,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3145,10 +3153,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125075336</v>
+        <v>125072596</v>
       </c>
       <c r="B27" t="n">
-        <v>78726</v>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3156,34 +3164,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473532</v>
+        <v>473742</v>
       </c>
       <c r="R27" t="n">
-        <v>6872688</v>
+        <v>6872438</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3242,10 +3250,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125074741</v>
+        <v>125072658</v>
       </c>
       <c r="B28" t="n">
-        <v>80071</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3253,34 +3261,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473756</v>
+        <v>473760</v>
       </c>
       <c r="R28" t="n">
-        <v>6872526</v>
+        <v>6872467</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3339,10 +3347,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125073107</v>
+        <v>125072827</v>
       </c>
       <c r="B29" t="n">
-        <v>78999</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3350,21 +3358,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3374,13 +3382,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473750</v>
+        <v>473758</v>
       </c>
       <c r="R29" t="n">
-        <v>6872492</v>
+        <v>6872471</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3436,48 +3444,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125073267</v>
+        <v>125075349</v>
       </c>
       <c r="B30" t="n">
-        <v>80099</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473732</v>
+        <v>473530</v>
       </c>
       <c r="R30" t="n">
-        <v>6872498</v>
+        <v>6872681</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3533,57 +3541,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125073474</v>
+        <v>125075491</v>
       </c>
       <c r="B31" t="n">
-        <v>98324</v>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473716</v>
+        <v>473523</v>
       </c>
       <c r="R31" t="n">
-        <v>6872520</v>
+        <v>6872722</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3639,57 +3638,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125073578</v>
+        <v>125075710</v>
       </c>
       <c r="B32" t="n">
-        <v>98345</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473736</v>
+        <v>473570</v>
       </c>
       <c r="R32" t="n">
-        <v>6872499</v>
+        <v>6872751</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3745,10 +3735,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125073833</v>
+        <v>124659214</v>
       </c>
       <c r="B33" t="n">
-        <v>78634</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3756,37 +3746,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473697</v>
+        <v>473837</v>
       </c>
       <c r="R33" t="n">
-        <v>6872466</v>
+        <v>6872441</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3810,12 +3800,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3842,10 +3832,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125072827</v>
+        <v>124659240</v>
       </c>
       <c r="B34" t="n">
-        <v>78725</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3853,37 +3843,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473758</v>
+        <v>473810</v>
       </c>
       <c r="R34" t="n">
-        <v>6872471</v>
+        <v>6872485</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3907,12 +3897,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3939,10 +3929,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125074318</v>
+        <v>125071501</v>
       </c>
       <c r="B35" t="n">
-        <v>78634</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3950,37 +3940,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473722</v>
+        <v>473868</v>
       </c>
       <c r="R35" t="n">
-        <v>6872544</v>
+        <v>6872587</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4036,10 +4026,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125075710</v>
+        <v>125072999</v>
       </c>
       <c r="B36" t="n">
-        <v>79585</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4047,34 +4037,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473570</v>
+        <v>473747</v>
       </c>
       <c r="R36" t="n">
-        <v>6872751</v>
+        <v>6872493</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4133,10 +4123,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125073338</v>
+        <v>125076500</v>
       </c>
       <c r="B37" t="n">
-        <v>79556</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4144,37 +4134,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473722</v>
+        <v>473798</v>
       </c>
       <c r="R37" t="n">
-        <v>6872521</v>
+        <v>6872597</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4230,10 +4220,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125075883</v>
+        <v>128666711</v>
       </c>
       <c r="B38" t="n">
-        <v>78634</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4241,21 +4231,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4265,10 +4255,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473613</v>
+        <v>473783</v>
       </c>
       <c r="R38" t="n">
-        <v>6872761</v>
+        <v>6872634</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4295,12 +4285,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4327,48 +4327,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125075202</v>
+        <v>125073052</v>
       </c>
       <c r="B39" t="n">
-        <v>78634</v>
+        <v>80461</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473594</v>
+        <v>473748</v>
       </c>
       <c r="R39" t="n">
-        <v>6872603</v>
+        <v>6872489</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4424,45 +4424,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125075505</v>
+        <v>125073267</v>
       </c>
       <c r="B40" t="n">
-        <v>78634</v>
+        <v>80461</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473523</v>
+        <v>473732</v>
       </c>
       <c r="R40" t="n">
-        <v>6872722</v>
+        <v>6872498</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4521,45 +4521,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125072978</v>
+        <v>124829811</v>
       </c>
       <c r="B41" t="n">
-        <v>80071</v>
+        <v>80467</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473749</v>
+        <v>473654</v>
       </c>
       <c r="R41" t="n">
-        <v>6872487</v>
+        <v>6872997</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4618,54 +4618,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125074731</v>
+        <v>124829793</v>
       </c>
       <c r="B42" t="n">
-        <v>98324</v>
+        <v>80468</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473769</v>
+        <v>473654</v>
       </c>
       <c r="R42" t="n">
-        <v>6872532</v>
+        <v>6872997</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4692,12 +4683,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4724,54 +4715,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125073530</v>
+        <v>125072916</v>
       </c>
       <c r="B43" t="n">
-        <v>98324</v>
+        <v>80468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473728</v>
+        <v>473748</v>
       </c>
       <c r="R43" t="n">
-        <v>6872500</v>
+        <v>6872490</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4830,10 +4812,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125076500</v>
+        <v>124827491</v>
       </c>
       <c r="B44" t="n">
-        <v>80070</v>
+        <v>78334</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4841,21 +4823,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4865,13 +4847,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473798</v>
+        <v>473801</v>
       </c>
       <c r="R44" t="n">
-        <v>6872597</v>
+        <v>6872850</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4895,12 +4877,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4927,10 +4909,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125073255</v>
+        <v>124828799</v>
       </c>
       <c r="B45" t="n">
-        <v>80071</v>
+        <v>78334</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4938,34 +4920,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6487</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473735</v>
+        <v>473591</v>
       </c>
       <c r="R45" t="n">
-        <v>6872503</v>
+        <v>6872817</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4992,12 +4974,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5027,7 +5009,7 @@
         <v>125076033</v>
       </c>
       <c r="B46" t="n">
-        <v>57651</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5126,10 +5108,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125075630</v>
+        <v>125076393</v>
       </c>
       <c r="B47" t="n">
-        <v>79556</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5137,21 +5119,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5161,13 +5143,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473566</v>
+        <v>473731</v>
       </c>
       <c r="R47" t="n">
-        <v>6872757</v>
+        <v>6872691</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5197,6 +5179,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5223,32 +5210,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125073430</v>
+        <v>125071546</v>
       </c>
       <c r="B48" t="n">
-        <v>57811</v>
+        <v>57141</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5258,13 +5245,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473712</v>
+        <v>473832</v>
       </c>
       <c r="R48" t="n">
-        <v>6872523</v>
+        <v>6872552</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5298,7 +5285,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Konstaterad på läte.</t>
+          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5325,32 +5312,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125072916</v>
+        <v>125073430</v>
       </c>
       <c r="B49" t="n">
-        <v>80106</v>
+        <v>58114</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5360,13 +5347,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473748</v>
+        <v>473712</v>
       </c>
       <c r="R49" t="n">
-        <v>6872490</v>
+        <v>6872523</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5396,6 +5383,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Konstaterad på läte.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5422,10 +5414,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125074681</v>
+        <v>125073146</v>
       </c>
       <c r="B50" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5452,7 +5444,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5462,14 +5454,14 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473765</v>
+        <v>473748</v>
       </c>
       <c r="R50" t="n">
-        <v>6872521</v>
+        <v>6872493</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5528,10 +5520,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125074664</v>
+        <v>125073474</v>
       </c>
       <c r="B51" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5558,7 +5550,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5568,14 +5560,14 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473761</v>
+        <v>473716</v>
       </c>
       <c r="R51" t="n">
-        <v>6872503</v>
+        <v>6872520</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5634,48 +5626,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125074134</v>
+        <v>125073530</v>
       </c>
       <c r="B52" t="n">
-        <v>78634</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473684</v>
+        <v>473728</v>
       </c>
       <c r="R52" t="n">
-        <v>6872544</v>
+        <v>6872500</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5731,45 +5732,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125071546</v>
+        <v>125074664</v>
       </c>
       <c r="B53" t="n">
-        <v>56843</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473832</v>
+        <v>473761</v>
       </c>
       <c r="R53" t="n">
-        <v>6872552</v>
+        <v>6872503</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5802,11 +5812,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Spillning under barrgles tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5833,45 +5838,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125073936</v>
+        <v>125074681</v>
       </c>
       <c r="B54" t="n">
-        <v>79556</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473695</v>
+        <v>473765</v>
       </c>
       <c r="R54" t="n">
-        <v>6872466</v>
+        <v>6872521</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5930,45 +5944,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125072658</v>
+        <v>125074731</v>
       </c>
       <c r="B55" t="n">
-        <v>78725</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473760</v>
+        <v>473769</v>
       </c>
       <c r="R55" t="n">
-        <v>6872467</v>
+        <v>6872532</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6027,48 +6050,57 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125075349</v>
+        <v>125073578</v>
       </c>
       <c r="B56" t="n">
-        <v>78725</v>
+        <v>99140</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473530</v>
+        <v>473736</v>
       </c>
       <c r="R56" t="n">
-        <v>6872681</v>
+        <v>6872499</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6124,10 +6156,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125074047</v>
+        <v>124658172</v>
       </c>
       <c r="B57" t="n">
-        <v>78634</v>
+        <v>79085</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6135,37 +6167,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473665</v>
+        <v>473877</v>
       </c>
       <c r="R57" t="n">
-        <v>6872487</v>
+        <v>6872665</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6189,12 +6221,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6221,54 +6253,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125073146</v>
+        <v>124658285</v>
       </c>
       <c r="B58" t="n">
-        <v>98324</v>
+        <v>79085</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>473748</v>
+        <v>473876</v>
       </c>
       <c r="R58" t="n">
-        <v>6872493</v>
+        <v>6872637</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6295,12 +6318,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6327,10 +6350,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125072596</v>
+        <v>124658443</v>
       </c>
       <c r="B59" t="n">
-        <v>78725</v>
+        <v>79085</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6338,34 +6361,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473742</v>
+        <v>473856</v>
       </c>
       <c r="R59" t="n">
-        <v>6872438</v>
+        <v>6872612</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6392,12 +6415,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6424,45 +6447,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125073052</v>
+        <v>124826736</v>
       </c>
       <c r="B60" t="n">
-        <v>80099</v>
+        <v>79085</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473748</v>
+        <v>473821</v>
       </c>
       <c r="R60" t="n">
-        <v>6872489</v>
+        <v>6872738</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6489,12 +6512,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6521,10 +6544,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125075491</v>
+        <v>124826941</v>
       </c>
       <c r="B61" t="n">
-        <v>79585</v>
+        <v>79085</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6532,21 +6555,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6556,13 +6579,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473523</v>
+        <v>473804</v>
       </c>
       <c r="R61" t="n">
-        <v>6872722</v>
+        <v>6872761</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6586,12 +6609,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6618,10 +6641,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125074811</v>
+        <v>124827627</v>
       </c>
       <c r="B62" t="n">
-        <v>78967</v>
+        <v>79085</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6629,21 +6652,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6653,10 +6676,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>473732</v>
+        <v>473780</v>
       </c>
       <c r="R62" t="n">
-        <v>6872579</v>
+        <v>6872856</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6683,12 +6706,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6715,10 +6738,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125072999</v>
+        <v>124827748</v>
       </c>
       <c r="B63" t="n">
-        <v>80070</v>
+        <v>79085</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6726,37 +6749,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>473747</v>
+        <v>473754</v>
       </c>
       <c r="R63" t="n">
-        <v>6872493</v>
+        <v>6872803</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6780,12 +6803,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6812,10 +6835,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125073455</v>
+        <v>124828676</v>
       </c>
       <c r="B64" t="n">
-        <v>79556</v>
+        <v>79085</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6823,34 +6846,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Digerflon, Digerflon, Hjd</t>
+          <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>473712</v>
+        <v>473614</v>
       </c>
       <c r="R64" t="n">
-        <v>6872517</v>
+        <v>6872815</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6877,12 +6900,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6909,10 +6932,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125074232</v>
+        <v>125072602</v>
       </c>
       <c r="B65" t="n">
-        <v>78726</v>
+        <v>79085</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6944,10 +6967,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>473700</v>
+        <v>473742</v>
       </c>
       <c r="R65" t="n">
-        <v>6872562</v>
+        <v>6872438</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7006,10 +7029,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125074165</v>
+        <v>125074232</v>
       </c>
       <c r="B66" t="n">
-        <v>78634</v>
+        <v>79085</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7017,21 +7040,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7041,10 +7064,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>473690</v>
+        <v>473700</v>
       </c>
       <c r="R66" t="n">
-        <v>6872539</v>
+        <v>6872562</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7103,10 +7126,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125075154</v>
+        <v>125075295</v>
       </c>
       <c r="B67" t="n">
-        <v>78634</v>
+        <v>79085</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7114,21 +7137,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7138,13 +7161,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>473625</v>
+        <v>473553</v>
       </c>
       <c r="R67" t="n">
-        <v>6872585</v>
+        <v>6872662</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7200,10 +7223,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125075295</v>
+        <v>125075336</v>
       </c>
       <c r="B68" t="n">
-        <v>78726</v>
+        <v>79085</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7235,13 +7258,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>473553</v>
+        <v>473532</v>
       </c>
       <c r="R68" t="n">
-        <v>6872662</v>
+        <v>6872688</v>
       </c>
       <c r="S68" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7297,62 +7320,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128666766</v>
+        <v>124827497</v>
       </c>
       <c r="B69" t="n">
-        <v>92838</v>
+        <v>79917</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4366</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>473756</v>
+        <v>473801</v>
       </c>
       <c r="R69" t="n">
-        <v>6872629</v>
+        <v>6872850</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7376,22 +7385,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:33</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:33</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7418,59 +7417,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128667709</v>
+        <v>124828081</v>
       </c>
       <c r="B70" t="n">
-        <v>92826</v>
+        <v>79917</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Brännberget, Brännberget, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>473762</v>
+        <v>473705</v>
       </c>
       <c r="R70" t="n">
-        <v>6872800</v>
+        <v>6872721</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7497,22 +7482,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>12:33</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>12:33</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7539,10 +7514,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128666711</v>
+        <v>125073338</v>
       </c>
       <c r="B71" t="n">
-        <v>80144</v>
+        <v>79917</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7550,37 +7525,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Brännberget, Brännberget, Hjd</t>
+          <t>Digerflon, Digerflon, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>473783</v>
+        <v>473722</v>
       </c>
       <c r="R71" t="n">
-        <v>6872634</v>
+        <v>6872521</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7604,22 +7579,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>12:33</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>12:33</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7643,6 +7608,297 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>125073455</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>473712</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6872517</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>125073936</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Digerflon, Digerflon, Hjd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>473695</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6872466</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>125075630</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Brännberget, Brännberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>473566</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6872757</v>
+      </c>
+      <c r="S74" t="n">
+        <v>20</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18116-2025 artfynd.xlsx
+++ b/artfynd/A 18116-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125073107</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124657817</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124658043</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124658099</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124827660</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125073833</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125074047</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125074134</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125074165</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125074318</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125075154</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125075202</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125075258</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125075505</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125075883</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124658818</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125072978</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125073255</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125074741</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2641,6 +2741,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128667709</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2762,6 +2867,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128666766</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2859,6 +2969,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125074811</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2956,6 +3071,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124828791</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3053,6 +3173,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124828245</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3150,6 +3275,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124828707</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3247,6 +3377,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125072596</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3344,6 +3479,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125072658</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3441,6 +3581,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125072827</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3538,6 +3683,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125075349</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3635,6 +3785,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125075491</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3732,6 +3887,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125075710</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3829,6 +3989,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124659214</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3926,6 +4091,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124659240</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4023,6 +4193,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125071501</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4120,6 +4295,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125072999</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4217,6 +4397,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125076500</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4324,6 +4509,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128666711</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4421,6 +4611,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125073052</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4518,6 +4713,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125073267</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4615,6 +4815,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124829811</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4712,6 +4917,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124829793</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4809,6 +5019,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125072916</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4906,6 +5121,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124827491</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5003,6 +5223,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124828799</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5105,6 +5330,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125076033</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5207,6 +5437,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125076393</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5309,6 +5544,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125071546</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5411,6 +5651,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125073430</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5517,6 +5762,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125073146</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5623,6 +5873,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125073474</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5729,6 +5984,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125073530</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5835,6 +6095,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125074664</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5941,6 +6206,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125074681</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6047,6 +6317,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125074731</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6153,6 +6428,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125073578</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6250,6 +6530,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124658172</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6347,6 +6632,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124658285</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6444,6 +6734,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124658443</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6541,6 +6836,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124826736</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6638,6 +6938,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124826941</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6735,6 +7040,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124827627</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6832,6 +7142,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124827748</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6929,6 +7244,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124828676</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7026,6 +7346,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125072602</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7123,6 +7448,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125074232</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7220,6 +7550,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125075295</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7317,6 +7652,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125075336</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7414,6 +7754,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124827497</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7511,6 +7856,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124828081</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7608,6 +7958,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125073338</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7705,6 +8060,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125073455</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7802,6 +8162,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125073936</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7899,8 +8264,88 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125075630</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>